--- a/research/traditional_assets/database/data/mexico/mexico_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_telecom_wireless.xlsx
@@ -650,10 +650,10 @@
         <v>0.08925973835212062</v>
       </c>
       <c r="X2">
-        <v>0.1165357604888319</v>
+        <v>0.1165197960230164</v>
       </c>
       <c r="Y2">
-        <v>-0.02727602213671129</v>
+        <v>-0.02726005767089576</v>
       </c>
       <c r="Z2">
         <v>0.8912009587221508</v>
@@ -662,10 +662,10 @@
         <v>0.0964206874550102</v>
       </c>
       <c r="AB2">
-        <v>0.08624894867000292</v>
+        <v>0.08624046596652245</v>
       </c>
       <c r="AC2">
-        <v>0.01017173878500728</v>
+        <v>0.01018022148848775</v>
       </c>
       <c r="AD2">
         <v>38612.2</v>
@@ -787,10 +787,10 @@
         <v>0.08925973835212062</v>
       </c>
       <c r="X3">
-        <v>0.1165357604888319</v>
+        <v>0.1165197960230164</v>
       </c>
       <c r="Y3">
-        <v>-0.02727602213671129</v>
+        <v>-0.02726005767089576</v>
       </c>
       <c r="Z3">
         <v>0.8912009587221508</v>
@@ -799,10 +799,10 @@
         <v>0.0964206874550102</v>
       </c>
       <c r="AB3">
-        <v>0.08624894867000292</v>
+        <v>0.08624046596652245</v>
       </c>
       <c r="AC3">
-        <v>0.01017173878500728</v>
+        <v>0.01018022148848775</v>
       </c>
       <c r="AD3">
         <v>38612.2</v>
@@ -1139,49 +1139,49 @@
         <v>2.39488144523899</v>
       </c>
       <c r="F2">
-        <v>3.00496286790986</v>
+        <v>3.02392069061187</v>
       </c>
       <c r="G2">
         <v>2.73569879979028</v>
       </c>
       <c r="H2">
-        <v>2.04308674951467</v>
+        <v>2.10146065664366</v>
       </c>
       <c r="I2">
         <v>0.468650966560303</v>
       </c>
       <c r="J2">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K2">
         <v>43777.9</v>
       </c>
       <c r="L2">
-        <v>51993.0078509897</v>
+        <v>51913.1784053095</v>
       </c>
       <c r="M2">
         <v>81121.7</v>
       </c>
       <c r="N2">
-        <v>79561.14285098969</v>
+        <v>80305.2144053095</v>
       </c>
       <c r="O2">
         <v>38612.2</v>
       </c>
       <c r="P2">
-        <v>28836.535</v>
+        <v>29660.436</v>
       </c>
       <c r="Q2">
-        <v>0.08624894867000291</v>
+        <v>0.08624046596652241</v>
       </c>
       <c r="R2">
-        <v>0.08771769413085501</v>
+        <v>0.0870017895133124</v>
       </c>
       <c r="S2">
         <v>0.051910241755517</v>
       </c>
       <c r="T2">
-        <v>0.053730241755517</v>
+        <v>0.051910241755517</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.116535760488832</v>
+        <v>0.116519796023016</v>
       </c>
       <c r="X2">
-        <v>0.106018630025268</v>
+        <v>0.106740785127072</v>
       </c>
       <c r="Y2">
         <v>1.02905920158558</v>
       </c>
       <c r="Z2">
-        <v>0.876056677784124</v>
+        <v>0.886762677687213</v>
       </c>
       <c r="AA2">
         <v>38612.2</v>
@@ -1236,7 +1236,7 @@
         <v>43777.9</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524601</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08953420057701014</v>
+        <v>0.08952433013601599</v>
       </c>
       <c r="C2">
-        <v>78980.60517170675</v>
+        <v>78981.95938756995</v>
       </c>
       <c r="D2">
-        <v>77712.20517170675</v>
+        <v>77713.55938756996</v>
       </c>
       <c r="E2">
         <v>-38612.2</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08953420057701014</v>
+        <v>0.08952433013601599</v>
       </c>
       <c r="T2">
         <v>0.6362422799549506</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08943890039283429</v>
+        <v>0.0894192595631631</v>
       </c>
       <c r="C3">
-        <v>78251.56722700506</v>
+        <v>78262.66457292988</v>
       </c>
       <c r="D3">
-        <v>77807.06822700506</v>
+        <v>77818.16557292988</v>
       </c>
       <c r="E3">
         <v>-37788.299</v>
@@ -1539,37 +1539,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M3">
-        <v>58.13238510373171</v>
+        <v>56.97892370373172</v>
       </c>
       <c r="N3">
-        <v>6593.112512855453</v>
+        <v>6594.265974255452</v>
       </c>
       <c r="O3">
-        <v>1977.933753856636</v>
+        <v>1978.279792276636</v>
       </c>
       <c r="P3">
-        <v>4615.178758998817</v>
+        <v>4615.986181978817</v>
       </c>
       <c r="Q3">
-        <v>12366.17875899882</v>
+        <v>12366.98618197882</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08984343229826174</v>
+        <v>0.08983349206627064</v>
       </c>
       <c r="T3">
         <v>0.6407409627425109</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.4154826279822</v>
+        <v>116.7316696353037</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08934360020865843</v>
+        <v>0.08931418899031024</v>
       </c>
       <c r="C4">
-        <v>77522.761163453</v>
+        <v>77543.65174776557</v>
       </c>
       <c r="D4">
-        <v>77902.16316345301</v>
+        <v>77923.05374776557</v>
       </c>
       <c r="E4">
         <v>-36964.39799999999</v>
@@ -1621,37 +1621,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M4">
-        <v>116.2647702074634</v>
+        <v>113.9578474074634</v>
       </c>
       <c r="N4">
-        <v>6534.980127751721</v>
+        <v>6537.287050551721</v>
       </c>
       <c r="O4">
-        <v>1960.494038325516</v>
+        <v>1961.186115165516</v>
       </c>
       <c r="P4">
-        <v>4574.486089426205</v>
+        <v>4576.100935386205</v>
       </c>
       <c r="Q4">
-        <v>12325.48608942621</v>
+        <v>12327.1009353862</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09015897487096744</v>
+        <v>0.09014896342367337</v>
       </c>
       <c r="T4">
         <v>0.6453314553828785</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.20774131399107</v>
+        <v>58.36583481765184</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08924830002448256</v>
+        <v>0.08920911841745735</v>
       </c>
       <c r="C5">
-        <v>76794.18783229869</v>
+        <v>76824.92205386506</v>
       </c>
       <c r="D5">
-        <v>77997.49083229869</v>
+        <v>78028.22505386506</v>
       </c>
       <c r="E5">
         <v>-36140.497</v>
@@ -1703,37 +1703,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M5">
-        <v>174.3971553111951</v>
+        <v>170.9367711111951</v>
       </c>
       <c r="N5">
-        <v>6476.847742647989</v>
+        <v>6480.308126847989</v>
       </c>
       <c r="O5">
-        <v>1943.054322794397</v>
+        <v>1944.092438054397</v>
       </c>
       <c r="P5">
-        <v>4533.793419853593</v>
+        <v>4536.215688793593</v>
       </c>
       <c r="Q5">
-        <v>12284.79341985359</v>
+        <v>12287.21568879359</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09048102347610006</v>
+        <v>0.09047093934514623</v>
       </c>
       <c r="T5">
         <v>0.6500165973560371</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.13849420932739</v>
+        <v>38.91055654510123</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.0891529998403067</v>
+        <v>0.08910404784460449</v>
       </c>
       <c r="C6">
-        <v>76065.84808896192</v>
+        <v>76106.47663918874</v>
       </c>
       <c r="D6">
-        <v>78093.05208896194</v>
+        <v>78133.68063918875</v>
       </c>
       <c r="E6">
         <v>-35316.596</v>
@@ -1785,37 +1785,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M6">
-        <v>232.5295404149269</v>
+        <v>227.9156948149269</v>
       </c>
       <c r="N6">
-        <v>6418.715357544258</v>
+        <v>6423.329203144258</v>
       </c>
       <c r="O6">
-        <v>1925.614607263277</v>
+        <v>1926.998760943277</v>
       </c>
       <c r="P6">
-        <v>4493.100750280981</v>
+        <v>4496.330442200981</v>
       </c>
       <c r="Q6">
-        <v>12244.10075028098</v>
+        <v>12247.33044220098</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09080978142717294</v>
+        <v>0.09079962309831646</v>
       </c>
       <c r="T6">
         <v>0.6547993464536367</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.60387065699554</v>
+        <v>29.18291740882592</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08905769965613085</v>
+        <v>0.08899897727175161</v>
       </c>
       <c r="C7">
-        <v>75337.74279305989</v>
+        <v>75388.31665791151</v>
       </c>
       <c r="D7">
-        <v>78188.8477930599</v>
+        <v>78239.42165791152</v>
       </c>
       <c r="E7">
         <v>-34492.695</v>
@@ -1867,37 +1867,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M7">
-        <v>290.6619255186586</v>
+        <v>284.8946185186585</v>
       </c>
       <c r="N7">
-        <v>6360.582972440526</v>
+        <v>6366.350279440526</v>
       </c>
       <c r="O7">
-        <v>1908.174891732158</v>
+        <v>1909.905083832158</v>
       </c>
       <c r="P7">
-        <v>4452.408080708368</v>
+        <v>4456.445195608369</v>
       </c>
       <c r="Q7">
-        <v>12203.40808070837</v>
+        <v>12207.44519560837</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09114546059826842</v>
+        <v>0.09113522650944816</v>
       </c>
       <c r="T7">
         <v>0.6596827850059225</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.88309652559643</v>
+        <v>23.34633392706074</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08896239947195499</v>
+        <v>0.08889390669889871</v>
       </c>
       <c r="C8">
-        <v>74609.87280843289</v>
+        <v>74670.44327046453</v>
       </c>
       <c r="D8">
-        <v>78284.8788084329</v>
+        <v>78345.44927046454</v>
       </c>
       <c r="E8">
         <v>-33668.79399999999</v>
@@ -1949,37 +1949,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M8">
-        <v>348.7943106223902</v>
+        <v>341.8735422223903</v>
       </c>
       <c r="N8">
-        <v>6302.450587336794</v>
+        <v>6309.371355736795</v>
       </c>
       <c r="O8">
-        <v>1890.735176201038</v>
+        <v>1892.811406721038</v>
       </c>
       <c r="P8">
-        <v>4411.715411135756</v>
+        <v>4416.559949015757</v>
       </c>
       <c r="Q8">
-        <v>12162.71541113576</v>
+        <v>12167.55994901576</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09148828187938719</v>
+        <v>0.09147797041868905</v>
       </c>
       <c r="T8">
         <v>0.6646701265061292</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.0692471046637</v>
+        <v>19.45527827255061</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08886709928777911</v>
+        <v>0.08878883612604582</v>
       </c>
       <c r="C9">
-        <v>73882.23900317025</v>
+        <v>73952.85764357782</v>
       </c>
       <c r="D9">
-        <v>78381.14600317026</v>
+        <v>78451.76464357783</v>
       </c>
       <c r="E9">
         <v>-32844.893</v>
@@ -2031,37 +2031,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M9">
-        <v>406.926695726122</v>
+        <v>398.852465926122</v>
       </c>
       <c r="N9">
-        <v>6244.318202233062</v>
+        <v>6252.392432033063</v>
       </c>
       <c r="O9">
-        <v>1873.295460669919</v>
+        <v>1875.717729609919</v>
       </c>
       <c r="P9">
-        <v>4371.022741563143</v>
+        <v>4376.674702423144</v>
       </c>
       <c r="Q9">
-        <v>12122.02274156314</v>
+        <v>12127.67470242314</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0918384756611752</v>
+        <v>0.09182808516468779</v>
       </c>
       <c r="T9">
         <v>0.6697647226622545</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.34506894685459</v>
+        <v>16.67595280504338</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08877179910360328</v>
+        <v>0.08868376555319298</v>
       </c>
       <c r="C10">
-        <v>73154.84224963649</v>
+        <v>73235.56095032305</v>
       </c>
       <c r="D10">
-        <v>78477.6502496365</v>
+        <v>78558.36895032306</v>
       </c>
       <c r="E10">
         <v>-32020.992</v>
@@ -2113,37 +2113,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M10">
-        <v>465.0590808298537</v>
+        <v>455.8313896298537</v>
       </c>
       <c r="N10">
-        <v>6186.185817129331</v>
+        <v>6195.41350832933</v>
       </c>
       <c r="O10">
-        <v>1855.855745138799</v>
+        <v>1858.624052498799</v>
       </c>
       <c r="P10">
-        <v>4330.330071990531</v>
+        <v>4336.789455830532</v>
       </c>
       <c r="Q10">
-        <v>12081.33007199053</v>
+        <v>12087.78945583053</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09219628235126295</v>
+        <v>0.09218581110081697</v>
       </c>
       <c r="T10">
         <v>0.6749700709087303</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.30193532849777</v>
+        <v>14.59145870441296</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0886764989194274</v>
+        <v>0.08857869498034009</v>
       </c>
       <c r="C11">
-        <v>72427.68342449785</v>
+        <v>72518.55437015682</v>
       </c>
       <c r="D11">
-        <v>78574.39242449786</v>
+        <v>78665.26337015683</v>
       </c>
       <c r="E11">
         <v>-31197.091</v>
@@ -2195,37 +2195,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M11">
-        <v>523.1914659335854</v>
+        <v>512.8103133335854</v>
       </c>
       <c r="N11">
-        <v>6128.053432025599</v>
+        <v>6138.434584625599</v>
       </c>
       <c r="O11">
-        <v>1838.41602960768</v>
+        <v>1841.53037538768</v>
       </c>
       <c r="P11">
-        <v>4289.637402417919</v>
+        <v>4296.90420923792</v>
       </c>
       <c r="Q11">
-        <v>12040.63740241792</v>
+        <v>12047.90420923792</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09256195292464932</v>
+        <v>0.09255139914543248</v>
       </c>
       <c r="T11">
         <v>0.6802898224133703</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.71283140310913</v>
+        <v>12.97018551503374</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08858119873525154</v>
+        <v>0.08847362440748721</v>
       </c>
       <c r="C12">
-        <v>71700.76340874853</v>
+        <v>71801.83908896385</v>
       </c>
       <c r="D12">
-        <v>78671.37340874854</v>
+        <v>78772.44908896385</v>
       </c>
       <c r="E12">
         <v>-30373.19</v>
@@ -2277,37 +2277,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M12">
-        <v>581.3238510373171</v>
+        <v>569.7892370373171</v>
       </c>
       <c r="N12">
-        <v>6069.921046921867</v>
+        <v>6081.455660921867</v>
       </c>
       <c r="O12">
-        <v>1820.97631407656</v>
+        <v>1824.43669827656</v>
       </c>
       <c r="P12">
-        <v>4248.944732845307</v>
+        <v>4257.018962645307</v>
       </c>
       <c r="Q12">
-        <v>11999.94473284531</v>
+        <v>12008.01896264531</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0929357495107776</v>
+        <v>0.09292511136881723</v>
       </c>
       <c r="T12">
         <v>0.6857277906181134</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.44154826279821</v>
+        <v>11.67316696353037</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08848589855107569</v>
+        <v>0.08836855383463435</v>
       </c>
       <c r="C13">
-        <v>70974.0830877377</v>
+        <v>71085.41629910108</v>
       </c>
       <c r="D13">
-        <v>78768.5940877377</v>
+        <v>78879.92729910109</v>
       </c>
       <c r="E13">
         <v>-29549.289</v>
@@ -2359,37 +2359,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M13">
-        <v>639.4562361410489</v>
+        <v>626.7681607410489</v>
       </c>
       <c r="N13">
-        <v>6011.788661818136</v>
+        <v>6024.476737218136</v>
       </c>
       <c r="O13">
-        <v>1803.536598545441</v>
+        <v>1807.343021165441</v>
       </c>
       <c r="P13">
-        <v>4208.252063272695</v>
+        <v>4217.133716052695</v>
       </c>
       <c r="Q13">
-        <v>11959.2520632727</v>
+        <v>11968.1337160527</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09331794602018968</v>
+        <v>0.09330722161969379</v>
       </c>
       <c r="T13">
         <v>0.6912879603555475</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.40140751163474</v>
+        <v>10.61196996684579</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08839059836689982</v>
+        <v>0.08826348326178146</v>
       </c>
       <c r="C14">
-        <v>70247.64335119633</v>
+        <v>70369.2871994419</v>
       </c>
       <c r="D14">
-        <v>78866.05535119634</v>
+        <v>78987.69919944191</v>
       </c>
       <c r="E14">
         <v>-28725.388</v>
@@ -2441,37 +2441,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M14">
-        <v>697.5886212447805</v>
+        <v>683.7470844447805</v>
       </c>
       <c r="N14">
-        <v>5953.656276714404</v>
+        <v>5967.497813514404</v>
       </c>
       <c r="O14">
-        <v>1786.096883014321</v>
+        <v>1790.249344054321</v>
       </c>
       <c r="P14">
-        <v>4167.559393700083</v>
+        <v>4177.248469460083</v>
       </c>
       <c r="Q14">
-        <v>11918.55939370008</v>
+        <v>11928.24846946008</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09370882881390658</v>
+        <v>0.09369801619445389</v>
       </c>
       <c r="T14">
         <v>0.6969744975870141</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.534623552331848</v>
+        <v>9.727639136275307</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08829529818272396</v>
+        <v>0.08815841268892857</v>
       </c>
       <c r="C15">
-        <v>69521.44509326429</v>
+        <v>69653.45299542049</v>
       </c>
       <c r="D15">
-        <v>78963.7580932643</v>
+        <v>79095.7659954205</v>
       </c>
       <c r="E15">
         <v>-27901.48699999999</v>
@@ -2523,37 +2523,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M15">
-        <v>755.7210063485123</v>
+        <v>740.7260081485124</v>
       </c>
       <c r="N15">
-        <v>5895.523891610672</v>
+        <v>5910.518889810672</v>
       </c>
       <c r="O15">
-        <v>1768.657167483201</v>
+        <v>1773.155666943201</v>
       </c>
       <c r="P15">
-        <v>4126.866724127471</v>
+        <v>4137.363222867471</v>
       </c>
       <c r="Q15">
-        <v>11877.86672412747</v>
+        <v>11888.36322286747</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09410869741897326</v>
+        <v>0.0940977945525418</v>
       </c>
       <c r="T15">
         <v>0.7027917598123075</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.801190971383242</v>
+        <v>8.979359202715667</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0883077979985481</v>
+        <v>0.08820034211607569</v>
       </c>
       <c r="C16">
-        <v>68684.71536063043</v>
+        <v>68786.39145946695</v>
       </c>
       <c r="D16">
-        <v>78950.92936063044</v>
+        <v>79052.60545946695</v>
       </c>
       <c r="E16">
         <v>-27077.586</v>
@@ -2605,37 +2605,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M16">
-        <v>826.541466852244</v>
+        <v>815.0068528522439</v>
       </c>
       <c r="N16">
-        <v>5824.70343110694</v>
+        <v>5836.23804510694</v>
       </c>
       <c r="O16">
-        <v>1747.411029332082</v>
+        <v>1750.871413532082</v>
       </c>
       <c r="P16">
-        <v>4077.292401774858</v>
+        <v>4085.366631574858</v>
       </c>
       <c r="Q16">
-        <v>11828.29240177486</v>
+        <v>11836.36663157486</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09451786529392525</v>
+        <v>0.09450687008174805</v>
       </c>
       <c r="T16">
         <v>0.708744307205631</v>
       </c>
       <c r="U16">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.047079505024023</v>
+        <v>8.160968063866104</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08822019781437224</v>
+        <v>0.08810577154322281</v>
       </c>
       <c r="C17">
-        <v>67950.80748920188</v>
+        <v>68059.90453420048</v>
       </c>
       <c r="D17">
-        <v>79040.92248920188</v>
+        <v>79150.01953420049</v>
       </c>
       <c r="E17">
         <v>-26253.685</v>
@@ -2687,37 +2687,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M17">
-        <v>885.5801430559757</v>
+        <v>873.2216280559757</v>
       </c>
       <c r="N17">
-        <v>5765.664754903209</v>
+        <v>5778.023269903209</v>
       </c>
       <c r="O17">
-        <v>1729.699426470963</v>
+        <v>1733.406980970962</v>
       </c>
       <c r="P17">
-        <v>4035.965328432246</v>
+        <v>4044.616288932246</v>
       </c>
       <c r="Q17">
-        <v>11786.96532843224</v>
+        <v>11795.61628893225</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09493666064828787</v>
+        <v>0.09492557091752385</v>
       </c>
       <c r="T17">
         <v>0.714836914537621</v>
       </c>
       <c r="U17">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.510607538022421</v>
+        <v>7.61690352627503</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08813259763019637</v>
+        <v>0.08801120097036993</v>
       </c>
       <c r="C18">
-        <v>67217.10501130721</v>
+        <v>67333.65798583107</v>
       </c>
       <c r="D18">
-        <v>79131.12101130722</v>
+        <v>79247.67398583108</v>
       </c>
       <c r="E18">
         <v>-25429.784</v>
@@ -2769,37 +2769,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M18">
-        <v>944.6188192597074</v>
+        <v>931.4364032597073</v>
       </c>
       <c r="N18">
-        <v>5706.626078699477</v>
+        <v>5719.808494699477</v>
       </c>
       <c r="O18">
-        <v>1711.987823609843</v>
+        <v>1715.942548409843</v>
       </c>
       <c r="P18">
-        <v>3994.638255089634</v>
+        <v>4003.865946289634</v>
       </c>
       <c r="Q18">
-        <v>11745.63825508963</v>
+        <v>11754.86594628963</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09536542732061151</v>
+        <v>0.09535424082081813</v>
       </c>
       <c r="T18">
         <v>0.7210745839489441</v>
       </c>
       <c r="U18">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.041194566896019</v>
+        <v>7.140847055882841</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08830679744602052</v>
+        <v>0.08791663039751706</v>
       </c>
       <c r="C19">
-        <v>66214.03908795089</v>
+        <v>66607.65270518119</v>
       </c>
       <c r="D19">
-        <v>78951.95608795091</v>
+        <v>79345.56970518119</v>
       </c>
       <c r="E19">
         <v>-24605.88299999999</v>
@@ -2851,45 +2851,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M19">
-        <v>1034.471392863439</v>
+        <v>989.6511784634391</v>
       </c>
       <c r="N19">
-        <v>5616.773505095745</v>
+        <v>5661.593719495745</v>
       </c>
       <c r="O19">
-        <v>1685.032051528724</v>
+        <v>1698.478115848724</v>
       </c>
       <c r="P19">
-        <v>3931.741453567022</v>
+        <v>3963.115603647022</v>
       </c>
       <c r="Q19">
-        <v>11682.74145356702</v>
+        <v>11714.11560364702</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09580452571997908</v>
+        <v>0.09579324011937251</v>
       </c>
       <c r="T19">
         <v>0.727462558647287</v>
       </c>
       <c r="U19">
-        <v>0.07385748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.05170024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.429607376138643</v>
+        <v>6.720797229066203</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08823459726184466</v>
+        <v>0.08803625982466419</v>
       </c>
       <c r="C20">
-        <v>65464.29760951144</v>
+        <v>65659.95652181588</v>
       </c>
       <c r="D20">
-        <v>79026.11560951144</v>
+        <v>79221.7745218159</v>
       </c>
       <c r="E20">
         <v>-23781.982</v>
@@ -2933,37 +2933,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M20">
-        <v>1095.322651267171</v>
+        <v>1073.077324267171</v>
       </c>
       <c r="N20">
-        <v>5555.922246692014</v>
+        <v>5578.167573692013</v>
       </c>
       <c r="O20">
-        <v>1666.776674007604</v>
+        <v>1673.450272107604</v>
       </c>
       <c r="P20">
-        <v>3889.14557268441</v>
+        <v>3904.717301584409</v>
       </c>
       <c r="Q20">
-        <v>11640.14557268441</v>
+        <v>11655.71730158441</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09625433383640439</v>
+        <v>0.09624294671789162</v>
       </c>
       <c r="T20">
         <v>0.734006337606565</v>
       </c>
       <c r="U20">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.072406966353163</v>
+        <v>6.198290419100481</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08816239707766881</v>
+        <v>0.08795358925181131</v>
       </c>
       <c r="C21">
-        <v>64714.69557803618</v>
+        <v>64921.5635827213</v>
       </c>
       <c r="D21">
-        <v>79100.41457803619</v>
+        <v>79307.28258272131</v>
       </c>
       <c r="E21">
         <v>-22958.081</v>
@@ -3015,37 +3015,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M21">
-        <v>1156.173909670903</v>
+        <v>1132.692731170903</v>
       </c>
       <c r="N21">
-        <v>5495.070988288282</v>
+        <v>5518.552166788282</v>
       </c>
       <c r="O21">
-        <v>1648.521296486485</v>
+        <v>1655.565650036485</v>
       </c>
       <c r="P21">
-        <v>3846.549691801798</v>
+        <v>3862.986516751797</v>
       </c>
       <c r="Q21">
-        <v>11597.5496918018</v>
+        <v>11613.9865167518</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09671524832607478</v>
+        <v>0.09670375718304083</v>
       </c>
       <c r="T21">
         <v>0.740711691354961</v>
       </c>
       <c r="U21">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.752806599702997</v>
+        <v>5.872064607568876</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08830019689349294</v>
+        <v>0.08787091867895844</v>
       </c>
       <c r="C22">
-        <v>63749.10998238514</v>
+        <v>64183.35542940965</v>
       </c>
       <c r="D22">
-        <v>78958.72998238515</v>
+        <v>79392.97542940966</v>
       </c>
       <c r="E22">
         <v>-22134.18</v>
@@ -3097,45 +3097,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M22">
-        <v>1241.742198074634</v>
+        <v>1192.308138074634</v>
       </c>
       <c r="N22">
-        <v>5409.502699884551</v>
+        <v>5458.93675988455</v>
       </c>
       <c r="O22">
-        <v>1622.850809965365</v>
+        <v>1637.681027965365</v>
       </c>
       <c r="P22">
-        <v>3786.651889919185</v>
+        <v>3821.255731919185</v>
       </c>
       <c r="Q22">
-        <v>11537.65188991919</v>
+        <v>11572.25573191919</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09718768567798693</v>
+        <v>0.0971760879098188</v>
       </c>
       <c r="T22">
         <v>0.747584678947067</v>
       </c>
       <c r="U22">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05275024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.356381468127747</v>
+        <v>5.578461377190433</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08823849670931708</v>
+        <v>0.08790584810610555</v>
       </c>
       <c r="C23">
-        <v>62988.58578174238</v>
+        <v>63323.22546909517</v>
       </c>
       <c r="D23">
-        <v>79022.10678174239</v>
+        <v>79356.74646909517</v>
       </c>
       <c r="E23">
         <v>-21310.27899999999</v>
@@ -3179,37 +3179,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M23">
-        <v>1303.829307978366</v>
+        <v>1265.765081778366</v>
       </c>
       <c r="N23">
-        <v>5347.415589980818</v>
+        <v>5385.479816180818</v>
       </c>
       <c r="O23">
-        <v>1604.224676994246</v>
+        <v>1615.643944854246</v>
       </c>
       <c r="P23">
-        <v>3743.190912986573</v>
+        <v>3769.835871326573</v>
       </c>
       <c r="Q23">
-        <v>11494.19091298657</v>
+        <v>11520.83587132657</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09767208346918799</v>
+        <v>0.09766037637651517</v>
       </c>
       <c r="T23">
         <v>0.754631666225049</v>
       </c>
       <c r="U23">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.101315683931187</v>
+        <v>5.254723008012169</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08817679652514121</v>
+        <v>0.08782877753325267</v>
       </c>
       <c r="C24">
-        <v>62228.16340252598</v>
+        <v>62579.30647030557</v>
       </c>
       <c r="D24">
-        <v>79085.58540252599</v>
+        <v>79436.72847030558</v>
       </c>
       <c r="E24">
         <v>-20486.378</v>
@@ -3261,37 +3261,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M24">
-        <v>1365.916417882098</v>
+        <v>1326.039609482098</v>
       </c>
       <c r="N24">
-        <v>5285.328480077087</v>
+        <v>5325.205288477087</v>
       </c>
       <c r="O24">
-        <v>1585.598544023126</v>
+        <v>1597.561586543126</v>
       </c>
       <c r="P24">
-        <v>3699.729936053961</v>
+        <v>3727.643701933961</v>
       </c>
       <c r="Q24">
-        <v>11450.72993605396</v>
+        <v>11478.64370193396</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09816890171657369</v>
+        <v>0.09815708249620377</v>
       </c>
       <c r="T24">
         <v>0.7618593454845178</v>
       </c>
       <c r="U24">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.869437698297951</v>
+        <v>5.015871962193435</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08811509634096534</v>
+        <v>0.08775170696039979</v>
       </c>
       <c r="C25">
-        <v>61467.8430903133</v>
+        <v>61835.5488585393</v>
       </c>
       <c r="D25">
-        <v>79149.1660903133</v>
+        <v>79516.87185853931</v>
       </c>
       <c r="E25">
         <v>-19662.477</v>
@@ -3343,37 +3343,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M25">
-        <v>1428.003527785829</v>
+        <v>1386.314137185829</v>
       </c>
       <c r="N25">
-        <v>5223.241370173355</v>
+        <v>5264.930760773355</v>
       </c>
       <c r="O25">
-        <v>1566.972411052006</v>
+        <v>1579.479228232007</v>
       </c>
       <c r="P25">
-        <v>3656.268959121348</v>
+        <v>3685.451532541349</v>
       </c>
       <c r="Q25">
-        <v>11407.26895912135</v>
+        <v>11436.45153254135</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09867862433402136</v>
+        <v>0.0986666900735466</v>
       </c>
       <c r="T25">
         <v>0.7692747566728039</v>
       </c>
       <c r="U25">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.657723015763258</v>
+        <v>4.79779057253285</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08805339615678949</v>
+        <v>0.08767463638754693</v>
       </c>
       <c r="C26">
-        <v>60707.62509147201</v>
+        <v>61091.95312275774</v>
       </c>
       <c r="D26">
-        <v>79212.84909147202</v>
+        <v>79597.17712275774</v>
       </c>
       <c r="E26">
         <v>-18838.576</v>
@@ -3425,37 +3425,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M26">
-        <v>1490.090637689561</v>
+        <v>1446.588664889561</v>
       </c>
       <c r="N26">
-        <v>5161.154260269624</v>
+        <v>5204.656233069623</v>
       </c>
       <c r="O26">
-        <v>1548.346278080887</v>
+        <v>1561.396869920887</v>
       </c>
       <c r="P26">
-        <v>3612.807982188737</v>
+        <v>3643.259363148736</v>
       </c>
       <c r="Q26">
-        <v>11363.80798218874</v>
+        <v>11394.25936314874</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09920176070455977</v>
+        <v>0.09918970837660901</v>
       </c>
       <c r="T26">
         <v>0.7768853102607819</v>
       </c>
       <c r="U26">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.46365122343979</v>
+        <v>4.597882632010649</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08799169597261362</v>
+        <v>0.08759756581469404</v>
       </c>
       <c r="C27">
-        <v>59947.50965316341</v>
+        <v>60348.51975389958</v>
       </c>
       <c r="D27">
-        <v>79276.63465316342</v>
+        <v>79677.64475389959</v>
       </c>
       <c r="E27">
         <v>-18014.675</v>
@@ -3507,37 +3507,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M27">
-        <v>1552.177747593293</v>
+        <v>1506.863192593293</v>
       </c>
       <c r="N27">
-        <v>5099.067150365891</v>
+        <v>5144.381705365891</v>
       </c>
       <c r="O27">
-        <v>1529.720145109767</v>
+        <v>1543.314511609767</v>
       </c>
       <c r="P27">
-        <v>3569.347005256124</v>
+        <v>3601.067193756124</v>
       </c>
       <c r="Q27">
-        <v>11320.34700525612</v>
+        <v>11352.06719375612</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09973884737831251</v>
+        <v>0.09972667383441972</v>
       </c>
       <c r="T27">
         <v>0.7846988119444391</v>
       </c>
       <c r="U27">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.285105174502197</v>
+        <v>4.413967326730222</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08818479578843777</v>
+        <v>0.08770249524184116</v>
       </c>
       <c r="C28">
-        <v>58924.3238163573</v>
+        <v>59415.10430589892</v>
       </c>
       <c r="D28">
-        <v>79077.34981635731</v>
+        <v>79568.13030589893</v>
       </c>
       <c r="E28">
         <v>-17190.77399999999</v>
@@ -3589,37 +3589,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M28">
-        <v>1644.254853897025</v>
+        <v>1588.559146297025</v>
       </c>
       <c r="N28">
-        <v>5006.99004406216</v>
+        <v>5062.68575166216</v>
       </c>
       <c r="O28">
-        <v>1502.097013218648</v>
+        <v>1518.805725498648</v>
       </c>
       <c r="P28">
-        <v>3504.893030843512</v>
+        <v>3543.880026163512</v>
       </c>
       <c r="Q28">
-        <v>11255.89303084351</v>
+        <v>11294.88002616351</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1002904499081126</v>
+        <v>0.1002781518721713</v>
       </c>
       <c r="T28">
         <v>0.7927234893492763</v>
       </c>
       <c r="U28">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.045142322186347</v>
+        <v>4.186967110077973</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08813289560426192</v>
+        <v>0.08763242466898828</v>
       </c>
       <c r="C29">
-        <v>58153.8868500043</v>
+        <v>58664.30227486466</v>
       </c>
       <c r="D29">
-        <v>79130.81385000431</v>
+        <v>79641.22927486467</v>
       </c>
       <c r="E29">
         <v>-16366.87299999999</v>
@@ -3671,37 +3671,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M29">
-        <v>1707.495425200756</v>
+        <v>1649.657575000756</v>
       </c>
       <c r="N29">
-        <v>4943.749472758428</v>
+        <v>5001.587322958429</v>
       </c>
       <c r="O29">
-        <v>1483.124841827528</v>
+        <v>1500.476196887528</v>
       </c>
       <c r="P29">
-        <v>3460.6246309309</v>
+        <v>3501.1111260709</v>
       </c>
       <c r="Q29">
-        <v>11211.6246309309</v>
+        <v>11252.1111260709</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1008571648359895</v>
+        <v>0.1008447388972585</v>
       </c>
       <c r="T29">
         <v>0.8009680209295886</v>
       </c>
       <c r="U29">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.895322236179446</v>
+        <v>4.031894254149159</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08808099542008604</v>
+        <v>0.0875623540961354</v>
       </c>
       <c r="C30">
-        <v>57383.5222264086</v>
+        <v>57913.63467888061</v>
       </c>
       <c r="D30">
-        <v>79184.35022640861</v>
+        <v>79714.46267888062</v>
       </c>
       <c r="E30">
         <v>-15542.97199999999</v>
@@ -3753,37 +3753,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M30">
-        <v>1770.735996504488</v>
+        <v>1710.756003704488</v>
       </c>
       <c r="N30">
-        <v>4880.508901454697</v>
+        <v>4940.488894254697</v>
       </c>
       <c r="O30">
-        <v>1464.152670436409</v>
+        <v>1482.146668276409</v>
       </c>
       <c r="P30">
-        <v>3416.356231018288</v>
+        <v>3458.342225978288</v>
       </c>
       <c r="Q30">
-        <v>11167.35623101829</v>
+        <v>11209.34222597829</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1014396218451962</v>
+        <v>0.1014270644508203</v>
       </c>
       <c r="T30">
         <v>0.8094415672760205</v>
       </c>
       <c r="U30">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.756203584887323</v>
+        <v>3.887898030786689</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08802909523591018</v>
+        <v>0.08749228352328252</v>
       </c>
       <c r="C31">
-        <v>56613.2300925012</v>
+        <v>57163.10188914384</v>
       </c>
       <c r="D31">
-        <v>79237.9590925012</v>
+        <v>79787.83088914385</v>
       </c>
       <c r="E31">
         <v>-14719.071</v>
@@ -3835,37 +3835,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M31">
-        <v>1833.97656780822</v>
+        <v>1771.85443240822</v>
       </c>
       <c r="N31">
-        <v>4817.268330150965</v>
+        <v>4879.390465550965</v>
       </c>
       <c r="O31">
-        <v>1445.180499045289</v>
+        <v>1463.817139665289</v>
       </c>
       <c r="P31">
-        <v>3372.087831105676</v>
+        <v>3415.573325885675</v>
       </c>
       <c r="Q31">
-        <v>11123.08783110568</v>
+        <v>11166.57332588567</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.102038486094099</v>
+        <v>0.1020257935411022</v>
       </c>
       <c r="T31">
         <v>0.818153805068831</v>
       </c>
       <c r="U31">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.626679323339485</v>
+        <v>3.753832581449217</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08797719505173432</v>
+        <v>0.08742221295042964</v>
       </c>
       <c r="C32">
-        <v>55843.01059561134</v>
+        <v>56412.70427821929</v>
       </c>
       <c r="D32">
-        <v>79291.64059561134</v>
+        <v>79861.33427821929</v>
       </c>
       <c r="E32">
         <v>-13895.16999999999</v>
@@ -3917,37 +3917,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M32">
-        <v>1897.217139111951</v>
+        <v>1832.952861111951</v>
       </c>
       <c r="N32">
-        <v>4754.027758847233</v>
+        <v>4818.292036847233</v>
       </c>
       <c r="O32">
-        <v>1426.20832765417</v>
+        <v>1445.48761105417</v>
       </c>
       <c r="P32">
-        <v>3327.819431193063</v>
+        <v>3372.804425793063</v>
       </c>
       <c r="Q32">
-        <v>11078.81943119306</v>
+        <v>11123.80442579306</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1026544607501132</v>
+        <v>0.1026416291768208</v>
       </c>
       <c r="T32">
         <v>0.8271149639414359</v>
       </c>
       <c r="U32">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.505790012561501</v>
+        <v>3.628704828734243</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08792529486755847</v>
+        <v>0.08735214237757677</v>
       </c>
       <c r="C33">
-        <v>55072.86388346771</v>
+        <v>55662.44222004604</v>
       </c>
       <c r="D33">
-        <v>79345.39488346771</v>
+        <v>79934.97322004604</v>
       </c>
       <c r="E33">
         <v>-13071.269</v>
@@ -3999,37 +3999,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M33">
-        <v>1960.457710415683</v>
+        <v>1894.051289815683</v>
       </c>
       <c r="N33">
-        <v>4690.787187543501</v>
+        <v>4757.193608143501</v>
       </c>
       <c r="O33">
-        <v>1407.23615626305</v>
+        <v>1427.15808244305</v>
       </c>
       <c r="P33">
-        <v>3283.551031280451</v>
+        <v>3330.035525700451</v>
       </c>
       <c r="Q33">
-        <v>11034.55103128045</v>
+        <v>11081.03552570045</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1032882897439829</v>
+        <v>0.103275315120821</v>
       </c>
       <c r="T33">
         <v>0.8363358665494786</v>
       </c>
       <c r="U33">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.392700012156292</v>
+        <v>3.511649834258945</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08787339468338259</v>
+        <v>0.08728207180472389</v>
       </c>
       <c r="C34">
-        <v>54302.79010419998</v>
+        <v>54912.31608994367</v>
       </c>
       <c r="D34">
-        <v>79399.22210419999</v>
+        <v>80008.74808994368</v>
       </c>
       <c r="E34">
         <v>-12247.36799999999</v>
@@ -4081,37 +4081,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M34">
-        <v>2023.698281719415</v>
+        <v>1955.149718519415</v>
       </c>
       <c r="N34">
-        <v>4627.54661623977</v>
+        <v>4696.09517943977</v>
       </c>
       <c r="O34">
-        <v>1388.263984871931</v>
+        <v>1408.828553831931</v>
       </c>
       <c r="P34">
-        <v>3239.282631367839</v>
+        <v>3287.266625607839</v>
       </c>
       <c r="Q34">
-        <v>10990.28263136784</v>
+        <v>11038.26662560784</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1039407607670841</v>
+        <v>0.1039276388867036</v>
       </c>
       <c r="T34">
         <v>0.845827972175405</v>
       </c>
       <c r="U34">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.286678136776408</v>
+        <v>3.401910776938353</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08782149449920673</v>
+        <v>0.08721200123187101</v>
       </c>
       <c r="C35">
-        <v>53532.78940633993</v>
+        <v>54162.3262646186</v>
       </c>
       <c r="D35">
-        <v>79453.12240633994</v>
+        <v>80082.65926461862</v>
       </c>
       <c r="E35">
         <v>-11423.46699999999</v>
@@ -4163,37 +4163,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M35">
-        <v>2086.938853023147</v>
+        <v>2016.248147223147</v>
       </c>
       <c r="N35">
-        <v>4564.306044936038</v>
+        <v>4634.996750736038</v>
       </c>
       <c r="O35">
-        <v>1369.291813480811</v>
+        <v>1390.499025220811</v>
       </c>
       <c r="P35">
-        <v>3195.014231455227</v>
+        <v>3244.497725515227</v>
       </c>
       <c r="Q35">
-        <v>10946.01423145523</v>
+        <v>10995.49772551523</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1046127085371435</v>
+        <v>0.1045994350038066</v>
       </c>
       <c r="T35">
         <v>0.8556034242379262</v>
       </c>
       <c r="U35">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.187081829601365</v>
+        <v>3.298822571576585</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08776959431503088</v>
+        <v>0.08714193065901814</v>
       </c>
       <c r="C36">
-        <v>52762.86193882301</v>
+        <v>53412.47312217056</v>
       </c>
       <c r="D36">
-        <v>79507.09593882303</v>
+        <v>80156.70712217057</v>
       </c>
       <c r="E36">
         <v>-10599.56599999999</v>
@@ -4245,37 +4245,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M36">
-        <v>2150.179424326879</v>
+        <v>2077.346575926878</v>
       </c>
       <c r="N36">
-        <v>4501.065473632306</v>
+        <v>4573.898322032306</v>
       </c>
       <c r="O36">
-        <v>1350.319642089692</v>
+        <v>1372.169496609692</v>
       </c>
       <c r="P36">
-        <v>3150.745831542614</v>
+        <v>3201.728825422614</v>
       </c>
       <c r="Q36">
-        <v>10901.74583154261</v>
+        <v>10952.72882542262</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1053050183608411</v>
+        <v>0.1052915885790036</v>
       </c>
       <c r="T36">
         <v>0.8656751021205238</v>
       </c>
       <c r="U36">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.093344128730736</v>
+        <v>3.20179837829492</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08771769413085501</v>
+        <v>0.08707186008616524</v>
       </c>
       <c r="C37">
-        <v>51993.00785098966</v>
+        <v>52662.75704209899</v>
       </c>
       <c r="D37">
-        <v>79561.14285098967</v>
+        <v>80230.892042099</v>
       </c>
       <c r="E37">
         <v>-9775.664999999994</v>
@@ -4327,37 +4327,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M37">
-        <v>2213.41999563061</v>
+        <v>2138.44500463061</v>
       </c>
       <c r="N37">
-        <v>4437.824902328574</v>
+        <v>4512.799893328574</v>
       </c>
       <c r="O37">
-        <v>1331.347470698572</v>
+        <v>1353.839967998572</v>
       </c>
       <c r="P37">
-        <v>3106.477431630002</v>
+        <v>3158.959925330002</v>
       </c>
       <c r="Q37">
-        <v>10857.47743163</v>
+        <v>10909.95992533</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1060186300252678</v>
+        <v>0.1060050391872836</v>
       </c>
       <c r="T37">
         <v>0.8760566777841243</v>
       </c>
       <c r="U37">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.004962867909859</v>
+        <v>3.110318424629351</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08832099394667917</v>
+        <v>0.08700178951331239</v>
       </c>
       <c r="C38">
-        <v>50545.35470015822</v>
+        <v>51913.17840530947</v>
       </c>
       <c r="D38">
-        <v>78937.39070015823</v>
+        <v>80305.21440530948</v>
       </c>
       <c r="E38">
         <v>-8951.763999999996</v>
@@ -4409,45 +4409,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M38">
-        <v>2353.777700534342</v>
+        <v>2199.543433334341</v>
       </c>
       <c r="N38">
-        <v>4297.467197424843</v>
+        <v>4451.701464624843</v>
       </c>
       <c r="O38">
-        <v>1289.240159227453</v>
+        <v>1335.510439387453</v>
       </c>
       <c r="P38">
-        <v>3008.22703819739</v>
+        <v>3116.19102523739</v>
       </c>
       <c r="Q38">
-        <v>10759.22703819739</v>
+        <v>10867.19102523739</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1067545420542079</v>
+        <v>0.1067407851270723</v>
       </c>
       <c r="T38">
         <v>0.8867626776872125</v>
       </c>
       <c r="U38">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.05555024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.825774454592401</v>
+        <v>3.023920690611869</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0882872937625033</v>
+        <v>0.0875792189404595</v>
       </c>
       <c r="C39">
-        <v>49756.0383295443</v>
+        <v>50480.8872884571</v>
       </c>
       <c r="D39">
-        <v>78971.97532954431</v>
+        <v>79696.82428845711</v>
       </c>
       <c r="E39">
         <v>-8127.862999999994</v>
@@ -4491,37 +4491,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M39">
-        <v>2419.160414438074</v>
+        <v>2336.852704538073</v>
       </c>
       <c r="N39">
-        <v>4232.084483521111</v>
+        <v>4314.392193421111</v>
       </c>
       <c r="O39">
-        <v>1269.625345056333</v>
+        <v>1294.317658026333</v>
       </c>
       <c r="P39">
-        <v>2962.459138464777</v>
+        <v>3020.074535394778</v>
       </c>
       <c r="Q39">
-        <v>10713.45913846478</v>
+        <v>10771.07453539478</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.107513816369781</v>
+        <v>0.1074998880808226</v>
       </c>
       <c r="T39">
         <v>0.8978085506030969</v>
       </c>
       <c r="U39">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.749402172035849</v>
+        <v>2.846240537558374</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08825359357832743</v>
+        <v>0.08752664836760662</v>
       </c>
       <c r="C40">
-        <v>48966.75227715731</v>
+        <v>49711.9939102288</v>
       </c>
       <c r="D40">
-        <v>79006.59027715732</v>
+        <v>79751.83191022881</v>
       </c>
       <c r="E40">
         <v>-7303.961999999996</v>
@@ -4573,37 +4573,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M40">
-        <v>2484.543128341805</v>
+        <v>2400.010885741805</v>
       </c>
       <c r="N40">
-        <v>4166.701769617379</v>
+        <v>4251.234012217379</v>
       </c>
       <c r="O40">
-        <v>1250.010530885214</v>
+        <v>1275.370203665214</v>
       </c>
       <c r="P40">
-        <v>2916.691238732165</v>
+        <v>2975.863808552165</v>
       </c>
       <c r="Q40">
-        <v>10667.69123873216</v>
+        <v>10726.86380855217</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1082975834052113</v>
+        <v>0.1082834782266293</v>
       </c>
       <c r="T40">
         <v>0.9092107420001391</v>
       </c>
       <c r="U40">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.677049483298064</v>
+        <v>2.771339470780521</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08821989339415159</v>
+        <v>0.08747407779475375</v>
       </c>
       <c r="C41">
-        <v>48177.4965828819</v>
+        <v>48943.1765181741</v>
       </c>
       <c r="D41">
-        <v>79041.23558288191</v>
+        <v>79806.91551817411</v>
       </c>
       <c r="E41">
         <v>-6480.060999999994</v>
@@ -4655,37 +4655,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M41">
-        <v>2549.925842245537</v>
+        <v>2463.169066945537</v>
       </c>
       <c r="N41">
-        <v>4101.319055713648</v>
+        <v>4188.075831013648</v>
       </c>
       <c r="O41">
-        <v>1230.395716714094</v>
+        <v>1256.422749304094</v>
       </c>
       <c r="P41">
-        <v>2870.923338999553</v>
+        <v>2931.653081709554</v>
       </c>
       <c r="Q41">
-        <v>10621.92333899955</v>
+        <v>10682.65308170955</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1091070477204917</v>
+        <v>0.1090927598526264</v>
       </c>
       <c r="T41">
         <v>0.9209867757380679</v>
       </c>
       <c r="U41">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.608407188854524</v>
+        <v>2.700279484350252</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08818619320997573</v>
+        <v>0.08742150722190087</v>
       </c>
       <c r="C42">
-        <v>47388.2712866728</v>
+        <v>48174.43526984995</v>
       </c>
       <c r="D42">
-        <v>79075.91128667281</v>
+        <v>79862.07526984996</v>
       </c>
       <c r="E42">
         <v>-5656.159999999996</v>
@@ -4737,37 +4737,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M42">
-        <v>2615.308556149268</v>
+        <v>2526.327248149268</v>
       </c>
       <c r="N42">
-        <v>4035.936341809916</v>
+        <v>4124.917649809917</v>
       </c>
       <c r="O42">
-        <v>1210.780902542975</v>
+        <v>1237.475294942975</v>
       </c>
       <c r="P42">
-        <v>2825.155439266941</v>
+        <v>2887.442354866942</v>
       </c>
       <c r="Q42">
-        <v>10576.15543926694</v>
+        <v>10638.44235486694</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1099434941796149</v>
+        <v>0.1099290175328235</v>
       </c>
       <c r="T42">
         <v>0.9331553439339276</v>
       </c>
       <c r="U42">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.543197009133161</v>
+        <v>2.632772497241496</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08892739302579986</v>
+        <v>0.08736893664904799</v>
       </c>
       <c r="C43">
-        <v>45808.67197490996</v>
+        <v>47405.77032324919</v>
       </c>
       <c r="D43">
-        <v>78320.21297490997</v>
+        <v>79917.3113232492</v>
       </c>
       <c r="E43">
         <v>-4832.258999999991</v>
@@ -4819,45 +4819,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M43">
-        <v>2771.897110753001</v>
+        <v>2589.485429353001</v>
       </c>
       <c r="N43">
-        <v>3879.347787206184</v>
+        <v>4061.759468606184</v>
       </c>
       <c r="O43">
-        <v>1163.804336161855</v>
+        <v>1218.527840581855</v>
       </c>
       <c r="P43">
-        <v>2715.543451044329</v>
+        <v>2843.231628024329</v>
       </c>
       <c r="Q43">
-        <v>10466.54345104433</v>
+        <v>10594.23162802433</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1108082947559964</v>
+        <v>0.1107936229309933</v>
       </c>
       <c r="T43">
         <v>0.9457364059669351</v>
       </c>
       <c r="U43">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.05744024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.399528060459769</v>
+        <v>2.568558533894142</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08891259284162399</v>
+        <v>0.08731636607619513</v>
       </c>
       <c r="C44">
-        <v>44999.71930934658</v>
+        <v>46637.1818368021</v>
       </c>
       <c r="D44">
-        <v>78335.16130934659</v>
+        <v>79972.62383680211</v>
       </c>
       <c r="E44">
         <v>-4008.357999999993</v>
@@ -4901,45 +4901,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M44">
-        <v>2839.504357356732</v>
+        <v>2652.643610556732</v>
       </c>
       <c r="N44">
-        <v>3811.740540602452</v>
+        <v>3998.601287402453</v>
       </c>
       <c r="O44">
-        <v>1143.522162180736</v>
+        <v>1199.580386220736</v>
       </c>
       <c r="P44">
-        <v>2668.218378421717</v>
+        <v>2799.020901181717</v>
       </c>
       <c r="Q44">
-        <v>10419.21837842172</v>
+        <v>10550.02090118172</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1117029160419084</v>
+        <v>0.1116880423084103</v>
       </c>
       <c r="T44">
         <v>0.9587512977252186</v>
       </c>
       <c r="U44">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05744024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.342396439972632</v>
+        <v>2.507402378325234</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08889779265744814</v>
+        <v>0.08831729550334223</v>
       </c>
       <c r="C45">
-        <v>44190.7723510036</v>
+        <v>44773.12369995275</v>
       </c>
       <c r="D45">
-        <v>78350.11535100361</v>
+        <v>78932.46669995275</v>
       </c>
       <c r="E45">
         <v>-3184.456999999995</v>
@@ -4983,37 +4983,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M45">
-        <v>2907.111603960464</v>
+        <v>2839.798892260464</v>
       </c>
       <c r="N45">
-        <v>3744.133293998721</v>
+        <v>3811.446005698721</v>
       </c>
       <c r="O45">
-        <v>1123.239988199616</v>
+        <v>1143.433801709616</v>
       </c>
       <c r="P45">
-        <v>2620.893305799105</v>
+        <v>2668.012203989105</v>
       </c>
       <c r="Q45">
-        <v>10371.89330579911</v>
+        <v>10419.0122039891</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1126289275483787</v>
+        <v>0.1126138448218771</v>
       </c>
       <c r="T45">
         <v>0.972222852352214</v>
       </c>
       <c r="U45">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.287922104159315</v>
+        <v>2.342153494068318</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09033059247327228</v>
+        <v>0.08828922493048937</v>
       </c>
       <c r="C46">
-        <v>41945.17435859182</v>
+        <v>43978.02449414352</v>
       </c>
       <c r="D46">
-        <v>76928.41835859182</v>
+        <v>78961.26849414353</v>
       </c>
       <c r="E46">
         <v>-2360.555999999997</v>
@@ -5065,45 +5065,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M46">
-        <v>3145.101577364195</v>
+        <v>2905.840726964195</v>
       </c>
       <c r="N46">
-        <v>3506.143320594989</v>
+        <v>3745.404170994989</v>
       </c>
       <c r="O46">
-        <v>1051.842996178497</v>
+        <v>1123.621251298497</v>
       </c>
       <c r="P46">
-        <v>2454.300324416492</v>
+        <v>2621.782919696493</v>
       </c>
       <c r="Q46">
-        <v>10205.30032441649</v>
+        <v>10372.78291969649</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1135880108943657</v>
+        <v>0.1135727117108248</v>
       </c>
       <c r="T46">
         <v>0.9861755339301734</v>
       </c>
       <c r="U46">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.06073024175551697</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.114794938843715</v>
+        <v>2.288922732839493</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09034869228909642</v>
+        <v>0.08914315435763646</v>
       </c>
       <c r="C47">
-        <v>41103.64372410348</v>
+        <v>42287.25254114823</v>
       </c>
       <c r="D47">
-        <v>76910.78872410349</v>
+        <v>78094.39754114824</v>
       </c>
       <c r="E47">
         <v>-1536.654999999992</v>
@@ -5147,37 +5147,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M47">
-        <v>3216.581158667927</v>
+        <v>3075.694087667927</v>
       </c>
       <c r="N47">
-        <v>3434.663739291257</v>
+        <v>3575.550810291257</v>
       </c>
       <c r="O47">
-        <v>1030.399121787377</v>
+        <v>1072.665243087377</v>
       </c>
       <c r="P47">
-        <v>2404.26461750388</v>
+        <v>2502.88556720388</v>
       </c>
       <c r="Q47">
-        <v>10155.26461750388</v>
+        <v>10253.88556720388</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1145819699983887</v>
+        <v>0.1145664464866433</v>
       </c>
       <c r="T47">
         <v>1.000635585747331</v>
       </c>
       <c r="U47">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.067799495758299</v>
+        <v>2.162518348176276</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09036679210492056</v>
+        <v>0.08913468378478361</v>
       </c>
       <c r="C48">
-        <v>40262.12116810703</v>
+        <v>41471.85701106626</v>
       </c>
       <c r="D48">
-        <v>76893.16716810704</v>
+        <v>78102.90301106627</v>
       </c>
       <c r="E48">
         <v>-712.7539999999935</v>
@@ -5229,37 +5229,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M48">
-        <v>3288.060739971659</v>
+        <v>3144.042845171659</v>
       </c>
       <c r="N48">
-        <v>3363.184157987526</v>
+        <v>3507.202052787526</v>
       </c>
       <c r="O48">
-        <v>1008.955247396258</v>
+        <v>1052.160615836258</v>
       </c>
       <c r="P48">
-        <v>2354.228910591268</v>
+        <v>2455.041436951268</v>
       </c>
       <c r="Q48">
-        <v>10105.22891059127</v>
+        <v>10206.04143695127</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1156127424025606</v>
+        <v>0.1155969862541589</v>
       </c>
       <c r="T48">
         <v>1.015631195039199</v>
       </c>
       <c r="U48">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.022847332807031</v>
+        <v>2.115507079737661</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09344459192074471</v>
+        <v>0.08912621321193073</v>
       </c>
       <c r="C49">
-        <v>36554.77322039143</v>
+        <v>40656.46333389312</v>
       </c>
       <c r="D49">
-        <v>74009.72022039143</v>
+        <v>78111.41033389313</v>
       </c>
       <c r="E49">
         <v>111.1470000000045</v>
@@ -5311,45 +5311,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M49">
-        <v>3719.66744837539</v>
+        <v>3212.39160267539</v>
       </c>
       <c r="N49">
-        <v>2931.577449583794</v>
+        <v>3438.853295283794</v>
       </c>
       <c r="O49">
-        <v>879.4732348751382</v>
+        <v>1031.655988585138</v>
       </c>
       <c r="P49">
-        <v>2052.104214708656</v>
+        <v>2407.197306698656</v>
       </c>
       <c r="Q49">
-        <v>9803.104214708655</v>
+        <v>10158.19730669866</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1166824118785882</v>
+        <v>0.1166664143147882</v>
       </c>
       <c r="T49">
         <v>1.031192676379816</v>
       </c>
       <c r="U49">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.788128909444363</v>
+        <v>2.070496290807073</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09352779173656883</v>
+        <v>0.08911774263907783</v>
       </c>
       <c r="C50">
-        <v>35655.92509919919</v>
+        <v>39841.07151023437</v>
       </c>
       <c r="D50">
-        <v>73934.7730991992</v>
+        <v>78119.91951023438</v>
       </c>
       <c r="E50">
         <v>935.0480000000025</v>
@@ -5393,45 +5393,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M50">
-        <v>3798.809308979122</v>
+        <v>3280.740360179122</v>
       </c>
       <c r="N50">
-        <v>2852.435588980063</v>
+        <v>3370.504537780062</v>
       </c>
       <c r="O50">
-        <v>855.7306766940188</v>
+        <v>1011.151361334019</v>
       </c>
       <c r="P50">
-        <v>1996.704912286044</v>
+        <v>2359.353176446044</v>
       </c>
       <c r="Q50">
-        <v>9747.704912286044</v>
+        <v>10110.35317644604</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.117793222488309</v>
+        <v>0.1177769742239032</v>
       </c>
       <c r="T50">
         <v>1.047352676233534</v>
       </c>
       <c r="U50">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.750876223830939</v>
+        <v>2.027360951415259</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09522309155239297</v>
+        <v>0.09178467206622495</v>
       </c>
       <c r="C51">
-        <v>33337.27288098242</v>
+        <v>36426.64550219761</v>
       </c>
       <c r="D51">
-        <v>72440.02188098243</v>
+        <v>75529.39450219763</v>
       </c>
       <c r="E51">
         <v>1758.949000000008</v>
@@ -5475,45 +5475,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M51">
-        <v>4067.695569882855</v>
+        <v>3663.984079882854</v>
       </c>
       <c r="N51">
-        <v>2583.54932807633</v>
+        <v>2987.26081807633</v>
       </c>
       <c r="O51">
-        <v>775.0647984228989</v>
+        <v>896.1782454228991</v>
       </c>
       <c r="P51">
-        <v>1808.484529653431</v>
+        <v>2091.082572653431</v>
       </c>
       <c r="Q51">
-        <v>9559.484529653431</v>
+        <v>9842.082572653431</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1189475942984111</v>
+        <v>0.1189310855020032</v>
       </c>
       <c r="T51">
         <v>1.064146401571711</v>
       </c>
       <c r="U51">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.635138319397568</v>
+        <v>1.815303984118796</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09533919136821711</v>
+        <v>0.09183080149337208</v>
       </c>
       <c r="C52">
-        <v>32413.21451867417</v>
+        <v>35559.44733201037</v>
       </c>
       <c r="D52">
-        <v>72339.86451867418</v>
+        <v>75486.09733201038</v>
       </c>
       <c r="E52">
         <v>2582.850000000006</v>
@@ -5557,45 +5557,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M52">
-        <v>4150.709765186586</v>
+        <v>3738.759265186586</v>
       </c>
       <c r="N52">
-        <v>2500.535132772598</v>
+        <v>2912.485632772599</v>
       </c>
       <c r="O52">
-        <v>750.1605398317795</v>
+        <v>873.7456898317796</v>
       </c>
       <c r="P52">
-        <v>1750.374592940819</v>
+        <v>2038.739942940819</v>
       </c>
       <c r="Q52">
-        <v>9501.37459294082</v>
+        <v>9789.73994294082</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1201481409809173</v>
+        <v>0.1201313612312272</v>
       </c>
       <c r="T52">
         <v>1.081611875923416</v>
       </c>
       <c r="U52">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.602435553009617</v>
+        <v>1.77899790443642</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09545529118404125</v>
+        <v>0.0932692309205192</v>
       </c>
       <c r="C53">
-        <v>31489.43273404548</v>
+        <v>33409.9039129025</v>
       </c>
       <c r="D53">
-        <v>72239.98373404548</v>
+        <v>74160.45491290251</v>
       </c>
       <c r="E53">
         <v>3406.751000000004</v>
@@ -5639,37 +5639,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M53">
-        <v>4233.723960490318</v>
+        <v>3977.408359390317</v>
       </c>
       <c r="N53">
-        <v>2417.520937468867</v>
+        <v>2673.836538568867</v>
       </c>
       <c r="O53">
-        <v>725.25628124066</v>
+        <v>802.1509615706601</v>
       </c>
       <c r="P53">
-        <v>1692.264656228207</v>
+        <v>1871.685576998207</v>
       </c>
       <c r="Q53">
-        <v>9443.264656228206</v>
+        <v>9622.685576998207</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1213976895688318</v>
+        <v>0.1213806278065419</v>
       </c>
       <c r="T53">
         <v>1.099790226779272</v>
       </c>
       <c r="U53">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.571015248048644</v>
+        <v>1.672255975994059</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09557139099986539</v>
+        <v>0.09334266034766632</v>
       </c>
       <c r="C54">
-        <v>30565.92638305052</v>
+        <v>32519.57903544617</v>
       </c>
       <c r="D54">
-        <v>72140.37838305053</v>
+        <v>74094.03103544618</v>
       </c>
       <c r="E54">
         <v>4230.652000000009</v>
@@ -5721,37 +5721,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M54">
-        <v>4316.73815579405</v>
+        <v>4055.39675859405</v>
       </c>
       <c r="N54">
-        <v>2334.506742165135</v>
+        <v>2595.848139365135</v>
       </c>
       <c r="O54">
-        <v>700.3520226495403</v>
+        <v>778.7544418095405</v>
       </c>
       <c r="P54">
-        <v>1634.154719515594</v>
+        <v>1817.093697555595</v>
       </c>
       <c r="Q54">
-        <v>9385.154719515594</v>
+        <v>9568.093697555594</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1226993026812428</v>
+        <v>0.1226819471558281</v>
       </c>
       <c r="T54">
         <v>1.118726008920788</v>
       </c>
       <c r="U54">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.540803416355401</v>
+        <v>1.640097207224942</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09568749081568953</v>
+        <v>0.09341608977481344</v>
       </c>
       <c r="C55">
-        <v>29642.6943279445</v>
+        <v>31629.37304030224</v>
       </c>
       <c r="D55">
-        <v>72041.04732794451</v>
+        <v>74027.72604030225</v>
       </c>
       <c r="E55">
         <v>5054.553000000007</v>
@@ -5803,37 +5803,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M55">
-        <v>4399.752351097782</v>
+        <v>4133.385157797781</v>
       </c>
       <c r="N55">
-        <v>2251.492546861403</v>
+        <v>2517.859740161403</v>
       </c>
       <c r="O55">
-        <v>675.4477640584208</v>
+        <v>755.357922048421</v>
       </c>
       <c r="P55">
-        <v>1576.044782802982</v>
+        <v>1762.501818112982</v>
       </c>
       <c r="Q55">
-        <v>9327.044782802983</v>
+        <v>9513.501818112982</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1240563035856714</v>
+        <v>0.1240386417965733</v>
       </c>
       <c r="T55">
         <v>1.138467569025773</v>
       </c>
       <c r="U55">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.511731653782658</v>
+        <v>1.609151976899943</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1019649906315137</v>
+        <v>0.09348951920196058</v>
       </c>
       <c r="C56">
-        <v>23827.00893749669</v>
+        <v>30739.28560860113</v>
       </c>
       <c r="D56">
-        <v>67049.26293749671</v>
+        <v>73961.53960860115</v>
       </c>
       <c r="E56">
         <v>5878.454000000012</v>
@@ -5885,45 +5885,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M56">
-        <v>5207.964206601514</v>
+        <v>4211.373557001513</v>
       </c>
       <c r="N56">
-        <v>1443.280691357671</v>
+        <v>2439.871340957671</v>
       </c>
       <c r="O56">
-        <v>432.9842074073011</v>
+        <v>731.9614022873013</v>
       </c>
       <c r="P56">
-        <v>1010.296483950369</v>
+        <v>1707.90993867037</v>
       </c>
       <c r="Q56">
-        <v>8761.296483950369</v>
+        <v>9458.909938670369</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1254723045294228</v>
+        <v>0.1254543231608291</v>
       </c>
       <c r="T56">
         <v>1.159067457830975</v>
       </c>
       <c r="U56">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.277129533557123</v>
+        <v>1.579352866216611</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1021951904473378</v>
+        <v>0.09356294862910769</v>
       </c>
       <c r="C57">
-        <v>22833.17171651375</v>
+        <v>29849.31642261271</v>
       </c>
       <c r="D57">
-        <v>66879.32671651377</v>
+        <v>73895.47142261273</v>
       </c>
       <c r="E57">
         <v>6702.35500000001</v>
@@ -5967,45 +5967,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M57">
-        <v>5304.407988205246</v>
+        <v>4289.361956205244</v>
       </c>
       <c r="N57">
-        <v>1346.836909753939</v>
+        <v>2361.88294175394</v>
       </c>
       <c r="O57">
-        <v>404.0510729261817</v>
+        <v>708.564882526182</v>
       </c>
       <c r="P57">
-        <v>942.7858368277573</v>
+        <v>1653.318059227758</v>
       </c>
       <c r="Q57">
-        <v>8693.785836827758</v>
+        <v>9404.318059227759</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1269512388484522</v>
+        <v>0.1269329236968297</v>
       </c>
       <c r="T57">
         <v>1.180582897249742</v>
       </c>
       <c r="U57">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.253908996583357</v>
+        <v>1.550637359558127</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1164591426131497</v>
+        <v>0.09363637805625481</v>
       </c>
       <c r="C58">
-        <v>12931.73176521002</v>
+        <v>28959.46516574097</v>
       </c>
       <c r="D58">
-        <v>57801.78776521003</v>
+        <v>73829.52116574098</v>
       </c>
       <c r="E58">
         <v>7526.256000000008</v>
@@ -6049,45 +6049,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M58">
-        <v>6909.579281008976</v>
+        <v>4367.350355408977</v>
       </c>
       <c r="N58">
-        <v>-258.3343830497915</v>
+        <v>2283.894542550208</v>
       </c>
       <c r="O58">
-        <v>-77.50031491493746</v>
+        <v>685.1683627650624</v>
       </c>
       <c r="P58">
-        <v>-180.8340681348541</v>
+        <v>1598.726179785146</v>
       </c>
       <c r="Q58">
-        <v>7570.165931865145</v>
+        <v>9349.726179785146</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1291217191195646</v>
+        <v>0.128478733348103</v>
       </c>
       <c r="T58">
-        <v>1.212158901796987</v>
+        <v>1.203076311187543</v>
       </c>
       <c r="U58">
-        <v>0.1497574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V58">
-        <v>0.2887836419899041</v>
+        <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.1065099753581095</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.9626121399663471</v>
+        <v>1.522947406708875</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1174987174953714</v>
+        <v>0.09937560748340193</v>
       </c>
       <c r="C59">
-        <v>11541.64572103572</v>
+        <v>23321.32791694087</v>
       </c>
       <c r="D59">
-        <v>57235.60272103573</v>
+        <v>69015.28491694089</v>
       </c>
       <c r="E59">
         <v>8350.157000000014</v>
@@ -6131,45 +6131,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M59">
-        <v>7032.964625312708</v>
+        <v>5112.204224012708</v>
       </c>
       <c r="N59">
-        <v>-381.7197273535239</v>
+        <v>1539.040673946476</v>
       </c>
       <c r="O59">
-        <v>-114.5159182060572</v>
+        <v>461.7122021839428</v>
       </c>
       <c r="P59">
-        <v>-267.2038091474668</v>
+        <v>1077.328471762533</v>
       </c>
       <c r="Q59">
-        <v>7483.796190852533</v>
+        <v>8828.328471762534</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.131059433517694</v>
+        <v>0.1300964411226913</v>
       </c>
       <c r="T59">
-        <v>1.240348643699243</v>
+        <v>1.226615930424777</v>
       </c>
       <c r="U59">
-        <v>0.1497574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V59">
-        <v>0.2837172623058707</v>
+        <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.1072687036539702</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.9457242076862357</v>
+        <v>1.301052267575187</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1185382923775931</v>
+        <v>0.09954843691054907</v>
       </c>
       <c r="C60">
-        <v>10162.5439714606</v>
+        <v>22362.17146639504</v>
       </c>
       <c r="D60">
-        <v>56680.4019714606</v>
+        <v>68880.02946639505</v>
       </c>
       <c r="E60">
         <v>9174.058000000005</v>
@@ -6213,45 +6213,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M60">
-        <v>7156.349969616439</v>
+        <v>5201.89201741644</v>
       </c>
       <c r="N60">
-        <v>-505.1050716572545</v>
+        <v>1449.352880542745</v>
       </c>
       <c r="O60">
-        <v>-151.5315214971763</v>
+        <v>434.8058641628235</v>
       </c>
       <c r="P60">
-        <v>-353.5735501600782</v>
+        <v>1014.547016379922</v>
       </c>
       <c r="Q60">
-        <v>7397.426449839922</v>
+        <v>8765.547016379922</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.13308942003002</v>
+        <v>0.1317911826008314</v>
       </c>
       <c r="T60">
-        <v>1.26988075426351</v>
+        <v>1.251276483911403</v>
       </c>
       <c r="U60">
-        <v>0.1497574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V60">
-        <v>0.2788255853695626</v>
+        <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.108001268905146</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.9294186178985421</v>
+        <v>1.278620331927339</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1195778672598148</v>
+        <v>0.09972126633769618</v>
       </c>
       <c r="C61">
-        <v>8794.109935563662</v>
+        <v>21403.54412341092</v>
       </c>
       <c r="D61">
-        <v>56135.86893556366</v>
+        <v>68745.30312341092</v>
       </c>
       <c r="E61">
         <v>9997.959000000003</v>
@@ -6295,45 +6295,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M61">
-        <v>7279.73531392017</v>
+        <v>5291.579810820171</v>
       </c>
       <c r="N61">
-        <v>-628.490415960986</v>
+        <v>1359.665087139014</v>
       </c>
       <c r="O61">
-        <v>-188.5471247882958</v>
+        <v>407.8995261417041</v>
       </c>
       <c r="P61">
-        <v>-439.9432911726902</v>
+        <v>951.7655609973096</v>
       </c>
       <c r="Q61">
-        <v>7311.05670882731</v>
+        <v>8702.76556099731</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1352184302746547</v>
+        <v>0.1335685943949784</v>
       </c>
       <c r="T61">
-        <v>1.30085345558701</v>
+        <v>1.277139991226645</v>
       </c>
       <c r="U61">
-        <v>0.1497574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V61">
-        <v>0.2740997279904175</v>
+        <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.108709001435943</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.9136657599680583</v>
+        <v>1.256948800877723</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1206174421420364</v>
+        <v>0.1125964349327888</v>
       </c>
       <c r="C62">
-        <v>7436.039082329844</v>
+        <v>11836.61020111425</v>
       </c>
       <c r="D62">
-        <v>55601.69908232985</v>
+        <v>60002.27020111425</v>
       </c>
       <c r="E62">
         <v>10821.86000000001</v>
@@ -6377,37 +6377,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M62">
-        <v>7403.120658223903</v>
+        <v>6795.081720223904</v>
       </c>
       <c r="N62">
-        <v>-751.8757602647183</v>
+        <v>-143.8368222647196</v>
       </c>
       <c r="O62">
-        <v>-225.5627280794155</v>
+        <v>-43.15104667941586</v>
       </c>
       <c r="P62">
-        <v>-526.3130321853029</v>
+        <v>-100.6857755853037</v>
       </c>
       <c r="Q62">
-        <v>7224.686967814697</v>
+        <v>7650.314224414697</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.137453891031521</v>
+        <v>0.135851373008402</v>
       </c>
       <c r="T62">
-        <v>1.333374791976685</v>
+        <v>1.310357201533102</v>
       </c>
       <c r="U62">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V62">
-        <v>0.2695313991905772</v>
+        <v>0.2936496647934362</v>
       </c>
       <c r="W62">
-        <v>0.10939314288238</v>
+        <v>0.09709314288238005</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.898437997301924</v>
+        <v>0.9788322159781208</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1216570170242581</v>
+        <v>0.1135130098150105</v>
       </c>
       <c r="C63">
-        <v>6088.038362739913</v>
+        <v>10474.33103256379</v>
       </c>
       <c r="D63">
-        <v>55077.59936273991</v>
+        <v>59463.8920325638</v>
       </c>
       <c r="E63">
         <v>11645.76100000001</v>
@@ -6459,37 +6459,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M63">
-        <v>7526.506002527634</v>
+        <v>6908.333082227636</v>
       </c>
       <c r="N63">
-        <v>-875.2611045684498</v>
+        <v>-257.0881842684512</v>
       </c>
       <c r="O63">
-        <v>-262.578331370535</v>
+        <v>-77.12645528053535</v>
       </c>
       <c r="P63">
-        <v>-612.6827731979149</v>
+        <v>-179.9617289879158</v>
       </c>
       <c r="Q63">
-        <v>7138.317226802085</v>
+        <v>7571.038271012084</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1398039908015601</v>
+        <v>0.13816038257272</v>
       </c>
       <c r="T63">
-        <v>1.367563889206857</v>
+        <v>1.343956104136515</v>
       </c>
       <c r="U63">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V63">
-        <v>0.2651128516628628</v>
+        <v>0.2888357358623962</v>
       </c>
       <c r="W63">
-        <v>0.1100548534617208</v>
+        <v>0.09775485346172082</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8837095055428761</v>
+        <v>0.9627857862079876</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1226965919064798</v>
+        <v>0.1144295846972322</v>
       </c>
       <c r="C64">
-        <v>4749.825673679181</v>
+        <v>9121.627283510039</v>
       </c>
       <c r="D64">
-        <v>54563.28767367918</v>
+        <v>58935.08928351004</v>
       </c>
       <c r="E64">
         <v>12469.662</v>
@@ -6541,37 +6541,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M64">
-        <v>7649.891346831366</v>
+        <v>7021.584444231367</v>
       </c>
       <c r="N64">
-        <v>-998.6464488721813</v>
+        <v>-370.3395462721828</v>
       </c>
       <c r="O64">
-        <v>-299.5939346616544</v>
+        <v>-111.1018638816548</v>
       </c>
       <c r="P64">
-        <v>-699.0525142105269</v>
+        <v>-259.237682390528</v>
       </c>
       <c r="Q64">
-        <v>7051.947485789473</v>
+        <v>7491.762317609472</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.14227778003318</v>
+        <v>0.1405909189562127</v>
       </c>
       <c r="T64">
-        <v>1.403552412607037</v>
+        <v>1.379323370034845</v>
       </c>
       <c r="U64">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V64">
-        <v>0.260836837926365</v>
+        <v>0.2841770949613899</v>
       </c>
       <c r="W64">
-        <v>0.1106952185385022</v>
+        <v>0.09839521853850221</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8694561264212168</v>
+        <v>0.947256983204633</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1237361667887015</v>
+        <v>0.1153461595794538</v>
       </c>
       <c r="C65">
-        <v>3421.129351604191</v>
+        <v>7778.245747716588</v>
       </c>
       <c r="D65">
-        <v>54058.4923516042</v>
+        <v>58415.60874771659</v>
       </c>
       <c r="E65">
         <v>13293.56300000001</v>
@@ -6623,37 +6623,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M65">
-        <v>7773.276691135098</v>
+        <v>7134.8358062351</v>
       </c>
       <c r="N65">
-        <v>-1122.031793175914</v>
+        <v>-483.5909082759154</v>
       </c>
       <c r="O65">
-        <v>-336.6095379527741</v>
+        <v>-145.0772724827746</v>
       </c>
       <c r="P65">
-        <v>-785.4222552231396</v>
+        <v>-338.5136357931408</v>
       </c>
       <c r="Q65">
-        <v>6965.577744776861</v>
+        <v>7412.486364206859</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1448852876016444</v>
+        <v>0.143152835684759</v>
       </c>
       <c r="T65">
-        <v>1.441486261596417</v>
+        <v>1.416602380035786</v>
       </c>
       <c r="U65">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V65">
-        <v>0.2566965706576925</v>
+        <v>0.2796663474223202</v>
       </c>
       <c r="W65">
-        <v>0.111315254565227</v>
+        <v>0.09901525456522706</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8556552355256419</v>
+        <v>0.9322211580744006</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1247757416709231</v>
+        <v>0.1162627344616755</v>
       </c>
       <c r="C66">
-        <v>2101.687694058171</v>
+        <v>6443.942068440752</v>
       </c>
       <c r="D66">
-        <v>53562.95169405817</v>
+        <v>57905.20606844076</v>
       </c>
       <c r="E66">
         <v>14117.46400000001</v>
@@ -6705,37 +6705,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M66">
-        <v>7896.66203543883</v>
+        <v>7248.087168238831</v>
       </c>
       <c r="N66">
-        <v>-1245.417137479645</v>
+        <v>-596.8422702796461</v>
       </c>
       <c r="O66">
-        <v>-373.6251412438936</v>
+        <v>-179.0526810838938</v>
       </c>
       <c r="P66">
-        <v>-871.7919962357516</v>
+        <v>-417.7895891957522</v>
       </c>
       <c r="Q66">
-        <v>6879.208003764248</v>
+        <v>7333.210410804248</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.14763765670169</v>
+        <v>0.1458570811204467</v>
       </c>
       <c r="T66">
-        <v>1.481527546640762</v>
+        <v>1.455952446147891</v>
       </c>
       <c r="U66">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V66">
-        <v>0.2526856867411661</v>
+        <v>0.2752965607438465</v>
       </c>
       <c r="W66">
-        <v>0.1119159144661167</v>
+        <v>0.09961591446611674</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8422856224705537</v>
+        <v>0.9176552024794882</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1258153165531448</v>
+        <v>0.1171793093438972</v>
       </c>
       <c r="C67">
-        <v>791.2485072640338</v>
+        <v>5118.480355172913</v>
       </c>
       <c r="D67">
-        <v>53076.41350726403</v>
+        <v>57403.64535517291</v>
       </c>
       <c r="E67">
         <v>14941.36500000001</v>
@@ -6787,37 +6787,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M67">
-        <v>8020.047379742561</v>
+        <v>7361.338530242562</v>
       </c>
       <c r="N67">
-        <v>-1368.802481783377</v>
+        <v>-710.0936322833777</v>
       </c>
       <c r="O67">
-        <v>-410.640744535013</v>
+        <v>-213.0280896850133</v>
       </c>
       <c r="P67">
-        <v>-958.1617372483636</v>
+        <v>-497.0655425983644</v>
       </c>
       <c r="Q67">
-        <v>6792.838262751637</v>
+        <v>7253.934457401636</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.150547304036024</v>
+        <v>0.1487158548667452</v>
       </c>
       <c r="T67">
-        <v>1.523856905116212</v>
+        <v>1.497551087466403</v>
       </c>
       <c r="U67">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V67">
-        <v>0.2487982146374559</v>
+        <v>0.271061229040095</v>
       </c>
       <c r="W67">
-        <v>0.1124980925239021</v>
+        <v>0.1001980925239021</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8293273821248529</v>
+        <v>0.90353743013365</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1268548914353665</v>
+        <v>0.1180958842261189</v>
       </c>
       <c r="C68">
-        <v>-510.4313218477182</v>
+        <v>3801.632820122941</v>
       </c>
       <c r="D68">
-        <v>52598.63467815229</v>
+        <v>56910.69882012295</v>
       </c>
       <c r="E68">
         <v>15765.26600000001</v>
@@ -6869,37 +6869,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M68">
-        <v>8143.432724046294</v>
+        <v>7474.589892246295</v>
       </c>
       <c r="N68">
-        <v>-1492.187826087109</v>
+        <v>-823.3449942871102</v>
       </c>
       <c r="O68">
-        <v>-447.6563478261327</v>
+        <v>-247.0034982861331</v>
       </c>
       <c r="P68">
-        <v>-1044.531478260976</v>
+        <v>-576.3414960009771</v>
       </c>
       <c r="Q68">
-        <v>6706.468521739023</v>
+        <v>7174.658503999023</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1536281070959071</v>
+        <v>0.1517427917745906</v>
       </c>
       <c r="T68">
-        <v>1.568676225854924</v>
+        <v>1.541596707686003</v>
       </c>
       <c r="U68">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V68">
-        <v>0.2450285447187065</v>
+        <v>0.2669542407213056</v>
       </c>
       <c r="W68">
-        <v>0.1130626288223607</v>
+        <v>0.1007626288223607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8167618157290217</v>
+        <v>0.8898474690710187</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1278944663175881</v>
+        <v>0.1190124591083405</v>
       </c>
       <c r="C69">
-        <v>-1803.586230702473</v>
+        <v>2493.179433277022</v>
       </c>
       <c r="D69">
-        <v>52129.38076929753</v>
+        <v>56426.14643327703</v>
       </c>
       <c r="E69">
         <v>16589.16700000001</v>
@@ -6951,37 +6951,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M69">
-        <v>8266.818068350025</v>
+        <v>7587.841254250026</v>
       </c>
       <c r="N69">
-        <v>-1615.57317039084</v>
+        <v>-936.5963562908419</v>
       </c>
       <c r="O69">
-        <v>-484.6719511172521</v>
+        <v>-280.9789068872525</v>
       </c>
       <c r="P69">
-        <v>-1130.901219273588</v>
+        <v>-655.6174494035893</v>
       </c>
       <c r="Q69">
-        <v>6620.098780726412</v>
+        <v>7095.382550596411</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1568956254927528</v>
+        <v>0.1549531794041237</v>
       </c>
       <c r="T69">
-        <v>1.616211869062649</v>
+        <v>1.588311759434064</v>
       </c>
       <c r="U69">
-        <v>0.1497574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V69">
-        <v>0.2413714022602184</v>
+        <v>0.2629698490687488</v>
       </c>
       <c r="W69">
-        <v>0.1136103132910145</v>
+        <v>0.1013103132910145</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8045713408673946</v>
+        <v>0.8765661635624962</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1524375992837747</v>
+        <v>0.1199290339905622</v>
       </c>
       <c r="C70">
-        <v>-11696.93769112055</v>
+        <v>1192.907594927194</v>
       </c>
       <c r="D70">
-        <v>43059.93030887945</v>
+        <v>55949.7755949272</v>
       </c>
       <c r="E70">
         <v>17413.06800000001</v>
@@ -7033,45 +7033,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M70">
-        <v>10222.22967625376</v>
+        <v>7701.092616253759</v>
       </c>
       <c r="N70">
-        <v>-3570.984778294574</v>
+        <v>-1049.847718294574</v>
       </c>
       <c r="O70">
-        <v>-1071.295433488372</v>
+        <v>-314.9543154883723</v>
       </c>
       <c r="P70">
-        <v>-2499.689344806202</v>
+        <v>-734.8934028062022</v>
       </c>
       <c r="Q70">
-        <v>5251.310655193798</v>
+        <v>7016.106597193798</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1643284828017916</v>
+        <v>0.1583642162605025</v>
       </c>
       <c r="T70">
-        <v>1.724344589416263</v>
+        <v>1.637946501916378</v>
       </c>
       <c r="U70">
-        <v>0.1824574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V70">
-        <v>0.1951994361878806</v>
+        <v>0.2591026454059731</v>
       </c>
       <c r="W70">
-        <v>0.1468418893929432</v>
+        <v>0.1018418893929433</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.6506647872929354</v>
+        <v>0.863675484686577</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.19111352649272</v>
+        <v>0.1208456088727839</v>
       </c>
       <c r="C71">
-        <v>-21786.09440143962</v>
+        <v>-99.38817535003182</v>
       </c>
       <c r="D71">
-        <v>33794.67459856039</v>
+        <v>55481.38082464998</v>
       </c>
       <c r="E71">
         <v>18236.96900000001</v>
@@ -7115,45 +7115,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M71">
-        <v>13340.08320505749</v>
+        <v>7814.343978257491</v>
       </c>
       <c r="N71">
-        <v>-6688.838307098307</v>
+        <v>-1163.099080298306</v>
       </c>
       <c r="O71">
-        <v>-2006.651492129492</v>
+        <v>-348.9297240894918</v>
       </c>
       <c r="P71">
-        <v>-4682.186814968815</v>
+        <v>-814.1693562088142</v>
       </c>
       <c r="Q71">
-        <v>3068.813185031185</v>
+        <v>6936.830643791186</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1723176349138609</v>
+        <v>0.1619953200108414</v>
       </c>
       <c r="T71">
-        <v>1.84057025005774</v>
+        <v>1.690783485849165</v>
       </c>
       <c r="U71">
-        <v>0.2346574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V71">
-        <v>0.1495772881409967</v>
+        <v>0.255347534602988</v>
       </c>
       <c r="W71">
-        <v>0.1995580574919175</v>
+        <v>0.1023580574919175</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.4985909604699891</v>
+        <v>0.8511584486766266</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1930021013749416</v>
+        <v>0.1217621837550056</v>
       </c>
       <c r="C72">
-        <v>-22961.38307067029</v>
+        <v>-1383.906534222282</v>
       </c>
       <c r="D72">
-        <v>33443.28692932972</v>
+        <v>55020.76346577772</v>
       </c>
       <c r="E72">
         <v>19060.87000000001</v>
@@ -7197,45 +7197,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M72">
-        <v>13533.41774426122</v>
+        <v>7927.595340261221</v>
       </c>
       <c r="N72">
-        <v>-6882.172846302039</v>
+        <v>-1276.350442302037</v>
       </c>
       <c r="O72">
-        <v>-2064.651853890612</v>
+        <v>-382.905132690611</v>
       </c>
       <c r="P72">
-        <v>-4817.520992411428</v>
+        <v>-893.4453096114257</v>
       </c>
       <c r="Q72">
-        <v>2933.479007588572</v>
+        <v>6857.554690388574</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1765348894109896</v>
+        <v>0.1658684973445361</v>
       </c>
       <c r="T72">
-        <v>1.901922591726331</v>
+        <v>1.74714293537747</v>
       </c>
       <c r="U72">
-        <v>0.2346574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V72">
-        <v>0.1474404697389825</v>
+        <v>0.2516997126800882</v>
       </c>
       <c r="W72">
-        <v>0.2000594779309211</v>
+        <v>0.1028594779309211</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.4914682324632749</v>
+        <v>0.8389990422669606</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1948906762571633</v>
+        <v>0.1226787586372272</v>
       </c>
       <c r="C73">
-        <v>-24129.43967354326</v>
+        <v>-2660.839595529767</v>
       </c>
       <c r="D73">
-        <v>33099.13132645674</v>
+        <v>54567.73140447023</v>
       </c>
       <c r="E73">
         <v>19884.771</v>
@@ -7279,45 +7279,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M73">
-        <v>13726.75228346495</v>
+        <v>8040.846702264952</v>
       </c>
       <c r="N73">
-        <v>-7075.507385505767</v>
+        <v>-1389.601804305767</v>
       </c>
       <c r="O73">
-        <v>-2122.65221565173</v>
+        <v>-416.8805412917303</v>
       </c>
       <c r="P73">
-        <v>-4952.855169854038</v>
+        <v>-972.7212630140373</v>
       </c>
       <c r="Q73">
-        <v>2798.144830145962</v>
+        <v>6778.278736985962</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1810429890458513</v>
+        <v>0.1700087903564166</v>
       </c>
       <c r="T73">
-        <v>1.967506129372066</v>
+        <v>1.807389243493934</v>
       </c>
       <c r="U73">
-        <v>0.2346574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V73">
-        <v>0.1453638434046307</v>
+        <v>0.2481546463043123</v>
       </c>
       <c r="W73">
-        <v>0.2005467738505161</v>
+        <v>0.1033467738505161</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4845461446821021</v>
+        <v>0.8271821543477078</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1967792511393849</v>
+        <v>0.1235953335194489</v>
       </c>
       <c r="C74">
-        <v>-25290.48520543176</v>
+        <v>-3930.373197448469</v>
       </c>
       <c r="D74">
-        <v>32761.98679456825</v>
+        <v>54122.09880255153</v>
       </c>
       <c r="E74">
         <v>20708.67200000001</v>
@@ -7361,45 +7361,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M74">
-        <v>13920.08682266869</v>
+        <v>8154.098064268685</v>
       </c>
       <c r="N74">
-        <v>-7268.841924709501</v>
+        <v>-1502.8531663095</v>
       </c>
       <c r="O74">
-        <v>-2180.65257741285</v>
+        <v>-450.85594989285</v>
       </c>
       <c r="P74">
-        <v>-5088.189347296651</v>
+        <v>-1051.99721641665</v>
       </c>
       <c r="Q74">
-        <v>2662.810652703349</v>
+        <v>6699.00278358335</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1858730957974888</v>
+        <v>0.1744448185834315</v>
       </c>
       <c r="T74">
-        <v>2.037774205421068</v>
+        <v>1.871938859333003</v>
       </c>
       <c r="U74">
-        <v>0.2346574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V74">
-        <v>0.1433449011351219</v>
+        <v>0.2447080539945302</v>
       </c>
       <c r="W74">
-        <v>0.2010205337723446</v>
+        <v>0.1038205337723446</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4778163371170729</v>
+        <v>0.8156935133151006</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1986678260216066</v>
+        <v>0.1245119084016706</v>
       </c>
       <c r="C75">
-        <v>-26444.73174835007</v>
+        <v>-5192.687156668362</v>
       </c>
       <c r="D75">
-        <v>32431.64125164993</v>
+        <v>53683.68584333164</v>
       </c>
       <c r="E75">
         <v>21532.573</v>
@@ -7443,45 +7443,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M75">
-        <v>14113.42136187242</v>
+        <v>8267.349426272416</v>
       </c>
       <c r="N75">
-        <v>-7462.176463913233</v>
+        <v>-1616.104528313232</v>
       </c>
       <c r="O75">
-        <v>-2238.65293917397</v>
+        <v>-484.8313584939694</v>
       </c>
       <c r="P75">
-        <v>-5223.523524739263</v>
+        <v>-1131.273169819262</v>
       </c>
       <c r="Q75">
-        <v>2527.476475260737</v>
+        <v>6619.726830180738</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1910609882344328</v>
+        <v>0.1792094414939289</v>
       </c>
       <c r="T75">
-        <v>2.113247324140367</v>
+        <v>1.941269928197188</v>
       </c>
       <c r="U75">
-        <v>0.2346574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V75">
-        <v>0.141381272352449</v>
+        <v>0.2413558888713174</v>
       </c>
       <c r="W75">
-        <v>0.2014813139702873</v>
+        <v>0.1042813139702873</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4712709078414965</v>
+        <v>0.8045196295710582</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2005564009038283</v>
+        <v>0.1476079037613627</v>
       </c>
       <c r="C76">
-        <v>-27592.38291584347</v>
+        <v>-15116.79807155282</v>
       </c>
       <c r="D76">
-        <v>32107.89108415654</v>
+        <v>44583.47592844719</v>
       </c>
       <c r="E76">
         <v>22356.47400000001</v>
@@ -7525,45 +7525,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M76">
-        <v>14306.75590107615</v>
+        <v>10099.91739507615</v>
       </c>
       <c r="N76">
-        <v>-7655.511003116964</v>
+        <v>-3448.672497116964</v>
       </c>
       <c r="O76">
-        <v>-2296.653300935089</v>
+        <v>-1034.601749135089</v>
       </c>
       <c r="P76">
-        <v>-5358.857702181875</v>
+        <v>-2414.070747981875</v>
       </c>
       <c r="Q76">
-        <v>2392.142297818125</v>
+        <v>5336.929252018125</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1966479493203726</v>
+        <v>0.1893844987724281</v>
       </c>
       <c r="T76">
-        <v>2.194526067376536</v>
+        <v>2.089329409529574</v>
       </c>
       <c r="U76">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V76">
-        <v>0.1394707146179564</v>
+        <v>0.1975633454547389</v>
       </c>
       <c r="W76">
-        <v>0.2019296406493668</v>
+        <v>0.1329296406493668</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4649023820598547</v>
+        <v>0.6585444848491295</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.20244497578605</v>
+        <v>0.1908779591670749</v>
       </c>
       <c r="C77">
-        <v>-28733.63427149454</v>
+        <v>-26686.90518644346</v>
       </c>
       <c r="D77">
-        <v>31790.54072850546</v>
+        <v>33837.26981355654</v>
       </c>
       <c r="E77">
         <v>23180.37500000001</v>
@@ -7607,37 +7607,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M77">
-        <v>14500.09044027988</v>
+        <v>13573.20181527988</v>
       </c>
       <c r="N77">
-        <v>-7848.845542320696</v>
+        <v>-6921.956917320695</v>
       </c>
       <c r="O77">
-        <v>-2354.653662696209</v>
+        <v>-2076.587075196208</v>
       </c>
       <c r="P77">
-        <v>-5494.191879624487</v>
+        <v>-4845.369842124486</v>
       </c>
       <c r="Q77">
-        <v>2256.808120375513</v>
+        <v>2905.630157875514</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2026818672931875</v>
+        <v>0.2014138008172871</v>
       </c>
       <c r="T77">
-        <v>2.282307110071597</v>
+        <v>2.264370411541027</v>
       </c>
       <c r="U77">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V77">
-        <v>0.137611105089717</v>
+        <v>0.14700831068035</v>
       </c>
       <c r="W77">
-        <v>0.2023660119503375</v>
+        <v>0.1873660119503374</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.45870368363239</v>
+        <v>0.4900277022678334</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2043335506682716</v>
+        <v>0.1926165340492965</v>
       </c>
       <c r="C78">
-        <v>-29868.67372285377</v>
+        <v>-27835.36747588204</v>
       </c>
       <c r="D78">
-        <v>31479.40227714623</v>
+        <v>33512.70852411796</v>
       </c>
       <c r="E78">
         <v>24004.27600000001</v>
@@ -7689,37 +7689,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M78">
-        <v>14693.42497948361</v>
+        <v>13754.17783948361</v>
       </c>
       <c r="N78">
-        <v>-8042.180081524428</v>
+        <v>-7102.932941524426</v>
       </c>
       <c r="O78">
-        <v>-2412.654024457328</v>
+        <v>-2130.879882457328</v>
       </c>
       <c r="P78">
-        <v>-5629.5260570671</v>
+        <v>-4972.053059067099</v>
       </c>
       <c r="Q78">
-        <v>2121.4739429329</v>
+        <v>2778.946940932901</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.209218611763737</v>
+        <v>0.2078977091846741</v>
       </c>
       <c r="T78">
-        <v>2.377403239657914</v>
+        <v>2.358719178688571</v>
       </c>
       <c r="U78">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V78">
-        <v>0.135800432654326</v>
+        <v>0.145073990802977</v>
       </c>
       <c r="W78">
-        <v>0.2027908997960194</v>
+        <v>0.1877908997960194</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4526681088477532</v>
+        <v>0.4835799693432566</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2062221255504933</v>
+        <v>0.1943551089315182</v>
       </c>
       <c r="C79">
-        <v>-30997.68189246157</v>
+        <v>-28977.66264680264</v>
       </c>
       <c r="D79">
-        <v>31174.29510753844</v>
+        <v>33194.31435319737</v>
       </c>
       <c r="E79">
         <v>24828.17700000001</v>
@@ -7771,37 +7771,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M79">
-        <v>14886.75951868735</v>
+        <v>13935.15386368734</v>
       </c>
       <c r="N79">
-        <v>-8235.514620728161</v>
+        <v>-7283.90896572816</v>
       </c>
       <c r="O79">
-        <v>-2470.654386218449</v>
+        <v>-2185.172689718448</v>
       </c>
       <c r="P79">
-        <v>-5764.860234509713</v>
+        <v>-5098.736276009712</v>
       </c>
       <c r="Q79">
-        <v>1986.139765490287</v>
+        <v>2652.263723990288</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2163237687969429</v>
+        <v>0.2149454356709642</v>
       </c>
       <c r="T79">
-        <v>2.48076859790391</v>
+        <v>2.461272186457639</v>
       </c>
       <c r="U79">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V79">
-        <v>0.1340367906718022</v>
+        <v>0.1431899130003409</v>
       </c>
       <c r="W79">
-        <v>0.2032047515937616</v>
+        <v>0.1882047515937616</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4467893022393408</v>
+        <v>0.4772997100011364</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.208110700432715</v>
+        <v>0.1960936838137399</v>
       </c>
       <c r="C80">
-        <v>-32120.83246750104</v>
+        <v>-30113.96482074703</v>
       </c>
       <c r="D80">
-        <v>30875.04553249897</v>
+        <v>32881.91317925297</v>
       </c>
       <c r="E80">
         <v>25652.07800000001</v>
@@ -7853,37 +7853,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M80">
-        <v>15080.09405789108</v>
+        <v>14116.12988789107</v>
       </c>
       <c r="N80">
-        <v>-8428.849159931891</v>
+        <v>-7464.88498993189</v>
       </c>
       <c r="O80">
-        <v>-2528.654747979567</v>
+        <v>-2239.465496979567</v>
       </c>
       <c r="P80">
-        <v>-5900.194411952324</v>
+        <v>-5225.419492952324</v>
       </c>
       <c r="Q80">
-        <v>1850.805588047676</v>
+        <v>2525.580507047676</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.224074849196804</v>
+        <v>0.222633864565099</v>
       </c>
       <c r="T80">
-        <v>2.593530806899542</v>
+        <v>2.573148194932986</v>
       </c>
       <c r="U80">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V80">
-        <v>0.132318370278574</v>
+        <v>0.1413541448849519</v>
       </c>
       <c r="W80">
-        <v>0.2036079918069463</v>
+        <v>0.1886079918069463</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4410612342619135</v>
+        <v>0.4711804829498398</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2099992753149367</v>
+        <v>0.1978322586959616</v>
       </c>
       <c r="C81">
-        <v>-33238.29252950396</v>
+        <v>-31244.44162554102</v>
       </c>
       <c r="D81">
-        <v>30581.48647049605</v>
+        <v>32575.33737445899</v>
       </c>
       <c r="E81">
         <v>26475.97900000001</v>
@@ -7935,37 +7935,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M81">
-        <v>15273.42859709481</v>
+        <v>14297.10591209481</v>
       </c>
       <c r="N81">
-        <v>-8622.183699135625</v>
+        <v>-7645.861014135624</v>
       </c>
       <c r="O81">
-        <v>-2586.655109740687</v>
+        <v>-2293.758304240687</v>
       </c>
       <c r="P81">
-        <v>-6035.528589394938</v>
+        <v>-5352.102709894936</v>
       </c>
       <c r="Q81">
-        <v>1715.471410605062</v>
+        <v>2398.897290105064</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2325641277299851</v>
+        <v>0.2310545247824847</v>
       </c>
       <c r="T81">
-        <v>2.717032273894759</v>
+        <v>2.695679061358367</v>
       </c>
       <c r="U81">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V81">
-        <v>0.1306434541990984</v>
+        <v>0.1395648519117247</v>
       </c>
       <c r="W81">
-        <v>0.204001023407139</v>
+        <v>0.189001023407139</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4354781806636613</v>
+        <v>0.4652161730390822</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2118878501971583</v>
+        <v>0.1995708335781832</v>
       </c>
       <c r="C82">
-        <v>-34350.22286542479</v>
+        <v>-32369.25449522</v>
       </c>
       <c r="D82">
-        <v>30293.45713457521</v>
+        <v>32274.42550478</v>
       </c>
       <c r="E82">
         <v>27299.88</v>
@@ -8017,37 +8017,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M82">
-        <v>15466.76313629854</v>
+        <v>14478.08193629854</v>
       </c>
       <c r="N82">
-        <v>-8815.518238339355</v>
+        <v>-7826.837038339354</v>
       </c>
       <c r="O82">
-        <v>-2644.655471501806</v>
+        <v>-2348.051111501806</v>
       </c>
       <c r="P82">
-        <v>-6170.862766837548</v>
+        <v>-5478.785926837548</v>
       </c>
       <c r="Q82">
-        <v>1580.137233162452</v>
+        <v>2272.214073162452</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2419023341164844</v>
+        <v>0.2403172510216089</v>
       </c>
       <c r="T82">
-        <v>2.852883887589497</v>
+        <v>2.830463014426285</v>
       </c>
       <c r="U82">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V82">
-        <v>0.1290104110216097</v>
+        <v>0.1378202912628281</v>
       </c>
       <c r="W82">
-        <v>0.2043842292173268</v>
+        <v>0.1893842292173268</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4300347034053656</v>
+        <v>0.4594009708760938</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.21377642507938</v>
+        <v>0.2013094084604049</v>
       </c>
       <c r="C83">
-        <v>-35456.77826129986</v>
+        <v>-33488.55895348376</v>
       </c>
       <c r="D83">
-        <v>30010.80273870015</v>
+        <v>31979.02204651626</v>
       </c>
       <c r="E83">
         <v>28123.78100000002</v>
@@ -8099,37 +8099,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M83">
-        <v>15660.09767550227</v>
+        <v>14659.05796050227</v>
       </c>
       <c r="N83">
-        <v>-9008.852777543088</v>
+        <v>-8007.813062543088</v>
       </c>
       <c r="O83">
-        <v>-2702.655833262927</v>
+        <v>-2402.343918762926</v>
       </c>
       <c r="P83">
-        <v>-6306.196944280162</v>
+        <v>-5605.469143780161</v>
       </c>
       <c r="Q83">
-        <v>1444.803055719838</v>
+        <v>2145.530856219839</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2522235095962994</v>
+        <v>0.2505550010753778</v>
       </c>
       <c r="T83">
-        <v>3.003035671146839</v>
+        <v>2.979434752027669</v>
       </c>
       <c r="U83">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V83">
-        <v>0.1274176898978861</v>
+        <v>0.1361188061855093</v>
       </c>
       <c r="W83">
-        <v>0.2047579731556582</v>
+        <v>0.1897579731556582</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4247256329929536</v>
+        <v>0.4537293539516976</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2156649999616017</v>
+        <v>0.2030479833426266</v>
       </c>
       <c r="C84">
-        <v>-36558.10777961832</v>
+        <v>-34602.50488172552</v>
       </c>
       <c r="D84">
-        <v>29733.37422038169</v>
+        <v>31688.97711827449</v>
       </c>
       <c r="E84">
         <v>28947.68200000002</v>
@@ -8181,37 +8181,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M84">
-        <v>15853.432214706</v>
+        <v>14840.033984706</v>
       </c>
       <c r="N84">
-        <v>-9202.18731674682</v>
+        <v>-8188.78908674682</v>
       </c>
       <c r="O84">
-        <v>-2760.656195024046</v>
+        <v>-2456.636726024046</v>
       </c>
       <c r="P84">
-        <v>-6441.531121722774</v>
+        <v>-5732.152360722774</v>
       </c>
       <c r="Q84">
-        <v>1309.468878277226</v>
+        <v>2018.847639277226</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2636914823516494</v>
+        <v>0.2619302789128988</v>
       </c>
       <c r="T84">
-        <v>3.169870986210552</v>
+        <v>3.144958904918095</v>
       </c>
       <c r="U84">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V84">
-        <v>0.1258638156308387</v>
+        <v>0.1344588207442226</v>
       </c>
       <c r="W84">
-        <v>0.2051226013881766</v>
+        <v>0.1901226013881766</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4195460521027956</v>
+        <v>0.4481960691474085</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2175535748438234</v>
+        <v>0.2047865582248483</v>
       </c>
       <c r="C85">
-        <v>-37654.35502144968</v>
+        <v>-35711.2367726067</v>
       </c>
       <c r="D85">
-        <v>29461.02797855033</v>
+        <v>31404.1462273933</v>
       </c>
       <c r="E85">
         <v>29771.58300000001</v>
@@ -8263,37 +8263,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M85">
-        <v>16046.76675390974</v>
+        <v>15021.01000890974</v>
       </c>
       <c r="N85">
-        <v>-9395.521855950552</v>
+        <v>-8369.765110950551</v>
       </c>
       <c r="O85">
-        <v>-2818.656556785165</v>
+        <v>-2510.929533285165</v>
       </c>
       <c r="P85">
-        <v>-6576.865299165387</v>
+        <v>-5858.835577665386</v>
       </c>
       <c r="Q85">
-        <v>1174.134700834613</v>
+        <v>1892.164422334614</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2765086283723346</v>
+        <v>0.2746438247313047</v>
       </c>
       <c r="T85">
-        <v>3.356333985399409</v>
+        <v>3.329956487560337</v>
       </c>
       <c r="U85">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V85">
-        <v>0.1243473841172141</v>
+        <v>0.1328388349521235</v>
       </c>
       <c r="W85">
-        <v>0.2054784433982247</v>
+        <v>0.1904784433982247</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4144912803907138</v>
+        <v>0.4427961165070783</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.219442149726045</v>
+        <v>0.2065251331070699</v>
       </c>
       <c r="C86">
-        <v>-38745.65837429609</v>
+        <v>-36814.89397007778</v>
       </c>
       <c r="D86">
-        <v>29193.62562570392</v>
+        <v>31124.39002992222</v>
       </c>
       <c r="E86">
         <v>30595.48400000001</v>
@@ -8345,37 +8345,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M86">
-        <v>16240.10129311347</v>
+        <v>15201.98603311347</v>
       </c>
       <c r="N86">
-        <v>-9588.856395154284</v>
+        <v>-8550.741135154281</v>
       </c>
       <c r="O86">
-        <v>-2876.656918546285</v>
+        <v>-2565.222340546284</v>
       </c>
       <c r="P86">
-        <v>-6712.199476607999</v>
+        <v>-5985.518794607997</v>
       </c>
       <c r="Q86">
-        <v>1038.800523392001</v>
+        <v>1765.481205392003</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2909279176456054</v>
+        <v>0.2889465637770111</v>
       </c>
       <c r="T86">
-        <v>3.56610485948687</v>
+        <v>3.538078768032856</v>
       </c>
       <c r="U86">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V86">
-        <v>0.1228670581158187</v>
+        <v>0.1312574202503125</v>
       </c>
       <c r="W86">
-        <v>0.2058258129794621</v>
+        <v>0.1908258129794621</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4095568603860624</v>
+        <v>0.4375247341677083</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2213307246082667</v>
+        <v>0.2082637079892916</v>
       </c>
       <c r="C87">
-        <v>-39832.15124656812</v>
+        <v>-37913.61089668361</v>
       </c>
       <c r="D87">
-        <v>28931.03375343189</v>
+        <v>30849.57410331639</v>
       </c>
       <c r="E87">
         <v>31419.38500000001</v>
@@ -8427,37 +8427,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M87">
-        <v>16433.4358323172</v>
+        <v>15382.9620573172</v>
       </c>
       <c r="N87">
-        <v>-9782.190934358014</v>
+        <v>-8731.717159358013</v>
       </c>
       <c r="O87">
-        <v>-2934.657280307404</v>
+        <v>-2619.515147807404</v>
       </c>
       <c r="P87">
-        <v>-6847.53365405061</v>
+        <v>-6112.202011550609</v>
       </c>
       <c r="Q87">
-        <v>903.4663459493904</v>
+        <v>1638.797988449391</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3072697788219791</v>
+        <v>0.3051563346954784</v>
       </c>
       <c r="T87">
-        <v>3.803845183452661</v>
+        <v>3.773950685901712</v>
       </c>
       <c r="U87">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V87">
-        <v>0.1214215633144562</v>
+        <v>0.1297132153061912</v>
       </c>
       <c r="W87">
-        <v>0.206165009158788</v>
+        <v>0.191165009158788</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4047385443815206</v>
+        <v>0.4323773843539707</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2232192994904884</v>
+        <v>0.2100022828715133</v>
       </c>
       <c r="C88">
-        <v>-40913.96228951919</v>
+        <v>-39007.51726893207</v>
       </c>
       <c r="D88">
-        <v>28673.12371048081</v>
+        <v>30579.56873106794</v>
       </c>
       <c r="E88">
         <v>32243.28600000001</v>
@@ -8509,37 +8509,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M88">
-        <v>16626.77037152093</v>
+        <v>15563.93808152093</v>
       </c>
       <c r="N88">
-        <v>-9975.525473561744</v>
+        <v>-8912.693183561745</v>
       </c>
       <c r="O88">
-        <v>-2992.657642068523</v>
+        <v>-2673.807955068523</v>
       </c>
       <c r="P88">
-        <v>-6982.86783149322</v>
+        <v>-6238.885228493222</v>
       </c>
       <c r="Q88">
-        <v>768.1321685067796</v>
+        <v>1512.114771506778</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3259461915949776</v>
+        <v>0.3236817871737269</v>
       </c>
       <c r="T88">
-        <v>4.075548410842137</v>
+        <v>4.043518592037549</v>
       </c>
       <c r="U88">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V88">
-        <v>0.1200096846712648</v>
+        <v>0.1282049221049564</v>
       </c>
       <c r="W88">
-        <v>0.2064963170548738</v>
+        <v>0.1914963170548738</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4000322822375494</v>
+        <v>0.4273497403498546</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.22510787437271</v>
+        <v>0.2117408577537349</v>
       </c>
       <c r="C89">
-        <v>-41991.21560741388</v>
+        <v>-40096.73830145088</v>
       </c>
       <c r="D89">
-        <v>28419.77139258612</v>
+        <v>30314.24869854912</v>
       </c>
       <c r="E89">
         <v>33067.18700000001</v>
@@ -8591,37 +8591,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M89">
-        <v>16820.10491072466</v>
+        <v>15744.91410572466</v>
       </c>
       <c r="N89">
-        <v>-10168.86001276548</v>
+        <v>-9093.669207765475</v>
       </c>
       <c r="O89">
-        <v>-3050.658003829643</v>
+        <v>-2728.100762329642</v>
       </c>
       <c r="P89">
-        <v>-7118.202008935834</v>
+        <v>-6365.568445435832</v>
       </c>
       <c r="Q89">
-        <v>632.7979910641661</v>
+        <v>1385.431554564168</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3474958986407451</v>
+        <v>0.3450573092640136</v>
       </c>
       <c r="T89">
-        <v>4.38905213475307</v>
+        <v>4.354558483732745</v>
       </c>
       <c r="U89">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V89">
-        <v>0.1186302630083767</v>
+        <v>0.1267313023106466</v>
       </c>
       <c r="W89">
-        <v>0.2068200086774864</v>
+        <v>0.1918200086774864</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3954342100279223</v>
+        <v>0.422437674368822</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2269964492549317</v>
+        <v>0.2134794326359566</v>
       </c>
       <c r="C90">
-        <v>-43064.0309566518</v>
+        <v>-41181.39490060796</v>
       </c>
       <c r="D90">
-        <v>28170.85704334821</v>
+        <v>30053.49309939204</v>
       </c>
       <c r="E90">
         <v>33891.088</v>
@@ -8673,37 +8673,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M90">
-        <v>17013.43944992839</v>
+        <v>15925.89012992839</v>
       </c>
       <c r="N90">
-        <v>-10362.19455196921</v>
+        <v>-9274.645231969207</v>
       </c>
       <c r="O90">
-        <v>-3108.658365590762</v>
+        <v>-2782.393569590762</v>
       </c>
       <c r="P90">
-        <v>-7253.536186378446</v>
+        <v>-6492.251662378445</v>
       </c>
       <c r="Q90">
-        <v>497.4638136215544</v>
+        <v>1258.748337621555</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3726372235274739</v>
+        <v>0.3699954183693481</v>
       </c>
       <c r="T90">
-        <v>4.754806479315827</v>
+        <v>4.717438357377142</v>
       </c>
       <c r="U90">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V90">
-        <v>0.117282191837827</v>
+        <v>0.1252911738752983</v>
       </c>
       <c r="W90">
-        <v>0.2071363436723123</v>
+        <v>0.1921363436723123</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3909406394594233</v>
+        <v>0.4176372462509944</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2288850241371534</v>
+        <v>0.2152180075181783</v>
       </c>
       <c r="C91">
-        <v>-44132.52393451807</v>
+        <v>-42261.60384822397</v>
       </c>
       <c r="D91">
-        <v>27926.26506548193</v>
+        <v>29797.18515177604</v>
       </c>
       <c r="E91">
         <v>34714.98900000002</v>
@@ -8755,37 +8755,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M91">
-        <v>17206.77398913213</v>
+        <v>16106.86615413213</v>
       </c>
       <c r="N91">
-        <v>-10555.52909117294</v>
+        <v>-9455.621256172941</v>
       </c>
       <c r="O91">
-        <v>-3166.658727351883</v>
+        <v>-2836.686376851882</v>
       </c>
       <c r="P91">
-        <v>-7388.870363821061</v>
+        <v>-6618.934879321059</v>
       </c>
       <c r="Q91">
-        <v>362.1296361789391</v>
+        <v>1132.065120678941</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.402349698393608</v>
+        <v>0.399467729130198</v>
       </c>
       <c r="T91">
-        <v>5.187061613799084</v>
+        <v>5.146296389865973</v>
       </c>
       <c r="U91">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V91">
-        <v>0.1159644144014469</v>
+        <v>0.1238834078766994</v>
       </c>
       <c r="W91">
-        <v>0.2074455700155691</v>
+        <v>0.1924455700155691</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3865480480048229</v>
+        <v>0.4129446929223315</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2307735990193751</v>
+        <v>0.2169565824003999</v>
       </c>
       <c r="C92">
-        <v>-45196.80615818568</v>
+        <v>-43337.47797596376</v>
       </c>
       <c r="D92">
-        <v>27685.88384181433</v>
+        <v>29545.21202403625</v>
       </c>
       <c r="E92">
         <v>35538.89000000001</v>
@@ -8837,37 +8837,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M92">
-        <v>17400.10852833586</v>
+        <v>16287.84217833586</v>
       </c>
       <c r="N92">
-        <v>-10748.86363037667</v>
+        <v>-9636.597280376673</v>
       </c>
       <c r="O92">
-        <v>-3224.659089113002</v>
+        <v>-2890.979184113002</v>
       </c>
       <c r="P92">
-        <v>-7524.204541263673</v>
+        <v>-6745.618096263671</v>
       </c>
       <c r="Q92">
-        <v>226.7954587363274</v>
+        <v>1005.381903736329</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4380046682329689</v>
+        <v>0.4348345020432178</v>
       </c>
       <c r="T92">
-        <v>5.705767775178995</v>
+        <v>5.660926028852571</v>
       </c>
       <c r="U92">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V92">
-        <v>0.1146759209080975</v>
+        <v>0.1225069255669583</v>
       </c>
       <c r="W92">
-        <v>0.2077479246623091</v>
+        <v>0.1927479246623091</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3822530696936582</v>
+        <v>0.4083564185565278</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2326621739015967</v>
+        <v>0.2186951572826216</v>
       </c>
       <c r="C93">
-        <v>-46256.98543455178</v>
+        <v>-44409.12633095396</v>
       </c>
       <c r="D93">
-        <v>27449.60556544822</v>
+        <v>29297.46466904605</v>
       </c>
       <c r="E93">
         <v>36362.79100000001</v>
@@ -8919,37 +8919,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M93">
-        <v>17593.44306753959</v>
+        <v>16468.81820253959</v>
       </c>
       <c r="N93">
-        <v>-10942.1981695804</v>
+        <v>-9817.573304580403</v>
       </c>
       <c r="O93">
-        <v>-3282.659450874121</v>
+        <v>-2945.271991374121</v>
       </c>
       <c r="P93">
-        <v>-7659.538718706282</v>
+        <v>-6872.301313206282</v>
       </c>
       <c r="Q93">
-        <v>91.46128129371755</v>
+        <v>878.6986867937176</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4815829647032987</v>
+        <v>0.4780605578257975</v>
       </c>
       <c r="T93">
-        <v>6.339741972421105</v>
+        <v>6.289917809836189</v>
       </c>
       <c r="U93">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V93">
-        <v>0.1134157459530634</v>
+        <v>0.1211606956156731</v>
       </c>
       <c r="W93">
-        <v>0.2080436341519779</v>
+        <v>0.1930436341519778</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3780524865102115</v>
+        <v>0.4038689853855769</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2345507487838184</v>
+        <v>0.2204337321648433</v>
       </c>
       <c r="C94">
-        <v>-47313.16592145122</v>
+        <v>-45476.65433313706</v>
       </c>
       <c r="D94">
-        <v>27217.32607854879</v>
+        <v>29053.83766686295</v>
       </c>
       <c r="E94">
         <v>37186.69200000001</v>
@@ -9001,37 +9001,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M94">
-        <v>17786.77760674332</v>
+        <v>16649.79422674332</v>
       </c>
       <c r="N94">
-        <v>-11135.53270878414</v>
+        <v>-9998.549328784136</v>
       </c>
       <c r="O94">
-        <v>-3340.659812635241</v>
+        <v>-2999.564798635241</v>
       </c>
       <c r="P94">
-        <v>-7794.872896148896</v>
+        <v>-6998.984530148895</v>
       </c>
       <c r="Q94">
-        <v>-43.87289614889596</v>
+        <v>752.0154698511051</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5360558352912111</v>
+        <v>0.5320931275540224</v>
       </c>
       <c r="T94">
-        <v>7.132209718973745</v>
+        <v>7.076157536065716</v>
       </c>
       <c r="U94">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V94">
-        <v>0.1121829661057475</v>
+        <v>0.119843731532894</v>
       </c>
       <c r="W94">
-        <v>0.2083329151744799</v>
+        <v>0.1933329151744799</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3739432203524917</v>
+        <v>0.3994791051096468</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2364393236660401</v>
+        <v>0.2221723070470649</v>
       </c>
       <c r="C95">
-        <v>-48365.44828075334</v>
+        <v>-46540.16392483936</v>
       </c>
       <c r="D95">
-        <v>26988.94471924666</v>
+        <v>28814.22907516064</v>
       </c>
       <c r="E95">
         <v>38010.59300000001</v>
@@ -9083,37 +9083,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M95">
-        <v>17980.11214594705</v>
+        <v>16830.77025094705</v>
       </c>
       <c r="N95">
-        <v>-11328.86724798787</v>
+        <v>-10179.52535298787</v>
       </c>
       <c r="O95">
-        <v>-3398.66017439636</v>
+        <v>-3053.85760589636</v>
       </c>
       <c r="P95">
-        <v>-7930.207073591508</v>
+        <v>-7125.667747091506</v>
       </c>
       <c r="Q95">
-        <v>-179.2070735915077</v>
+        <v>625.3322529084935</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6060923831899556</v>
+        <v>0.6015635743474541</v>
       </c>
       <c r="T95">
-        <v>8.151096821684281</v>
+        <v>8.087037184075104</v>
       </c>
       <c r="U95">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V95">
-        <v>0.1109766976529976</v>
+        <v>0.1185550892583468</v>
       </c>
       <c r="W95">
-        <v>0.2086159750997239</v>
+        <v>0.1936159750997238</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3699223255099919</v>
+        <v>0.3951836308611559</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2383278985482618</v>
+        <v>0.2239108819292866</v>
       </c>
       <c r="C96">
-        <v>-49413.92982381526</v>
+        <v>-47599.75371299853</v>
       </c>
       <c r="D96">
-        <v>26764.36417618475</v>
+        <v>28578.54028700147</v>
       </c>
       <c r="E96">
         <v>38834.49400000001</v>
@@ -9165,37 +9165,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M96">
-        <v>18173.44668515078</v>
+        <v>17011.74627515078</v>
       </c>
       <c r="N96">
-        <v>-11522.2017871916</v>
+        <v>-10360.5013771916</v>
       </c>
       <c r="O96">
-        <v>-3456.660536157479</v>
+        <v>-3108.150413157479</v>
       </c>
       <c r="P96">
-        <v>-8065.541251034118</v>
+        <v>-7252.350964034118</v>
       </c>
       <c r="Q96">
-        <v>-314.5412510341184</v>
+        <v>498.6490359658819</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6994744470549484</v>
+        <v>0.6941908367386967</v>
       </c>
       <c r="T96">
-        <v>9.509612958631664</v>
+        <v>9.43487671475429</v>
       </c>
       <c r="U96">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V96">
-        <v>0.1097960944864763</v>
+        <v>0.1172938649045346</v>
       </c>
       <c r="W96">
-        <v>0.2088930124733669</v>
+        <v>0.1938930124733668</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3659869816215877</v>
+        <v>0.3909795496817819</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2402164734304834</v>
+        <v>0.2256494568115083</v>
       </c>
       <c r="C97">
-        <v>-50458.704649733</v>
+        <v>-48655.5191044675</v>
       </c>
       <c r="D97">
-        <v>26543.49035026702</v>
+        <v>28346.67589553251</v>
       </c>
       <c r="E97">
         <v>39658.39500000002</v>
@@ -9247,37 +9247,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M97">
-        <v>18366.78122435452</v>
+        <v>17192.72229935452</v>
       </c>
       <c r="N97">
-        <v>-11715.53632639533</v>
+        <v>-10541.47740139533</v>
       </c>
       <c r="O97">
-        <v>-3514.6608979186</v>
+        <v>-3162.4432204186</v>
       </c>
       <c r="P97">
-        <v>-8200.875428476735</v>
+        <v>-7379.034180976734</v>
       </c>
       <c r="Q97">
-        <v>-449.8754284767347</v>
+        <v>371.9658190232658</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8302093364659384</v>
+        <v>0.8238690040864365</v>
       </c>
       <c r="T97">
-        <v>11.411535550358</v>
+        <v>11.32185205770515</v>
       </c>
       <c r="U97">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V97">
-        <v>0.1086403461234608</v>
+        <v>0.1160591926423816</v>
       </c>
       <c r="W97">
-        <v>0.209164217481249</v>
+        <v>0.194164217481249</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3621344870782025</v>
+        <v>0.3868639754746052</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2421050483127051</v>
+        <v>0.22738803169373</v>
       </c>
       <c r="C98">
-        <v>-51499.86377680291</v>
+        <v>-49707.55243478481</v>
       </c>
       <c r="D98">
-        <v>26326.23222319708</v>
+        <v>28118.54356521519</v>
       </c>
       <c r="E98">
         <v>40482.296</v>
@@ -9329,37 +9329,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M98">
-        <v>18560.11576355825</v>
+        <v>17373.69832355824</v>
       </c>
       <c r="N98">
-        <v>-11908.87086559906</v>
+        <v>-10722.45342559906</v>
       </c>
       <c r="O98">
-        <v>-3572.661259679718</v>
+        <v>-3216.736027679718</v>
       </c>
       <c r="P98">
-        <v>-8336.209605919343</v>
+        <v>-7505.717397919342</v>
       </c>
       <c r="Q98">
-        <v>-585.2096059193427</v>
+        <v>245.2826020806579</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.026311670582421</v>
+        <v>1.018386255108043</v>
       </c>
       <c r="T98">
-        <v>14.26441943794747</v>
+        <v>14.15231507213141</v>
       </c>
       <c r="U98">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V98">
-        <v>0.1075086758513414</v>
+        <v>0.1148502427190234</v>
       </c>
       <c r="W98">
-        <v>0.2094297723848002</v>
+        <v>0.1944297723848002</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3583622528378047</v>
+        <v>0.3828341423967448</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2439936231949267</v>
+        <v>0.2291266065759516</v>
       </c>
       <c r="C99">
-        <v>-52537.49526757988</v>
+        <v>-50755.94309077694</v>
       </c>
       <c r="D99">
-        <v>26112.50173242012</v>
+        <v>27894.05390922306</v>
       </c>
       <c r="E99">
         <v>41306.197</v>
@@ -9411,37 +9411,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M99">
-        <v>18753.45030276198</v>
+        <v>17554.67434776197</v>
       </c>
       <c r="N99">
-        <v>-12102.20540480279</v>
+        <v>-10903.42944980279</v>
       </c>
       <c r="O99">
-        <v>-3630.661621440837</v>
+        <v>-3271.028834940837</v>
       </c>
       <c r="P99">
-        <v>-8471.543783361954</v>
+        <v>-7632.400614861954</v>
       </c>
       <c r="Q99">
-        <v>-720.5437833619544</v>
+        <v>118.5993851380463</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.353148894109895</v>
+        <v>1.342581673477391</v>
       </c>
       <c r="T99">
-        <v>19.01922591726329</v>
+        <v>18.86975342950855</v>
       </c>
       <c r="U99">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V99">
-        <v>0.1064003389868946</v>
+        <v>0.1136662195982088</v>
       </c>
       <c r="W99">
-        <v>0.2096898519295153</v>
+        <v>0.1946898519295153</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.354667796622982</v>
+        <v>0.378887398660696</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2458821980771485</v>
+        <v>0.2308651814581733</v>
       </c>
       <c r="C100">
-        <v>-53571.68434789231</v>
+        <v>-51800.77762733374</v>
       </c>
       <c r="D100">
-        <v>25902.2136521077</v>
+        <v>27673.12037266627</v>
       </c>
       <c r="E100">
         <v>42130.09800000001</v>
@@ -9493,37 +9493,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M100">
-        <v>18946.78484196571</v>
+        <v>17735.65037196571</v>
       </c>
       <c r="N100">
-        <v>-12295.53994400653</v>
+        <v>-11084.40547400653</v>
       </c>
       <c r="O100">
-        <v>-3688.661983201958</v>
+        <v>-3325.321642201958</v>
       </c>
       <c r="P100">
-        <v>-8606.87796080457</v>
+        <v>-7759.08383180457</v>
       </c>
       <c r="Q100">
-        <v>-855.8779608045697</v>
+        <v>-8.083831804569854</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.006823341164842</v>
+        <v>1.990972510216087</v>
       </c>
       <c r="T100">
-        <v>28.52883887589494</v>
+        <v>28.30463014426283</v>
       </c>
       <c r="U100">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V100">
-        <v>0.1053146212421303</v>
+        <v>0.1125063602145536</v>
       </c>
       <c r="W100">
-        <v>0.20994462372842</v>
+        <v>0.1949446237284199</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3510487374737677</v>
+        <v>0.3750212007151785</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2477707729593701</v>
+        <v>0.232603756340395</v>
       </c>
       <c r="C101">
-        <v>-54602.51352015273</v>
+        <v>-52842.13987867824</v>
       </c>
       <c r="D101">
-        <v>25695.28547984728</v>
+        <v>27455.65912132177</v>
       </c>
       <c r="E101">
         <v>42953.99900000001</v>
@@ -9575,37 +9575,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M101">
-        <v>19140.11938116944</v>
+        <v>17916.62639616944</v>
       </c>
       <c r="N101">
-        <v>-12488.87448321026</v>
+        <v>-11265.38149821026</v>
       </c>
       <c r="O101">
-        <v>-3746.662344963077</v>
+        <v>-3379.614449463077</v>
       </c>
       <c r="P101">
-        <v>-8742.212138247181</v>
+        <v>-7885.767048747181</v>
       </c>
       <c r="Q101">
-        <v>-991.2121382471814</v>
+        <v>-134.7670487471805</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.967846682329684</v>
+        <v>3.936145020432174</v>
       </c>
       <c r="T101">
-        <v>57.05767775178988</v>
+        <v>56.60926028852565</v>
       </c>
       <c r="U101">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V101">
-        <v>0.1042508371891795</v>
+        <v>0.1113699323335985</v>
       </c>
       <c r="W101">
-        <v>0.2101942486222962</v>
+        <v>0.1951942486222962</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3475027906305984</v>
+        <v>0.3712331077786616</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/mexico/mexico_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_telecom_wireless.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08952433013601599</v>
+        <v>0.0894192595631631</v>
       </c>
       <c r="C2">
-        <v>78981.95938756995</v>
+        <v>78262.66457292988</v>
       </c>
       <c r="D2">
-        <v>77713.55938756996</v>
+        <v>77818.16557292988</v>
       </c>
       <c r="E2">
-        <v>-38612.2</v>
+        <v>-37788.299</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>823.9010000000001</v>
       </c>
       <c r="G2">
         <v>1268.4</v>
@@ -1457,28 +1457,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>56.97892370373172</v>
       </c>
       <c r="N2">
-        <v>6651.244897959185</v>
+        <v>6594.265974255452</v>
       </c>
       <c r="O2">
-        <v>1995.373469387755</v>
+        <v>1978.279792276636</v>
       </c>
       <c r="P2">
-        <v>4655.87142857143</v>
+        <v>4615.986181978817</v>
       </c>
       <c r="Q2">
-        <v>12406.87142857143</v>
+        <v>12366.98618197882</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08952433013601599</v>
+        <v>0.08983349206627064</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6407409627425109</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>116.7316696353037</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0894192595631631</v>
+        <v>0.08931418899031024</v>
       </c>
       <c r="C3">
-        <v>78262.66457292988</v>
+        <v>77543.65174776557</v>
       </c>
       <c r="D3">
-        <v>77818.16557292988</v>
+        <v>77923.05374776557</v>
       </c>
       <c r="E3">
-        <v>-37788.299</v>
+        <v>-36964.39799999999</v>
       </c>
       <c r="F3">
-        <v>823.9010000000001</v>
+        <v>1647.802</v>
       </c>
       <c r="G3">
         <v>1268.4</v>
@@ -1539,28 +1539,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M3">
-        <v>56.97892370373172</v>
+        <v>113.9578474074634</v>
       </c>
       <c r="N3">
-        <v>6594.265974255452</v>
+        <v>6537.287050551721</v>
       </c>
       <c r="O3">
-        <v>1978.279792276636</v>
+        <v>1961.186115165516</v>
       </c>
       <c r="P3">
-        <v>4615.986181978817</v>
+        <v>4576.100935386205</v>
       </c>
       <c r="Q3">
-        <v>12366.98618197882</v>
+        <v>12327.1009353862</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08983349206627064</v>
+        <v>0.09014896342367337</v>
       </c>
       <c r="T3">
-        <v>0.6407409627425109</v>
+        <v>0.6453314553828785</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>116.7316696353037</v>
+        <v>58.36583481765184</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08931418899031024</v>
+        <v>0.08920911841745735</v>
       </c>
       <c r="C4">
-        <v>77543.65174776557</v>
+        <v>76824.92205386506</v>
       </c>
       <c r="D4">
-        <v>77923.05374776557</v>
+        <v>78028.22505386506</v>
       </c>
       <c r="E4">
-        <v>-36964.39799999999</v>
+        <v>-36140.497</v>
       </c>
       <c r="F4">
-        <v>1647.802</v>
+        <v>2471.703</v>
       </c>
       <c r="G4">
         <v>1268.4</v>
@@ -1621,28 +1621,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M4">
-        <v>113.9578474074634</v>
+        <v>170.9367711111951</v>
       </c>
       <c r="N4">
-        <v>6537.287050551721</v>
+        <v>6480.308126847989</v>
       </c>
       <c r="O4">
-        <v>1961.186115165516</v>
+        <v>1944.092438054397</v>
       </c>
       <c r="P4">
-        <v>4576.100935386205</v>
+        <v>4536.215688793593</v>
       </c>
       <c r="Q4">
-        <v>12327.1009353862</v>
+        <v>12287.21568879359</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09014896342367337</v>
+        <v>0.09047093934514623</v>
       </c>
       <c r="T4">
-        <v>0.6453314553828785</v>
+        <v>0.6500165973560371</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.36583481765184</v>
+        <v>38.91055654510123</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08920911841745735</v>
+        <v>0.08910404784460449</v>
       </c>
       <c r="C5">
-        <v>76824.92205386506</v>
+        <v>76106.47663918874</v>
       </c>
       <c r="D5">
-        <v>78028.22505386506</v>
+        <v>78133.68063918875</v>
       </c>
       <c r="E5">
-        <v>-36140.497</v>
+        <v>-35316.596</v>
       </c>
       <c r="F5">
-        <v>2471.703</v>
+        <v>3295.604</v>
       </c>
       <c r="G5">
         <v>1268.4</v>
@@ -1703,28 +1703,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M5">
-        <v>170.9367711111951</v>
+        <v>227.9156948149269</v>
       </c>
       <c r="N5">
-        <v>6480.308126847989</v>
+        <v>6423.329203144258</v>
       </c>
       <c r="O5">
-        <v>1944.092438054397</v>
+        <v>1926.998760943277</v>
       </c>
       <c r="P5">
-        <v>4536.215688793593</v>
+        <v>4496.330442200981</v>
       </c>
       <c r="Q5">
-        <v>12287.21568879359</v>
+        <v>12247.33044220098</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09047093934514623</v>
+        <v>0.09079962309831646</v>
       </c>
       <c r="T5">
-        <v>0.6500165973560371</v>
+        <v>0.6547993464536367</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.91055654510123</v>
+        <v>29.18291740882592</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08910404784460449</v>
+        <v>0.08899897727175161</v>
       </c>
       <c r="C6">
-        <v>76106.47663918874</v>
+        <v>75388.31665791151</v>
       </c>
       <c r="D6">
-        <v>78133.68063918875</v>
+        <v>78239.42165791152</v>
       </c>
       <c r="E6">
-        <v>-35316.596</v>
+        <v>-34492.695</v>
       </c>
       <c r="F6">
-        <v>3295.604</v>
+        <v>4119.505</v>
       </c>
       <c r="G6">
         <v>1268.4</v>
@@ -1785,28 +1785,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M6">
-        <v>227.9156948149269</v>
+        <v>284.8946185186585</v>
       </c>
       <c r="N6">
-        <v>6423.329203144258</v>
+        <v>6366.350279440526</v>
       </c>
       <c r="O6">
-        <v>1926.998760943277</v>
+        <v>1909.905083832158</v>
       </c>
       <c r="P6">
-        <v>4496.330442200981</v>
+        <v>4456.445195608369</v>
       </c>
       <c r="Q6">
-        <v>12247.33044220098</v>
+        <v>12207.44519560837</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09079962309831646</v>
+        <v>0.09113522650944816</v>
       </c>
       <c r="T6">
-        <v>0.6547993464536367</v>
+        <v>0.6596827850059225</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.18291740882592</v>
+        <v>23.34633392706074</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08899897727175161</v>
+        <v>0.08889390669889871</v>
       </c>
       <c r="C7">
-        <v>75388.31665791151</v>
+        <v>74670.44327046453</v>
       </c>
       <c r="D7">
-        <v>78239.42165791152</v>
+        <v>78345.44927046454</v>
       </c>
       <c r="E7">
-        <v>-34492.695</v>
+        <v>-33668.79399999999</v>
       </c>
       <c r="F7">
-        <v>4119.505</v>
+        <v>4943.406000000001</v>
       </c>
       <c r="G7">
         <v>1268.4</v>
@@ -1867,28 +1867,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M7">
-        <v>284.8946185186585</v>
+        <v>341.8735422223903</v>
       </c>
       <c r="N7">
-        <v>6366.350279440526</v>
+        <v>6309.371355736795</v>
       </c>
       <c r="O7">
-        <v>1909.905083832158</v>
+        <v>1892.811406721038</v>
       </c>
       <c r="P7">
-        <v>4456.445195608369</v>
+        <v>4416.559949015757</v>
       </c>
       <c r="Q7">
-        <v>12207.44519560837</v>
+        <v>12167.55994901576</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09113522650944816</v>
+        <v>0.09147797041868905</v>
       </c>
       <c r="T7">
-        <v>0.6596827850059225</v>
+        <v>0.6646701265061292</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.34633392706074</v>
+        <v>19.45527827255061</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08889390669889871</v>
+        <v>0.08878883612604584</v>
       </c>
       <c r="C8">
-        <v>74670.44327046453</v>
+        <v>73952.85764357779</v>
       </c>
       <c r="D8">
-        <v>78345.44927046454</v>
+        <v>78451.7646435778</v>
       </c>
       <c r="E8">
-        <v>-33668.79399999999</v>
+        <v>-32844.893</v>
       </c>
       <c r="F8">
-        <v>4943.406</v>
+        <v>5767.307</v>
       </c>
       <c r="G8">
         <v>1268.4</v>
@@ -1949,28 +1949,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M8">
-        <v>341.8735422223903</v>
+        <v>398.852465926122</v>
       </c>
       <c r="N8">
-        <v>6309.371355736795</v>
+        <v>6252.392432033063</v>
       </c>
       <c r="O8">
-        <v>1892.811406721038</v>
+        <v>1875.717729609919</v>
       </c>
       <c r="P8">
-        <v>4416.559949015757</v>
+        <v>4376.674702423144</v>
       </c>
       <c r="Q8">
-        <v>12167.55994901576</v>
+        <v>12127.67470242314</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09147797041868905</v>
+        <v>0.09182808516468779</v>
       </c>
       <c r="T8">
-        <v>0.6646701265061292</v>
+        <v>0.6697647226622545</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.45527827255061</v>
+        <v>16.67595280504338</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08878883612604582</v>
+        <v>0.08868376555319298</v>
       </c>
       <c r="C9">
-        <v>73952.85764357782</v>
+        <v>73235.56095032305</v>
       </c>
       <c r="D9">
-        <v>78451.76464357783</v>
+        <v>78558.36895032306</v>
       </c>
       <c r="E9">
-        <v>-32844.893</v>
+        <v>-32020.992</v>
       </c>
       <c r="F9">
-        <v>5767.307000000001</v>
+        <v>6591.208000000001</v>
       </c>
       <c r="G9">
         <v>1268.4</v>
@@ -2031,28 +2031,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M9">
-        <v>398.852465926122</v>
+        <v>455.8313896298537</v>
       </c>
       <c r="N9">
-        <v>6252.392432033063</v>
+        <v>6195.41350832933</v>
       </c>
       <c r="O9">
-        <v>1875.717729609919</v>
+        <v>1858.624052498799</v>
       </c>
       <c r="P9">
-        <v>4376.674702423144</v>
+        <v>4336.789455830532</v>
       </c>
       <c r="Q9">
-        <v>12127.67470242314</v>
+        <v>12087.78945583053</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09182808516468779</v>
+        <v>0.09218581110081697</v>
       </c>
       <c r="T9">
-        <v>0.6697647226622545</v>
+        <v>0.6749700709087303</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.67595280504338</v>
+        <v>14.59145870441296</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08868376555319298</v>
+        <v>0.08857869498034009</v>
       </c>
       <c r="C10">
-        <v>73235.56095032305</v>
+        <v>72518.55437015682</v>
       </c>
       <c r="D10">
-        <v>78558.36895032306</v>
+        <v>78665.26337015683</v>
       </c>
       <c r="E10">
-        <v>-32020.992</v>
+        <v>-31197.091</v>
       </c>
       <c r="F10">
-        <v>6591.208000000001</v>
+        <v>7415.109</v>
       </c>
       <c r="G10">
         <v>1268.4</v>
@@ -2113,28 +2113,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M10">
-        <v>455.8313896298537</v>
+        <v>512.8103133335854</v>
       </c>
       <c r="N10">
-        <v>6195.41350832933</v>
+        <v>6138.434584625599</v>
       </c>
       <c r="O10">
-        <v>1858.624052498799</v>
+        <v>1841.53037538768</v>
       </c>
       <c r="P10">
-        <v>4336.789455830532</v>
+        <v>4296.90420923792</v>
       </c>
       <c r="Q10">
-        <v>12087.78945583053</v>
+        <v>12047.90420923792</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09218581110081697</v>
+        <v>0.09255139914543248</v>
       </c>
       <c r="T10">
-        <v>0.6749700709087303</v>
+        <v>0.6802898224133703</v>
       </c>
       <c r="U10">
         <v>0.06915748822216712</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.59145870441296</v>
+        <v>12.97018551503374</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08857869498034009</v>
+        <v>0.08847362440748721</v>
       </c>
       <c r="C11">
-        <v>72518.55437015682</v>
+        <v>71801.83908896385</v>
       </c>
       <c r="D11">
-        <v>78665.26337015683</v>
+        <v>78772.44908896385</v>
       </c>
       <c r="E11">
-        <v>-31197.091</v>
+        <v>-30373.19</v>
       </c>
       <c r="F11">
-        <v>7415.109</v>
+        <v>8239.01</v>
       </c>
       <c r="G11">
         <v>1268.4</v>
@@ -2195,28 +2195,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M11">
-        <v>512.8103133335854</v>
+        <v>569.7892370373171</v>
       </c>
       <c r="N11">
-        <v>6138.434584625599</v>
+        <v>6081.455660921867</v>
       </c>
       <c r="O11">
-        <v>1841.53037538768</v>
+        <v>1824.43669827656</v>
       </c>
       <c r="P11">
-        <v>4296.90420923792</v>
+        <v>4257.018962645307</v>
       </c>
       <c r="Q11">
-        <v>12047.90420923792</v>
+        <v>12008.01896264531</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09255139914543248</v>
+        <v>0.09292511136881723</v>
       </c>
       <c r="T11">
-        <v>0.6802898224133703</v>
+        <v>0.6857277906181134</v>
       </c>
       <c r="U11">
         <v>0.06915748822216712</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.97018551503374</v>
+        <v>11.67316696353037</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08847362440748721</v>
+        <v>0.08836855383463435</v>
       </c>
       <c r="C12">
-        <v>71801.83908896385</v>
+        <v>71085.41629910108</v>
       </c>
       <c r="D12">
-        <v>78772.44908896385</v>
+        <v>78879.92729910109</v>
       </c>
       <c r="E12">
-        <v>-30373.19</v>
+        <v>-29549.289</v>
       </c>
       <c r="F12">
-        <v>8239.01</v>
+        <v>9062.911</v>
       </c>
       <c r="G12">
         <v>1268.4</v>
@@ -2277,28 +2277,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M12">
-        <v>569.7892370373171</v>
+        <v>626.7681607410489</v>
       </c>
       <c r="N12">
-        <v>6081.455660921867</v>
+        <v>6024.476737218136</v>
       </c>
       <c r="O12">
-        <v>1824.43669827656</v>
+        <v>1807.343021165441</v>
       </c>
       <c r="P12">
-        <v>4257.018962645307</v>
+        <v>4217.133716052695</v>
       </c>
       <c r="Q12">
-        <v>12008.01896264531</v>
+        <v>11968.1337160527</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09292511136881723</v>
+        <v>0.09330722161969379</v>
       </c>
       <c r="T12">
-        <v>0.6857277906181134</v>
+        <v>0.6912879603555475</v>
       </c>
       <c r="U12">
         <v>0.06915748822216712</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.67316696353037</v>
+        <v>10.61196996684579</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08836855383463435</v>
+        <v>0.08826348326178146</v>
       </c>
       <c r="C13">
-        <v>71085.41629910108</v>
+        <v>70369.2871994419</v>
       </c>
       <c r="D13">
-        <v>78879.92729910109</v>
+        <v>78987.69919944191</v>
       </c>
       <c r="E13">
-        <v>-29549.289</v>
+        <v>-28725.388</v>
       </c>
       <c r="F13">
-        <v>9062.911</v>
+        <v>9886.812</v>
       </c>
       <c r="G13">
         <v>1268.4</v>
@@ -2359,28 +2359,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M13">
-        <v>626.7681607410489</v>
+        <v>683.7470844447805</v>
       </c>
       <c r="N13">
-        <v>6024.476737218136</v>
+        <v>5967.497813514404</v>
       </c>
       <c r="O13">
-        <v>1807.343021165441</v>
+        <v>1790.249344054321</v>
       </c>
       <c r="P13">
-        <v>4217.133716052695</v>
+        <v>4177.248469460083</v>
       </c>
       <c r="Q13">
-        <v>11968.1337160527</v>
+        <v>11928.24846946008</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09330722161969379</v>
+        <v>0.09369801619445389</v>
       </c>
       <c r="T13">
-        <v>0.6912879603555475</v>
+        <v>0.6969744975870141</v>
       </c>
       <c r="U13">
         <v>0.06915748822216712</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.61196996684579</v>
+        <v>9.727639136275307</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08826348326178146</v>
+        <v>0.08815841268892857</v>
       </c>
       <c r="C14">
-        <v>70369.2871994419</v>
+        <v>69653.45299542049</v>
       </c>
       <c r="D14">
-        <v>78987.69919944191</v>
+        <v>79095.7659954205</v>
       </c>
       <c r="E14">
-        <v>-28725.388</v>
+        <v>-27901.48699999999</v>
       </c>
       <c r="F14">
-        <v>9886.812</v>
+        <v>10710.713</v>
       </c>
       <c r="G14">
         <v>1268.4</v>
@@ -2441,28 +2441,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M14">
-        <v>683.7470844447805</v>
+        <v>740.7260081485124</v>
       </c>
       <c r="N14">
-        <v>5967.497813514404</v>
+        <v>5910.518889810672</v>
       </c>
       <c r="O14">
-        <v>1790.249344054321</v>
+        <v>1773.155666943201</v>
       </c>
       <c r="P14">
-        <v>4177.248469460083</v>
+        <v>4137.363222867471</v>
       </c>
       <c r="Q14">
-        <v>11928.24846946008</v>
+        <v>11888.36322286747</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09369801619445389</v>
+        <v>0.0940977945525418</v>
       </c>
       <c r="T14">
-        <v>0.6969744975870141</v>
+        <v>0.7027917598123075</v>
       </c>
       <c r="U14">
         <v>0.06915748822216712</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.727639136275307</v>
+        <v>8.979359202715667</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08815841268892857</v>
+        <v>0.08820034211607569</v>
       </c>
       <c r="C15">
-        <v>69653.45299542049</v>
+        <v>68786.39145946695</v>
       </c>
       <c r="D15">
-        <v>79095.7659954205</v>
+        <v>79052.60545946695</v>
       </c>
       <c r="E15">
-        <v>-27901.48699999999</v>
+        <v>-27077.586</v>
       </c>
       <c r="F15">
-        <v>10710.713</v>
+        <v>11534.614</v>
       </c>
       <c r="G15">
         <v>1268.4</v>
@@ -2523,45 +2523,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M15">
-        <v>740.7260081485124</v>
+        <v>815.0068528522439</v>
       </c>
       <c r="N15">
-        <v>5910.518889810672</v>
+        <v>5836.23804510694</v>
       </c>
       <c r="O15">
-        <v>1773.155666943201</v>
+        <v>1750.871413532082</v>
       </c>
       <c r="P15">
-        <v>4137.363222867471</v>
+        <v>4085.366631574858</v>
       </c>
       <c r="Q15">
-        <v>11888.36322286747</v>
+        <v>11836.36663157486</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0940977945525418</v>
+        <v>0.09450687008174805</v>
       </c>
       <c r="T15">
-        <v>0.7027917598123075</v>
+        <v>0.708744307205631</v>
       </c>
       <c r="U15">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.04841024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.979359202715667</v>
+        <v>8.160968063866104</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08820034211607569</v>
+        <v>0.08810577154322281</v>
       </c>
       <c r="C16">
-        <v>68786.39145946695</v>
+        <v>68059.90453420048</v>
       </c>
       <c r="D16">
-        <v>79052.60545946695</v>
+        <v>79150.01953420049</v>
       </c>
       <c r="E16">
-        <v>-27077.586</v>
+        <v>-26253.68499999999</v>
       </c>
       <c r="F16">
-        <v>11534.614</v>
+        <v>12358.515</v>
       </c>
       <c r="G16">
         <v>1268.4</v>
@@ -2605,28 +2605,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M16">
-        <v>815.0068528522439</v>
+        <v>873.2216280559758</v>
       </c>
       <c r="N16">
-        <v>5836.23804510694</v>
+        <v>5778.023269903209</v>
       </c>
       <c r="O16">
-        <v>1750.871413532082</v>
+        <v>1733.406980970962</v>
       </c>
       <c r="P16">
-        <v>4085.366631574858</v>
+        <v>4044.616288932246</v>
       </c>
       <c r="Q16">
-        <v>11836.36663157486</v>
+        <v>11795.61628893225</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09450687008174805</v>
+        <v>0.09492557091752385</v>
       </c>
       <c r="T16">
-        <v>0.708744307205631</v>
+        <v>0.714836914537621</v>
       </c>
       <c r="U16">
         <v>0.07065748822216711</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.160968063866104</v>
+        <v>7.61690352627503</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08810577154322281</v>
+        <v>0.08801120097036993</v>
       </c>
       <c r="C17">
-        <v>68059.90453420048</v>
+        <v>67333.65798583107</v>
       </c>
       <c r="D17">
-        <v>79150.01953420049</v>
+        <v>79247.67398583108</v>
       </c>
       <c r="E17">
-        <v>-26253.685</v>
+        <v>-25429.784</v>
       </c>
       <c r="F17">
-        <v>12358.515</v>
+        <v>13182.416</v>
       </c>
       <c r="G17">
         <v>1268.4</v>
@@ -2687,28 +2687,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M17">
-        <v>873.2216280559757</v>
+        <v>931.4364032597073</v>
       </c>
       <c r="N17">
-        <v>5778.023269903209</v>
+        <v>5719.808494699477</v>
       </c>
       <c r="O17">
-        <v>1733.406980970962</v>
+        <v>1715.942548409843</v>
       </c>
       <c r="P17">
-        <v>4044.616288932246</v>
+        <v>4003.865946289634</v>
       </c>
       <c r="Q17">
-        <v>11795.61628893225</v>
+        <v>11754.86594628963</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09492557091752385</v>
+        <v>0.09535424082081813</v>
       </c>
       <c r="T17">
-        <v>0.714836914537621</v>
+        <v>0.7210745839489441</v>
       </c>
       <c r="U17">
         <v>0.07065748822216711</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.61690352627503</v>
+        <v>7.140847055882841</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08801120097036993</v>
+        <v>0.08791663039751706</v>
       </c>
       <c r="C18">
-        <v>67333.65798583107</v>
+        <v>66607.65270518119</v>
       </c>
       <c r="D18">
-        <v>79247.67398583108</v>
+        <v>79345.56970518119</v>
       </c>
       <c r="E18">
-        <v>-25429.784</v>
+        <v>-24605.88299999999</v>
       </c>
       <c r="F18">
-        <v>13182.416</v>
+        <v>14006.317</v>
       </c>
       <c r="G18">
         <v>1268.4</v>
@@ -2769,28 +2769,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M18">
-        <v>931.4364032597073</v>
+        <v>989.6511784634391</v>
       </c>
       <c r="N18">
-        <v>5719.808494699477</v>
+        <v>5661.593719495745</v>
       </c>
       <c r="O18">
-        <v>1715.942548409843</v>
+        <v>1698.478115848724</v>
       </c>
       <c r="P18">
-        <v>4003.865946289634</v>
+        <v>3963.115603647022</v>
       </c>
       <c r="Q18">
-        <v>11754.86594628963</v>
+        <v>11714.11560364702</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09535424082081813</v>
+        <v>0.09579324011937251</v>
       </c>
       <c r="T18">
-        <v>0.7210745839489441</v>
+        <v>0.727462558647287</v>
       </c>
       <c r="U18">
         <v>0.07065748822216711</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.140847055882841</v>
+        <v>6.720797229066203</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08791663039751706</v>
+        <v>0.08803625982466418</v>
       </c>
       <c r="C19">
-        <v>66607.65270518119</v>
+        <v>65659.9565218159</v>
       </c>
       <c r="D19">
-        <v>79345.56970518119</v>
+        <v>79221.77452181591</v>
       </c>
       <c r="E19">
-        <v>-24605.88299999999</v>
+        <v>-23781.982</v>
       </c>
       <c r="F19">
-        <v>14006.317</v>
+        <v>14830.218</v>
       </c>
       <c r="G19">
         <v>1268.4</v>
@@ -2851,45 +2851,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M19">
-        <v>989.6511784634391</v>
+        <v>1073.077324267171</v>
       </c>
       <c r="N19">
-        <v>5661.593719495745</v>
+        <v>5578.167573692013</v>
       </c>
       <c r="O19">
-        <v>1698.478115848724</v>
+        <v>1673.450272107604</v>
       </c>
       <c r="P19">
-        <v>3963.115603647022</v>
+        <v>3904.717301584409</v>
       </c>
       <c r="Q19">
-        <v>11714.11560364702</v>
+        <v>11655.71730158441</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09579324011937251</v>
+        <v>0.09624294671789162</v>
       </c>
       <c r="T19">
-        <v>0.727462558647287</v>
+        <v>0.734006337606565</v>
       </c>
       <c r="U19">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.04946024175551697</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.720797229066203</v>
+        <v>6.19829041910048</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08803625982466419</v>
+        <v>0.08795358925181131</v>
       </c>
       <c r="C20">
-        <v>65659.95652181588</v>
+        <v>64921.5635827213</v>
       </c>
       <c r="D20">
-        <v>79221.7745218159</v>
+        <v>79307.28258272131</v>
       </c>
       <c r="E20">
-        <v>-23781.982</v>
+        <v>-22958.081</v>
       </c>
       <c r="F20">
-        <v>14830.218</v>
+        <v>15654.119</v>
       </c>
       <c r="G20">
         <v>1268.4</v>
@@ -2933,28 +2933,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M20">
-        <v>1073.077324267171</v>
+        <v>1132.692731170903</v>
       </c>
       <c r="N20">
-        <v>5578.167573692013</v>
+        <v>5518.552166788282</v>
       </c>
       <c r="O20">
-        <v>1673.450272107604</v>
+        <v>1655.565650036485</v>
       </c>
       <c r="P20">
-        <v>3904.717301584409</v>
+        <v>3862.986516751797</v>
       </c>
       <c r="Q20">
-        <v>11655.71730158441</v>
+        <v>11613.9865167518</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09624294671789162</v>
+        <v>0.09670375718304083</v>
       </c>
       <c r="T20">
-        <v>0.734006337606565</v>
+        <v>0.740711691354961</v>
       </c>
       <c r="U20">
         <v>0.07235748822216712</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.198290419100481</v>
+        <v>5.872064607568876</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08795358925181131</v>
+        <v>0.08787091867895844</v>
       </c>
       <c r="C21">
-        <v>64921.5635827213</v>
+        <v>64183.35542940965</v>
       </c>
       <c r="D21">
-        <v>79307.28258272131</v>
+        <v>79392.97542940966</v>
       </c>
       <c r="E21">
-        <v>-22958.081</v>
+        <v>-22134.18</v>
       </c>
       <c r="F21">
-        <v>15654.119</v>
+        <v>16478.02</v>
       </c>
       <c r="G21">
         <v>1268.4</v>
@@ -3015,28 +3015,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M21">
-        <v>1132.692731170903</v>
+        <v>1192.308138074634</v>
       </c>
       <c r="N21">
-        <v>5518.552166788282</v>
+        <v>5458.93675988455</v>
       </c>
       <c r="O21">
-        <v>1655.565650036485</v>
+        <v>1637.681027965365</v>
       </c>
       <c r="P21">
-        <v>3862.986516751797</v>
+        <v>3821.255731919185</v>
       </c>
       <c r="Q21">
-        <v>11613.9865167518</v>
+        <v>11572.25573191919</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09670375718304083</v>
+        <v>0.0971760879098188</v>
       </c>
       <c r="T21">
-        <v>0.740711691354961</v>
+        <v>0.747584678947067</v>
       </c>
       <c r="U21">
         <v>0.07235748822216712</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.872064607568876</v>
+        <v>5.578461377190433</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08787091867895844</v>
+        <v>0.08790584810610555</v>
       </c>
       <c r="C22">
-        <v>64183.35542940965</v>
+        <v>63323.22546909517</v>
       </c>
       <c r="D22">
-        <v>79392.97542940966</v>
+        <v>79356.74646909517</v>
       </c>
       <c r="E22">
-        <v>-22134.18</v>
+        <v>-21310.27899999999</v>
       </c>
       <c r="F22">
-        <v>16478.02</v>
+        <v>17301.921</v>
       </c>
       <c r="G22">
         <v>1268.4</v>
@@ -3097,45 +3097,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M22">
-        <v>1192.308138074634</v>
+        <v>1265.765081778366</v>
       </c>
       <c r="N22">
-        <v>5458.93675988455</v>
+        <v>5385.479816180818</v>
       </c>
       <c r="O22">
-        <v>1637.681027965365</v>
+        <v>1615.643944854246</v>
       </c>
       <c r="P22">
-        <v>3821.255731919185</v>
+        <v>3769.835871326573</v>
       </c>
       <c r="Q22">
-        <v>11572.25573191919</v>
+        <v>11520.83587132657</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0971760879098188</v>
+        <v>0.09766037637651517</v>
       </c>
       <c r="T22">
-        <v>0.747584678947067</v>
+        <v>0.7546316662250491</v>
       </c>
       <c r="U22">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05065024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.578461377190433</v>
+        <v>5.254723008012169</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08790584810610555</v>
+        <v>0.08782877753325267</v>
       </c>
       <c r="C23">
-        <v>63323.22546909517</v>
+        <v>62579.30647030557</v>
       </c>
       <c r="D23">
-        <v>79356.74646909517</v>
+        <v>79436.72847030558</v>
       </c>
       <c r="E23">
-        <v>-21310.27899999999</v>
+        <v>-20486.378</v>
       </c>
       <c r="F23">
-        <v>17301.921</v>
+        <v>18125.822</v>
       </c>
       <c r="G23">
         <v>1268.4</v>
@@ -3179,28 +3179,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M23">
-        <v>1265.765081778366</v>
+        <v>1326.039609482098</v>
       </c>
       <c r="N23">
-        <v>5385.479816180818</v>
+        <v>5325.205288477087</v>
       </c>
       <c r="O23">
-        <v>1615.643944854246</v>
+        <v>1597.561586543126</v>
       </c>
       <c r="P23">
-        <v>3769.835871326573</v>
+        <v>3727.643701933961</v>
       </c>
       <c r="Q23">
-        <v>11520.83587132657</v>
+        <v>11478.64370193396</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09766037637651517</v>
+        <v>0.09815708249620377</v>
       </c>
       <c r="T23">
-        <v>0.754631666225049</v>
+        <v>0.7618593454845178</v>
       </c>
       <c r="U23">
         <v>0.07315748822216711</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.254723008012169</v>
+        <v>5.015871962193435</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08782877753325267</v>
+        <v>0.08775170696039979</v>
       </c>
       <c r="C24">
-        <v>62579.30647030557</v>
+        <v>61835.5488585393</v>
       </c>
       <c r="D24">
-        <v>79436.72847030558</v>
+        <v>79516.87185853931</v>
       </c>
       <c r="E24">
-        <v>-20486.378</v>
+        <v>-19662.477</v>
       </c>
       <c r="F24">
-        <v>18125.822</v>
+        <v>18949.723</v>
       </c>
       <c r="G24">
         <v>1268.4</v>
@@ -3261,28 +3261,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M24">
-        <v>1326.039609482098</v>
+        <v>1386.314137185829</v>
       </c>
       <c r="N24">
-        <v>5325.205288477087</v>
+        <v>5264.930760773355</v>
       </c>
       <c r="O24">
-        <v>1597.561586543126</v>
+        <v>1579.479228232007</v>
       </c>
       <c r="P24">
-        <v>3727.643701933961</v>
+        <v>3685.451532541349</v>
       </c>
       <c r="Q24">
-        <v>11478.64370193396</v>
+        <v>11436.45153254135</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09815708249620377</v>
+        <v>0.0986666900735466</v>
       </c>
       <c r="T24">
-        <v>0.7618593454845178</v>
+        <v>0.7692747566728039</v>
       </c>
       <c r="U24">
         <v>0.07315748822216711</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.015871962193435</v>
+        <v>4.79779057253285</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08775170696039979</v>
+        <v>0.08767463638754693</v>
       </c>
       <c r="C25">
-        <v>61835.5488585393</v>
+        <v>61091.95312275773</v>
       </c>
       <c r="D25">
-        <v>79516.87185853931</v>
+        <v>79597.17712275774</v>
       </c>
       <c r="E25">
-        <v>-19662.477</v>
+        <v>-18838.57599999999</v>
       </c>
       <c r="F25">
-        <v>18949.723</v>
+        <v>19773.624</v>
       </c>
       <c r="G25">
         <v>1268.4</v>
@@ -3343,28 +3343,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M25">
-        <v>1386.314137185829</v>
+        <v>1446.588664889561</v>
       </c>
       <c r="N25">
-        <v>5264.930760773355</v>
+        <v>5204.656233069623</v>
       </c>
       <c r="O25">
-        <v>1579.479228232007</v>
+        <v>1561.396869920887</v>
       </c>
       <c r="P25">
-        <v>3685.451532541349</v>
+        <v>3643.259363148736</v>
       </c>
       <c r="Q25">
-        <v>11436.45153254135</v>
+        <v>11394.25936314874</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0986666900735466</v>
+        <v>0.09918970837660901</v>
       </c>
       <c r="T25">
-        <v>0.7692747566728039</v>
+        <v>0.7768853102607819</v>
       </c>
       <c r="U25">
         <v>0.07315748822216711</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.79779057253285</v>
+        <v>4.597882632010648</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08767463638754693</v>
+        <v>0.08759756581469404</v>
       </c>
       <c r="C26">
-        <v>61091.95312275774</v>
+        <v>60348.51975389958</v>
       </c>
       <c r="D26">
-        <v>79597.17712275774</v>
+        <v>79677.64475389959</v>
       </c>
       <c r="E26">
-        <v>-18838.576</v>
+        <v>-18014.675</v>
       </c>
       <c r="F26">
-        <v>19773.624</v>
+        <v>20597.525</v>
       </c>
       <c r="G26">
         <v>1268.4</v>
@@ -3425,28 +3425,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M26">
-        <v>1446.588664889561</v>
+        <v>1506.863192593293</v>
       </c>
       <c r="N26">
-        <v>5204.656233069623</v>
+        <v>5144.381705365891</v>
       </c>
       <c r="O26">
-        <v>1561.396869920887</v>
+        <v>1543.314511609767</v>
       </c>
       <c r="P26">
-        <v>3643.259363148736</v>
+        <v>3601.067193756124</v>
       </c>
       <c r="Q26">
-        <v>11394.25936314874</v>
+        <v>11352.06719375612</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09918970837660901</v>
+        <v>0.09972667383441972</v>
       </c>
       <c r="T26">
-        <v>0.7768853102607819</v>
+        <v>0.7846988119444391</v>
       </c>
       <c r="U26">
         <v>0.07315748822216711</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.597882632010649</v>
+        <v>4.413967326730222</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08759756581469404</v>
+        <v>0.08770249524184116</v>
       </c>
       <c r="C27">
-        <v>60348.51975389958</v>
+        <v>59415.10430589892</v>
       </c>
       <c r="D27">
-        <v>79677.64475389959</v>
+        <v>79568.13030589893</v>
       </c>
       <c r="E27">
-        <v>-18014.675</v>
+        <v>-17190.77399999999</v>
       </c>
       <c r="F27">
-        <v>20597.525</v>
+        <v>21421.426</v>
       </c>
       <c r="G27">
         <v>1268.4</v>
@@ -3507,45 +3507,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M27">
-        <v>1506.863192593293</v>
+        <v>1588.559146297025</v>
       </c>
       <c r="N27">
-        <v>5144.381705365891</v>
+        <v>5062.68575166216</v>
       </c>
       <c r="O27">
-        <v>1543.314511609767</v>
+        <v>1518.805725498648</v>
       </c>
       <c r="P27">
-        <v>3601.067193756124</v>
+        <v>3543.880026163512</v>
       </c>
       <c r="Q27">
-        <v>11352.06719375612</v>
+        <v>11294.88002616351</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09972667383441972</v>
+        <v>0.1002781518721713</v>
       </c>
       <c r="T27">
-        <v>0.7846988119444391</v>
+        <v>0.7927234893492763</v>
       </c>
       <c r="U27">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.05121024175551697</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.413967326730222</v>
+        <v>4.186967110077973</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08770249524184116</v>
+        <v>0.08763242466898828</v>
       </c>
       <c r="C28">
-        <v>59415.10430589892</v>
+        <v>58664.30227486466</v>
       </c>
       <c r="D28">
-        <v>79568.13030589893</v>
+        <v>79641.22927486467</v>
       </c>
       <c r="E28">
-        <v>-17190.77399999999</v>
+        <v>-16366.87299999999</v>
       </c>
       <c r="F28">
-        <v>21421.426</v>
+        <v>22245.327</v>
       </c>
       <c r="G28">
         <v>1268.4</v>
@@ -3589,28 +3589,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M28">
-        <v>1588.559146297025</v>
+        <v>1649.657575000756</v>
       </c>
       <c r="N28">
-        <v>5062.68575166216</v>
+        <v>5001.587322958429</v>
       </c>
       <c r="O28">
-        <v>1518.805725498648</v>
+        <v>1500.476196887528</v>
       </c>
       <c r="P28">
-        <v>3543.880026163512</v>
+        <v>3501.1111260709</v>
       </c>
       <c r="Q28">
-        <v>11294.88002616351</v>
+        <v>11252.1111260709</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1002781518721713</v>
+        <v>0.1008447388972585</v>
       </c>
       <c r="T28">
-        <v>0.7927234893492763</v>
+        <v>0.8009680209295886</v>
       </c>
       <c r="U28">
         <v>0.07415748822216711</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.186967110077973</v>
+        <v>4.031894254149159</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08763242466898828</v>
+        <v>0.0875623540961354</v>
       </c>
       <c r="C29">
-        <v>58664.30227486466</v>
+        <v>57913.63467888061</v>
       </c>
       <c r="D29">
-        <v>79641.22927486467</v>
+        <v>79714.46267888062</v>
       </c>
       <c r="E29">
-        <v>-16366.87299999999</v>
+        <v>-15542.97199999999</v>
       </c>
       <c r="F29">
-        <v>22245.327</v>
+        <v>23069.228</v>
       </c>
       <c r="G29">
         <v>1268.4</v>
@@ -3671,28 +3671,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M29">
-        <v>1649.657575000756</v>
+        <v>1710.756003704488</v>
       </c>
       <c r="N29">
-        <v>5001.587322958429</v>
+        <v>4940.488894254697</v>
       </c>
       <c r="O29">
-        <v>1500.476196887528</v>
+        <v>1482.146668276409</v>
       </c>
       <c r="P29">
-        <v>3501.1111260709</v>
+        <v>3458.342225978288</v>
       </c>
       <c r="Q29">
-        <v>11252.1111260709</v>
+        <v>11209.34222597829</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1008447388972585</v>
+        <v>0.1014270644508203</v>
       </c>
       <c r="T29">
-        <v>0.8009680209295886</v>
+        <v>0.8094415672760205</v>
       </c>
       <c r="U29">
         <v>0.07415748822216711</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.031894254149159</v>
+        <v>3.887898030786689</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0875623540961354</v>
+        <v>0.08749228352328252</v>
       </c>
       <c r="C30">
-        <v>57913.63467888061</v>
+        <v>57163.10188914384</v>
       </c>
       <c r="D30">
-        <v>79714.46267888062</v>
+        <v>79787.83088914385</v>
       </c>
       <c r="E30">
-        <v>-15542.97199999999</v>
+        <v>-14719.07099999999</v>
       </c>
       <c r="F30">
-        <v>23069.228</v>
+        <v>23893.129</v>
       </c>
       <c r="G30">
         <v>1268.4</v>
@@ -3753,28 +3753,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M30">
-        <v>1710.756003704488</v>
+        <v>1771.85443240822</v>
       </c>
       <c r="N30">
-        <v>4940.488894254697</v>
+        <v>4879.390465550965</v>
       </c>
       <c r="O30">
-        <v>1482.146668276409</v>
+        <v>1463.817139665289</v>
       </c>
       <c r="P30">
-        <v>3458.342225978288</v>
+        <v>3415.573325885675</v>
       </c>
       <c r="Q30">
-        <v>11209.34222597829</v>
+        <v>11166.57332588567</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1014270644508203</v>
+        <v>0.1020257935411022</v>
       </c>
       <c r="T30">
-        <v>0.8094415672760205</v>
+        <v>0.818153805068831</v>
       </c>
       <c r="U30">
         <v>0.07415748822216711</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.887898030786689</v>
+        <v>3.753832581449217</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08749228352328252</v>
+        <v>0.08742221295042964</v>
       </c>
       <c r="C31">
-        <v>57163.10188914384</v>
+        <v>56412.70427821929</v>
       </c>
       <c r="D31">
-        <v>79787.83088914385</v>
+        <v>79861.33427821929</v>
       </c>
       <c r="E31">
-        <v>-14719.071</v>
+        <v>-13895.16999999999</v>
       </c>
       <c r="F31">
-        <v>23893.129</v>
+        <v>24717.03</v>
       </c>
       <c r="G31">
         <v>1268.4</v>
@@ -3835,28 +3835,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M31">
-        <v>1771.85443240822</v>
+        <v>1832.952861111951</v>
       </c>
       <c r="N31">
-        <v>4879.390465550965</v>
+        <v>4818.292036847233</v>
       </c>
       <c r="O31">
-        <v>1463.817139665289</v>
+        <v>1445.48761105417</v>
       </c>
       <c r="P31">
-        <v>3415.573325885675</v>
+        <v>3372.804425793063</v>
       </c>
       <c r="Q31">
-        <v>11166.57332588567</v>
+        <v>11123.80442579306</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1020257935411022</v>
+        <v>0.1026416291768208</v>
       </c>
       <c r="T31">
-        <v>0.818153805068831</v>
+        <v>0.8271149639414359</v>
       </c>
       <c r="U31">
         <v>0.07415748822216711</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.753832581449217</v>
+        <v>3.628704828734243</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08742221295042964</v>
+        <v>0.08735214237757677</v>
       </c>
       <c r="C32">
-        <v>56412.70427821929</v>
+        <v>55662.44222004604</v>
       </c>
       <c r="D32">
-        <v>79861.33427821929</v>
+        <v>79934.97322004604</v>
       </c>
       <c r="E32">
-        <v>-13895.16999999999</v>
+        <v>-13071.269</v>
       </c>
       <c r="F32">
-        <v>24717.03</v>
+        <v>25540.931</v>
       </c>
       <c r="G32">
         <v>1268.4</v>
@@ -3917,28 +3917,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M32">
-        <v>1832.952861111951</v>
+        <v>1894.051289815683</v>
       </c>
       <c r="N32">
-        <v>4818.292036847233</v>
+        <v>4757.193608143501</v>
       </c>
       <c r="O32">
-        <v>1445.48761105417</v>
+        <v>1427.15808244305</v>
       </c>
       <c r="P32">
-        <v>3372.804425793063</v>
+        <v>3330.035525700451</v>
       </c>
       <c r="Q32">
-        <v>11123.80442579306</v>
+        <v>11081.03552570045</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1026416291768208</v>
+        <v>0.103275315120821</v>
       </c>
       <c r="T32">
-        <v>0.8271149639414359</v>
+        <v>0.8363358665494786</v>
       </c>
       <c r="U32">
         <v>0.07415748822216711</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.628704828734243</v>
+        <v>3.511649834258945</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08735214237757677</v>
+        <v>0.08728207180472389</v>
       </c>
       <c r="C33">
-        <v>55662.44222004604</v>
+        <v>54912.31608994367</v>
       </c>
       <c r="D33">
-        <v>79934.97322004604</v>
+        <v>80008.74808994368</v>
       </c>
       <c r="E33">
-        <v>-13071.269</v>
+        <v>-12247.36799999999</v>
       </c>
       <c r="F33">
-        <v>25540.931</v>
+        <v>26364.832</v>
       </c>
       <c r="G33">
         <v>1268.4</v>
@@ -3999,28 +3999,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M33">
-        <v>1894.051289815683</v>
+        <v>1955.149718519415</v>
       </c>
       <c r="N33">
-        <v>4757.193608143501</v>
+        <v>4696.09517943977</v>
       </c>
       <c r="O33">
-        <v>1427.15808244305</v>
+        <v>1408.828553831931</v>
       </c>
       <c r="P33">
-        <v>3330.035525700451</v>
+        <v>3287.266625607839</v>
       </c>
       <c r="Q33">
-        <v>11081.03552570045</v>
+        <v>11038.26662560784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.103275315120821</v>
+        <v>0.1039276388867036</v>
       </c>
       <c r="T33">
-        <v>0.8363358665494786</v>
+        <v>0.845827972175405</v>
       </c>
       <c r="U33">
         <v>0.07415748822216711</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.511649834258945</v>
+        <v>3.401910776938353</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08728207180472389</v>
+        <v>0.08721200123187101</v>
       </c>
       <c r="C34">
-        <v>54912.31608994367</v>
+        <v>54162.3262646186</v>
       </c>
       <c r="D34">
-        <v>80008.74808994368</v>
+        <v>80082.65926461862</v>
       </c>
       <c r="E34">
-        <v>-12247.36799999999</v>
+        <v>-11423.46699999999</v>
       </c>
       <c r="F34">
-        <v>26364.832</v>
+        <v>27188.733</v>
       </c>
       <c r="G34">
         <v>1268.4</v>
@@ -4081,28 +4081,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M34">
-        <v>1955.149718519415</v>
+        <v>2016.248147223147</v>
       </c>
       <c r="N34">
-        <v>4696.09517943977</v>
+        <v>4634.996750736038</v>
       </c>
       <c r="O34">
-        <v>1408.828553831931</v>
+        <v>1390.499025220811</v>
       </c>
       <c r="P34">
-        <v>3287.266625607839</v>
+        <v>3244.497725515227</v>
       </c>
       <c r="Q34">
-        <v>11038.26662560784</v>
+        <v>10995.49772551523</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1039276388867036</v>
+        <v>0.1045994350038066</v>
       </c>
       <c r="T34">
-        <v>0.845827972175405</v>
+        <v>0.8556034242379262</v>
       </c>
       <c r="U34">
         <v>0.07415748822216711</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.401910776938353</v>
+        <v>3.298822571576585</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08721200123187101</v>
+        <v>0.08714193065901814</v>
       </c>
       <c r="C35">
-        <v>54162.3262646186</v>
+        <v>53412.47312217056</v>
       </c>
       <c r="D35">
-        <v>80082.65926461862</v>
+        <v>80156.70712217057</v>
       </c>
       <c r="E35">
-        <v>-11423.46699999999</v>
+        <v>-10599.56599999999</v>
       </c>
       <c r="F35">
-        <v>27188.733</v>
+        <v>28012.63400000001</v>
       </c>
       <c r="G35">
         <v>1268.4</v>
@@ -4163,28 +4163,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M35">
-        <v>2016.248147223147</v>
+        <v>2077.346575926878</v>
       </c>
       <c r="N35">
-        <v>4634.996750736038</v>
+        <v>4573.898322032306</v>
       </c>
       <c r="O35">
-        <v>1390.499025220811</v>
+        <v>1372.169496609692</v>
       </c>
       <c r="P35">
-        <v>3244.497725515227</v>
+        <v>3201.728825422614</v>
       </c>
       <c r="Q35">
-        <v>10995.49772551523</v>
+        <v>10952.72882542262</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1045994350038066</v>
+        <v>0.1052915885790036</v>
       </c>
       <c r="T35">
-        <v>0.8556034242379262</v>
+        <v>0.8656751021205238</v>
       </c>
       <c r="U35">
         <v>0.07415748822216711</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.298822571576585</v>
+        <v>3.20179837829492</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08714193065901814</v>
+        <v>0.08707186008616524</v>
       </c>
       <c r="C36">
-        <v>53412.47312217056</v>
+        <v>52662.75704209899</v>
       </c>
       <c r="D36">
-        <v>80156.70712217057</v>
+        <v>80230.892042099</v>
       </c>
       <c r="E36">
-        <v>-10599.56599999999</v>
+        <v>-9775.664999999994</v>
       </c>
       <c r="F36">
-        <v>28012.63400000001</v>
+        <v>28836.535</v>
       </c>
       <c r="G36">
         <v>1268.4</v>
@@ -4245,28 +4245,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M36">
-        <v>2077.346575926878</v>
+        <v>2138.44500463061</v>
       </c>
       <c r="N36">
-        <v>4573.898322032306</v>
+        <v>4512.799893328574</v>
       </c>
       <c r="O36">
-        <v>1372.169496609692</v>
+        <v>1353.839967998572</v>
       </c>
       <c r="P36">
-        <v>3201.728825422614</v>
+        <v>3158.959925330002</v>
       </c>
       <c r="Q36">
-        <v>10952.72882542262</v>
+        <v>10909.95992533</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1052915885790036</v>
+        <v>0.1060050391872836</v>
       </c>
       <c r="T36">
-        <v>0.8656751021205238</v>
+        <v>0.8760566777841243</v>
       </c>
       <c r="U36">
         <v>0.07415748822216711</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.20179837829492</v>
+        <v>3.110318424629351</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08707186008616524</v>
+        <v>0.08700178951331237</v>
       </c>
       <c r="C37">
-        <v>52662.75704209899</v>
+        <v>51913.17840530949</v>
       </c>
       <c r="D37">
-        <v>80230.892042099</v>
+        <v>80305.2144053095</v>
       </c>
       <c r="E37">
-        <v>-9775.664999999994</v>
+        <v>-8951.763999999992</v>
       </c>
       <c r="F37">
-        <v>28836.535</v>
+        <v>29660.43600000001</v>
       </c>
       <c r="G37">
         <v>1268.4</v>
@@ -4327,28 +4327,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M37">
-        <v>2138.44500463061</v>
+        <v>2199.543433334342</v>
       </c>
       <c r="N37">
-        <v>4512.799893328574</v>
+        <v>4451.701464624843</v>
       </c>
       <c r="O37">
-        <v>1353.839967998572</v>
+        <v>1335.510439387453</v>
       </c>
       <c r="P37">
-        <v>3158.959925330002</v>
+        <v>3116.19102523739</v>
       </c>
       <c r="Q37">
-        <v>10909.95992533</v>
+        <v>10867.19102523739</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1060050391872836</v>
+        <v>0.1067407851270723</v>
       </c>
       <c r="T37">
-        <v>0.8760566777841243</v>
+        <v>0.8867626776872125</v>
       </c>
       <c r="U37">
         <v>0.07415748822216711</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.110318424629351</v>
+        <v>3.023920690611869</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08700178951331239</v>
+        <v>0.0875792189404595</v>
       </c>
       <c r="C38">
-        <v>51913.17840530947</v>
+        <v>50480.8872884571</v>
       </c>
       <c r="D38">
-        <v>80305.21440530948</v>
+        <v>79696.82428845711</v>
       </c>
       <c r="E38">
-        <v>-8951.763999999996</v>
+        <v>-8127.862999999994</v>
       </c>
       <c r="F38">
-        <v>29660.436</v>
+        <v>30484.337</v>
       </c>
       <c r="G38">
         <v>1268.4</v>
@@ -4409,45 +4409,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M38">
-        <v>2199.543433334341</v>
+        <v>2336.852704538073</v>
       </c>
       <c r="N38">
-        <v>4451.701464624843</v>
+        <v>4314.392193421111</v>
       </c>
       <c r="O38">
-        <v>1335.510439387453</v>
+        <v>1294.317658026333</v>
       </c>
       <c r="P38">
-        <v>3116.19102523739</v>
+        <v>3020.074535394778</v>
       </c>
       <c r="Q38">
-        <v>10867.19102523739</v>
+        <v>10771.07453539478</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1067407851270723</v>
+        <v>0.1074998880808226</v>
       </c>
       <c r="T38">
-        <v>0.8867626776872125</v>
+        <v>0.8978085506030969</v>
       </c>
       <c r="U38">
-        <v>0.07415748822216711</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.05191024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.023920690611869</v>
+        <v>2.846240537558374</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0875792189404595</v>
+        <v>0.08752664836760662</v>
       </c>
       <c r="C39">
-        <v>50480.8872884571</v>
+        <v>49711.9939102288</v>
       </c>
       <c r="D39">
-        <v>79696.82428845711</v>
+        <v>79751.83191022881</v>
       </c>
       <c r="E39">
-        <v>-8127.862999999994</v>
+        <v>-7303.961999999996</v>
       </c>
       <c r="F39">
-        <v>30484.337</v>
+        <v>31308.238</v>
       </c>
       <c r="G39">
         <v>1268.4</v>
@@ -4491,28 +4491,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M39">
-        <v>2336.852704538073</v>
+        <v>2400.010885741805</v>
       </c>
       <c r="N39">
-        <v>4314.392193421111</v>
+        <v>4251.234012217379</v>
       </c>
       <c r="O39">
-        <v>1294.317658026333</v>
+        <v>1275.370203665214</v>
       </c>
       <c r="P39">
-        <v>3020.074535394778</v>
+        <v>2975.863808552165</v>
       </c>
       <c r="Q39">
-        <v>10771.07453539478</v>
+        <v>10726.86380855217</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1074998880808226</v>
+        <v>0.1082834782266293</v>
       </c>
       <c r="T39">
-        <v>0.8978085506030969</v>
+        <v>0.9092107420001391</v>
       </c>
       <c r="U39">
         <v>0.07665748822216711</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.846240537558374</v>
+        <v>2.771339470780521</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08752664836760662</v>
+        <v>0.08747407779475375</v>
       </c>
       <c r="C40">
-        <v>49711.9939102288</v>
+        <v>48943.1765181741</v>
       </c>
       <c r="D40">
-        <v>79751.83191022881</v>
+        <v>79806.91551817411</v>
       </c>
       <c r="E40">
-        <v>-7303.961999999996</v>
+        <v>-6480.060999999994</v>
       </c>
       <c r="F40">
-        <v>31308.238</v>
+        <v>32132.139</v>
       </c>
       <c r="G40">
         <v>1268.4</v>
@@ -4573,28 +4573,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M40">
-        <v>2400.010885741805</v>
+        <v>2463.169066945537</v>
       </c>
       <c r="N40">
-        <v>4251.234012217379</v>
+        <v>4188.075831013648</v>
       </c>
       <c r="O40">
-        <v>1275.370203665214</v>
+        <v>1256.422749304094</v>
       </c>
       <c r="P40">
-        <v>2975.863808552165</v>
+        <v>2931.653081709554</v>
       </c>
       <c r="Q40">
-        <v>10726.86380855217</v>
+        <v>10682.65308170955</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1082834782266293</v>
+        <v>0.1090927598526264</v>
       </c>
       <c r="T40">
-        <v>0.9092107420001391</v>
+        <v>0.9209867757380679</v>
       </c>
       <c r="U40">
         <v>0.07665748822216711</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.771339470780521</v>
+        <v>2.700279484350252</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08747407779475375</v>
+        <v>0.08742150722190087</v>
       </c>
       <c r="C41">
-        <v>48943.1765181741</v>
+        <v>48174.43526984995</v>
       </c>
       <c r="D41">
-        <v>79806.91551817411</v>
+        <v>79862.07526984996</v>
       </c>
       <c r="E41">
-        <v>-6480.060999999994</v>
+        <v>-5656.159999999996</v>
       </c>
       <c r="F41">
-        <v>32132.139</v>
+        <v>32956.04</v>
       </c>
       <c r="G41">
         <v>1268.4</v>
@@ -4655,28 +4655,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M41">
-        <v>2463.169066945537</v>
+        <v>2526.327248149268</v>
       </c>
       <c r="N41">
-        <v>4188.075831013648</v>
+        <v>4124.917649809917</v>
       </c>
       <c r="O41">
-        <v>1256.422749304094</v>
+        <v>1237.475294942975</v>
       </c>
       <c r="P41">
-        <v>2931.653081709554</v>
+        <v>2887.442354866942</v>
       </c>
       <c r="Q41">
-        <v>10682.65308170955</v>
+        <v>10638.44235486694</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1090927598526264</v>
+        <v>0.1099290175328235</v>
       </c>
       <c r="T41">
-        <v>0.9209867757380679</v>
+        <v>0.9331553439339276</v>
       </c>
       <c r="U41">
         <v>0.07665748822216711</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.700279484350252</v>
+        <v>2.632772497241496</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08742150722190087</v>
+        <v>0.08736893664904799</v>
       </c>
       <c r="C42">
-        <v>48174.43526984995</v>
+        <v>47405.77032324919</v>
       </c>
       <c r="D42">
-        <v>79862.07526984996</v>
+        <v>79917.3113232492</v>
       </c>
       <c r="E42">
-        <v>-5656.159999999996</v>
+        <v>-4832.258999999991</v>
       </c>
       <c r="F42">
-        <v>32956.04</v>
+        <v>33779.94100000001</v>
       </c>
       <c r="G42">
         <v>1268.4</v>
@@ -4737,28 +4737,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M42">
-        <v>2526.327248149268</v>
+        <v>2589.485429353001</v>
       </c>
       <c r="N42">
-        <v>4124.917649809917</v>
+        <v>4061.759468606184</v>
       </c>
       <c r="O42">
-        <v>1237.475294942975</v>
+        <v>1218.527840581855</v>
       </c>
       <c r="P42">
-        <v>2887.442354866942</v>
+        <v>2843.231628024329</v>
       </c>
       <c r="Q42">
-        <v>10638.44235486694</v>
+        <v>10594.23162802433</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1099290175328235</v>
+        <v>0.1107936229309933</v>
       </c>
       <c r="T42">
-        <v>0.9331553439339276</v>
+        <v>0.9457364059669351</v>
       </c>
       <c r="U42">
         <v>0.07665748822216711</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.632772497241496</v>
+        <v>2.568558533894142</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08736893664904799</v>
+        <v>0.08731636607619511</v>
       </c>
       <c r="C43">
-        <v>47405.77032324919</v>
+        <v>46637.18183680212</v>
       </c>
       <c r="D43">
-        <v>79917.3113232492</v>
+        <v>79972.62383680213</v>
       </c>
       <c r="E43">
-        <v>-4832.258999999991</v>
+        <v>-4008.357999999993</v>
       </c>
       <c r="F43">
-        <v>33779.94100000001</v>
+        <v>34603.842</v>
       </c>
       <c r="G43">
         <v>1268.4</v>
@@ -4819,28 +4819,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M43">
-        <v>2589.485429353001</v>
+        <v>2652.643610556732</v>
       </c>
       <c r="N43">
-        <v>4061.759468606184</v>
+        <v>3998.601287402453</v>
       </c>
       <c r="O43">
-        <v>1218.527840581855</v>
+        <v>1199.580386220736</v>
       </c>
       <c r="P43">
-        <v>2843.231628024329</v>
+        <v>2799.020901181717</v>
       </c>
       <c r="Q43">
-        <v>10594.23162802433</v>
+        <v>10550.02090118172</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1107936229309933</v>
+        <v>0.1116880423084103</v>
       </c>
       <c r="T43">
-        <v>0.9457364059669351</v>
+        <v>0.9587512977252187</v>
       </c>
       <c r="U43">
         <v>0.07665748822216711</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.568558533894142</v>
+        <v>2.507402378325234</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08731636607619513</v>
+        <v>0.08831729550334223</v>
       </c>
       <c r="C44">
-        <v>46637.1818368021</v>
+        <v>44773.12369995275</v>
       </c>
       <c r="D44">
-        <v>79972.62383680211</v>
+        <v>78932.46669995275</v>
       </c>
       <c r="E44">
-        <v>-4008.357999999993</v>
+        <v>-3184.456999999995</v>
       </c>
       <c r="F44">
-        <v>34603.842</v>
+        <v>35427.743</v>
       </c>
       <c r="G44">
         <v>1268.4</v>
@@ -4901,45 +4901,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M44">
-        <v>2652.643610556732</v>
+        <v>2839.798892260464</v>
       </c>
       <c r="N44">
-        <v>3998.601287402453</v>
+        <v>3811.446005698721</v>
       </c>
       <c r="O44">
-        <v>1199.580386220736</v>
+        <v>1143.433801709616</v>
       </c>
       <c r="P44">
-        <v>2799.020901181717</v>
+        <v>2668.012203989105</v>
       </c>
       <c r="Q44">
-        <v>10550.02090118172</v>
+        <v>10419.0122039891</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1116880423084103</v>
+        <v>0.1126138448218771</v>
       </c>
       <c r="T44">
-        <v>0.9587512977252186</v>
+        <v>0.972222852352214</v>
       </c>
       <c r="U44">
-        <v>0.07665748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05366024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.507402378325234</v>
+        <v>2.342153494068318</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08831729550334223</v>
+        <v>0.08828922493048937</v>
       </c>
       <c r="C45">
-        <v>44773.12369995275</v>
+        <v>43978.02449414352</v>
       </c>
       <c r="D45">
-        <v>78932.46669995275</v>
+        <v>78961.26849414353</v>
       </c>
       <c r="E45">
-        <v>-3184.456999999995</v>
+        <v>-2360.555999999997</v>
       </c>
       <c r="F45">
-        <v>35427.743</v>
+        <v>36251.644</v>
       </c>
       <c r="G45">
         <v>1268.4</v>
@@ -4983,28 +4983,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M45">
-        <v>2839.798892260464</v>
+        <v>2905.840726964195</v>
       </c>
       <c r="N45">
-        <v>3811.446005698721</v>
+        <v>3745.404170994989</v>
       </c>
       <c r="O45">
-        <v>1143.433801709616</v>
+        <v>1123.621251298497</v>
       </c>
       <c r="P45">
-        <v>2668.012203989105</v>
+        <v>2621.782919696493</v>
       </c>
       <c r="Q45">
-        <v>10419.0122039891</v>
+        <v>10372.78291969649</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1126138448218771</v>
+        <v>0.1135727117108248</v>
       </c>
       <c r="T45">
-        <v>0.972222852352214</v>
+        <v>0.9861755339301734</v>
       </c>
       <c r="U45">
         <v>0.08015748822216712</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.342153494068318</v>
+        <v>2.288922732839493</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08828922493048937</v>
+        <v>0.08914315435763646</v>
       </c>
       <c r="C46">
-        <v>43978.02449414352</v>
+        <v>42287.25254114823</v>
       </c>
       <c r="D46">
-        <v>78961.26849414353</v>
+        <v>78094.39754114824</v>
       </c>
       <c r="E46">
-        <v>-2360.555999999997</v>
+        <v>-1536.654999999992</v>
       </c>
       <c r="F46">
-        <v>36251.644</v>
+        <v>37075.54500000001</v>
       </c>
       <c r="G46">
         <v>1268.4</v>
@@ -5065,45 +5065,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M46">
-        <v>2905.840726964195</v>
+        <v>3075.694087667927</v>
       </c>
       <c r="N46">
-        <v>3745.404170994989</v>
+        <v>3575.550810291257</v>
       </c>
       <c r="O46">
-        <v>1123.621251298497</v>
+        <v>1072.665243087377</v>
       </c>
       <c r="P46">
-        <v>2621.782919696493</v>
+        <v>2502.88556720388</v>
       </c>
       <c r="Q46">
-        <v>10372.78291969649</v>
+        <v>10253.88556720388</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1135727117108248</v>
+        <v>0.1145664464866433</v>
       </c>
       <c r="T46">
-        <v>0.9861755339301734</v>
+        <v>1.000635585747331</v>
       </c>
       <c r="U46">
-        <v>0.08015748822216712</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.05611024175551698</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.288922732839493</v>
+        <v>2.162518348176276</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08914315435763646</v>
+        <v>0.08913468378478361</v>
       </c>
       <c r="C47">
-        <v>42287.25254114823</v>
+        <v>41471.85701106626</v>
       </c>
       <c r="D47">
-        <v>78094.39754114824</v>
+        <v>78102.90301106627</v>
       </c>
       <c r="E47">
-        <v>-1536.654999999992</v>
+        <v>-712.7539999999935</v>
       </c>
       <c r="F47">
-        <v>37075.54500000001</v>
+        <v>37899.446</v>
       </c>
       <c r="G47">
         <v>1268.4</v>
@@ -5147,28 +5147,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M47">
-        <v>3075.694087667927</v>
+        <v>3144.042845171659</v>
       </c>
       <c r="N47">
-        <v>3575.550810291257</v>
+        <v>3507.202052787526</v>
       </c>
       <c r="O47">
-        <v>1072.665243087377</v>
+        <v>1052.160615836258</v>
       </c>
       <c r="P47">
-        <v>2502.88556720388</v>
+        <v>2455.041436951268</v>
       </c>
       <c r="Q47">
-        <v>10253.88556720388</v>
+        <v>10206.04143695127</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1145664464866433</v>
+        <v>0.1155969862541589</v>
       </c>
       <c r="T47">
-        <v>1.000635585747331</v>
+        <v>1.015631195039199</v>
       </c>
       <c r="U47">
         <v>0.08295748822216711</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.162518348176276</v>
+        <v>2.115507079737661</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08913468378478361</v>
+        <v>0.08912621321193073</v>
       </c>
       <c r="C48">
-        <v>41471.85701106626</v>
+        <v>40656.46333389312</v>
       </c>
       <c r="D48">
-        <v>78102.90301106627</v>
+        <v>78111.41033389313</v>
       </c>
       <c r="E48">
-        <v>-712.7539999999935</v>
+        <v>111.1470000000045</v>
       </c>
       <c r="F48">
-        <v>37899.446</v>
+        <v>38723.347</v>
       </c>
       <c r="G48">
         <v>1268.4</v>
@@ -5229,28 +5229,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M48">
-        <v>3144.042845171659</v>
+        <v>3212.39160267539</v>
       </c>
       <c r="N48">
-        <v>3507.202052787526</v>
+        <v>3438.853295283794</v>
       </c>
       <c r="O48">
-        <v>1052.160615836258</v>
+        <v>1031.655988585138</v>
       </c>
       <c r="P48">
-        <v>2455.041436951268</v>
+        <v>2407.197306698656</v>
       </c>
       <c r="Q48">
-        <v>10206.04143695127</v>
+        <v>10158.19730669866</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1155969862541589</v>
+        <v>0.1166664143147882</v>
       </c>
       <c r="T48">
-        <v>1.015631195039199</v>
+        <v>1.031192676379816</v>
       </c>
       <c r="U48">
         <v>0.08295748822216711</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.115507079737661</v>
+        <v>2.070496290807073</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08912621321193073</v>
+        <v>0.08911774263907783</v>
       </c>
       <c r="C49">
-        <v>40656.46333389312</v>
+        <v>39841.07151023437</v>
       </c>
       <c r="D49">
-        <v>78111.41033389313</v>
+        <v>78119.91951023438</v>
       </c>
       <c r="E49">
-        <v>111.1470000000045</v>
+        <v>935.0480000000098</v>
       </c>
       <c r="F49">
-        <v>38723.347</v>
+        <v>39547.24800000001</v>
       </c>
       <c r="G49">
         <v>1268.4</v>
@@ -5311,28 +5311,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M49">
-        <v>3212.39160267539</v>
+        <v>3280.740360179122</v>
       </c>
       <c r="N49">
-        <v>3438.853295283794</v>
+        <v>3370.504537780062</v>
       </c>
       <c r="O49">
-        <v>1031.655988585138</v>
+        <v>1011.151361334019</v>
       </c>
       <c r="P49">
-        <v>2407.197306698656</v>
+        <v>2359.353176446044</v>
       </c>
       <c r="Q49">
-        <v>10158.19730669866</v>
+        <v>10110.35317644604</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1166664143147882</v>
+        <v>0.1177769742239032</v>
       </c>
       <c r="T49">
-        <v>1.031192676379816</v>
+        <v>1.047352676233534</v>
       </c>
       <c r="U49">
         <v>0.08295748822216711</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.070496290807073</v>
+        <v>2.027360951415259</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08911774263907783</v>
+        <v>0.09178467206622495</v>
       </c>
       <c r="C50">
-        <v>39841.07151023437</v>
+        <v>36426.64550219761</v>
       </c>
       <c r="D50">
-        <v>78119.91951023438</v>
+        <v>75529.39450219763</v>
       </c>
       <c r="E50">
-        <v>935.0480000000025</v>
+        <v>1758.949000000008</v>
       </c>
       <c r="F50">
-        <v>39547.248</v>
+        <v>40371.149</v>
       </c>
       <c r="G50">
         <v>1268.4</v>
@@ -5393,45 +5393,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M50">
-        <v>3280.740360179122</v>
+        <v>3663.984079882854</v>
       </c>
       <c r="N50">
-        <v>3370.504537780062</v>
+        <v>2987.26081807633</v>
       </c>
       <c r="O50">
-        <v>1011.151361334019</v>
+        <v>896.1782454228991</v>
       </c>
       <c r="P50">
-        <v>2359.353176446044</v>
+        <v>2091.082572653431</v>
       </c>
       <c r="Q50">
-        <v>10110.35317644604</v>
+        <v>9842.082572653431</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1177769742239032</v>
+        <v>0.1189310855020032</v>
       </c>
       <c r="T50">
-        <v>1.047352676233534</v>
+        <v>1.064146401571711</v>
       </c>
       <c r="U50">
-        <v>0.08295748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.05807024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.027360951415259</v>
+        <v>1.815303984118796</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09178467206622495</v>
+        <v>0.09183080149337208</v>
       </c>
       <c r="C51">
-        <v>36426.64550219761</v>
+        <v>35559.44733201037</v>
       </c>
       <c r="D51">
-        <v>75529.39450219763</v>
+        <v>75486.09733201038</v>
       </c>
       <c r="E51">
-        <v>1758.949000000008</v>
+        <v>2582.850000000006</v>
       </c>
       <c r="F51">
-        <v>40371.149</v>
+        <v>41195.05</v>
       </c>
       <c r="G51">
         <v>1268.4</v>
@@ -5475,28 +5475,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M51">
-        <v>3663.984079882854</v>
+        <v>3738.759265186586</v>
       </c>
       <c r="N51">
-        <v>2987.26081807633</v>
+        <v>2912.485632772599</v>
       </c>
       <c r="O51">
-        <v>896.1782454228991</v>
+        <v>873.7456898317796</v>
       </c>
       <c r="P51">
-        <v>2091.082572653431</v>
+        <v>2038.739942940819</v>
       </c>
       <c r="Q51">
-        <v>9842.082572653431</v>
+        <v>9789.73994294082</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1189310855020032</v>
+        <v>0.1201313612312272</v>
       </c>
       <c r="T51">
-        <v>1.064146401571711</v>
+        <v>1.081611875923416</v>
       </c>
       <c r="U51">
         <v>0.09075748822216712</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.815303984118796</v>
+        <v>1.77899790443642</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09183080149337208</v>
+        <v>0.0932692309205192</v>
       </c>
       <c r="C52">
-        <v>35559.44733201037</v>
+        <v>33409.9039129025</v>
       </c>
       <c r="D52">
-        <v>75486.09733201038</v>
+        <v>74160.45491290251</v>
       </c>
       <c r="E52">
-        <v>2582.850000000006</v>
+        <v>3406.751000000004</v>
       </c>
       <c r="F52">
-        <v>41195.05</v>
+        <v>42018.951</v>
       </c>
       <c r="G52">
         <v>1268.4</v>
@@ -5557,45 +5557,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M52">
-        <v>3738.759265186586</v>
+        <v>3977.408359390317</v>
       </c>
       <c r="N52">
-        <v>2912.485632772599</v>
+        <v>2673.836538568867</v>
       </c>
       <c r="O52">
-        <v>873.7456898317796</v>
+        <v>802.1509615706601</v>
       </c>
       <c r="P52">
-        <v>2038.739942940819</v>
+        <v>1871.685576998207</v>
       </c>
       <c r="Q52">
-        <v>9789.73994294082</v>
+        <v>9622.685576998207</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1201313612312272</v>
+        <v>0.1213806278065419</v>
       </c>
       <c r="T52">
-        <v>1.081611875923416</v>
+        <v>1.099790226779272</v>
       </c>
       <c r="U52">
-        <v>0.09075748822216712</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.06353024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.77899790443642</v>
+        <v>1.672255975994059</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0932692309205192</v>
+        <v>0.09334266034766632</v>
       </c>
       <c r="C53">
-        <v>33409.9039129025</v>
+        <v>32519.57903544617</v>
       </c>
       <c r="D53">
-        <v>74160.45491290251</v>
+        <v>74094.03103544618</v>
       </c>
       <c r="E53">
-        <v>3406.751000000004</v>
+        <v>4230.652000000009</v>
       </c>
       <c r="F53">
-        <v>42018.951</v>
+        <v>42842.85200000001</v>
       </c>
       <c r="G53">
         <v>1268.4</v>
@@ -5639,28 +5639,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M53">
-        <v>3977.408359390317</v>
+        <v>4055.39675859405</v>
       </c>
       <c r="N53">
-        <v>2673.836538568867</v>
+        <v>2595.848139365135</v>
       </c>
       <c r="O53">
-        <v>802.1509615706601</v>
+        <v>778.7544418095405</v>
       </c>
       <c r="P53">
-        <v>1871.685576998207</v>
+        <v>1817.093697555595</v>
       </c>
       <c r="Q53">
-        <v>9622.685576998207</v>
+        <v>9568.093697555594</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1213806278065419</v>
+        <v>0.1226819471558281</v>
       </c>
       <c r="T53">
-        <v>1.099790226779272</v>
+        <v>1.118726008920788</v>
       </c>
       <c r="U53">
         <v>0.09465748822216712</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.672255975994059</v>
+        <v>1.640097207224942</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09334266034766632</v>
+        <v>0.09341608977481344</v>
       </c>
       <c r="C54">
-        <v>32519.57903544617</v>
+        <v>31629.37304030224</v>
       </c>
       <c r="D54">
-        <v>74094.03103544618</v>
+        <v>74027.72604030225</v>
       </c>
       <c r="E54">
-        <v>4230.652000000009</v>
+        <v>5054.553000000007</v>
       </c>
       <c r="F54">
-        <v>42842.85200000001</v>
+        <v>43666.753</v>
       </c>
       <c r="G54">
         <v>1268.4</v>
@@ -5721,28 +5721,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M54">
-        <v>4055.39675859405</v>
+        <v>4133.385157797781</v>
       </c>
       <c r="N54">
-        <v>2595.848139365135</v>
+        <v>2517.859740161403</v>
       </c>
       <c r="O54">
-        <v>778.7544418095405</v>
+        <v>755.357922048421</v>
       </c>
       <c r="P54">
-        <v>1817.093697555595</v>
+        <v>1762.501818112982</v>
       </c>
       <c r="Q54">
-        <v>9568.093697555594</v>
+        <v>9513.501818112982</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1226819471558281</v>
+        <v>0.1240386417965733</v>
       </c>
       <c r="T54">
-        <v>1.118726008920788</v>
+        <v>1.138467569025773</v>
       </c>
       <c r="U54">
         <v>0.09465748822216712</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.640097207224942</v>
+        <v>1.609151976899943</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09341608977481344</v>
+        <v>0.09348951920196058</v>
       </c>
       <c r="C55">
-        <v>31629.37304030224</v>
+        <v>30739.28560860113</v>
       </c>
       <c r="D55">
-        <v>74027.72604030225</v>
+        <v>73961.53960860115</v>
       </c>
       <c r="E55">
-        <v>5054.553000000007</v>
+        <v>5878.454000000012</v>
       </c>
       <c r="F55">
-        <v>43666.753</v>
+        <v>44490.65400000001</v>
       </c>
       <c r="G55">
         <v>1268.4</v>
@@ -5803,28 +5803,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M55">
-        <v>4133.385157797781</v>
+        <v>4211.373557001513</v>
       </c>
       <c r="N55">
-        <v>2517.859740161403</v>
+        <v>2439.871340957671</v>
       </c>
       <c r="O55">
-        <v>755.357922048421</v>
+        <v>731.9614022873013</v>
       </c>
       <c r="P55">
-        <v>1762.501818112982</v>
+        <v>1707.90993867037</v>
       </c>
       <c r="Q55">
-        <v>9513.501818112982</v>
+        <v>9458.909938670369</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1240386417965733</v>
+        <v>0.1254543231608291</v>
       </c>
       <c r="T55">
-        <v>1.138467569025773</v>
+        <v>1.159067457830975</v>
       </c>
       <c r="U55">
         <v>0.09465748822216712</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.609151976899943</v>
+        <v>1.579352866216611</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09348951920196058</v>
+        <v>0.09356294862910769</v>
       </c>
       <c r="C56">
-        <v>30739.28560860113</v>
+        <v>29849.31642261271</v>
       </c>
       <c r="D56">
-        <v>73961.53960860115</v>
+        <v>73895.47142261273</v>
       </c>
       <c r="E56">
-        <v>5878.454000000012</v>
+        <v>6702.35500000001</v>
       </c>
       <c r="F56">
-        <v>44490.65400000001</v>
+        <v>45314.55500000001</v>
       </c>
       <c r="G56">
         <v>1268.4</v>
@@ -5885,28 +5885,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M56">
-        <v>4211.373557001513</v>
+        <v>4289.361956205244</v>
       </c>
       <c r="N56">
-        <v>2439.871340957671</v>
+        <v>2361.88294175394</v>
       </c>
       <c r="O56">
-        <v>731.9614022873013</v>
+        <v>708.564882526182</v>
       </c>
       <c r="P56">
-        <v>1707.90993867037</v>
+        <v>1653.318059227758</v>
       </c>
       <c r="Q56">
-        <v>9458.909938670369</v>
+        <v>9404.318059227759</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1254543231608291</v>
+        <v>0.1269329236968297</v>
       </c>
       <c r="T56">
-        <v>1.159067457830975</v>
+        <v>1.180582897249742</v>
       </c>
       <c r="U56">
         <v>0.09465748822216712</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.579352866216611</v>
+        <v>1.550637359558127</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09356294862910769</v>
+        <v>0.09363637805625481</v>
       </c>
       <c r="C57">
-        <v>29849.31642261271</v>
+        <v>28959.46516574097</v>
       </c>
       <c r="D57">
-        <v>73895.47142261273</v>
+        <v>73829.52116574098</v>
       </c>
       <c r="E57">
-        <v>6702.35500000001</v>
+        <v>7526.256000000008</v>
       </c>
       <c r="F57">
-        <v>45314.55500000001</v>
+        <v>46138.45600000001</v>
       </c>
       <c r="G57">
         <v>1268.4</v>
@@ -5967,28 +5967,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M57">
-        <v>4289.361956205244</v>
+        <v>4367.350355408977</v>
       </c>
       <c r="N57">
-        <v>2361.88294175394</v>
+        <v>2283.894542550208</v>
       </c>
       <c r="O57">
-        <v>708.564882526182</v>
+        <v>685.1683627650624</v>
       </c>
       <c r="P57">
-        <v>1653.318059227758</v>
+        <v>1598.726179785146</v>
       </c>
       <c r="Q57">
-        <v>9404.318059227759</v>
+        <v>9349.726179785146</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1269329236968297</v>
+        <v>0.128478733348103</v>
       </c>
       <c r="T57">
-        <v>1.180582897249742</v>
+        <v>1.203076311187543</v>
       </c>
       <c r="U57">
         <v>0.09465748822216712</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.550637359558127</v>
+        <v>1.522947406708875</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09363637805625481</v>
+        <v>0.09937560748340193</v>
       </c>
       <c r="C58">
-        <v>28959.46516574097</v>
+        <v>23321.32791694087</v>
       </c>
       <c r="D58">
-        <v>73829.52116574098</v>
+        <v>69015.28491694089</v>
       </c>
       <c r="E58">
-        <v>7526.256000000008</v>
+        <v>8350.157000000014</v>
       </c>
       <c r="F58">
-        <v>46138.45600000001</v>
+        <v>46962.35700000001</v>
       </c>
       <c r="G58">
         <v>1268.4</v>
@@ -6049,45 +6049,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M58">
-        <v>4367.350355408977</v>
+        <v>5112.204224012708</v>
       </c>
       <c r="N58">
-        <v>2283.894542550208</v>
+        <v>1539.040673946476</v>
       </c>
       <c r="O58">
-        <v>685.1683627650624</v>
+        <v>461.7122021839428</v>
       </c>
       <c r="P58">
-        <v>1598.726179785146</v>
+        <v>1077.328471762533</v>
       </c>
       <c r="Q58">
-        <v>9349.726179785146</v>
+        <v>8828.328471762534</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.128478733348103</v>
+        <v>0.1300964411226913</v>
       </c>
       <c r="T58">
-        <v>1.203076311187543</v>
+        <v>1.226615930424777</v>
       </c>
       <c r="U58">
-        <v>0.09465748822216712</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.06626024175551698</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.522947406708875</v>
+        <v>1.301052267575187</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09937560748340193</v>
+        <v>0.09954843691054906</v>
       </c>
       <c r="C59">
-        <v>23321.32791694087</v>
+        <v>22362.17146639503</v>
       </c>
       <c r="D59">
-        <v>69015.28491694089</v>
+        <v>68880.02946639505</v>
       </c>
       <c r="E59">
-        <v>8350.157000000014</v>
+        <v>9174.058000000012</v>
       </c>
       <c r="F59">
-        <v>46962.35700000001</v>
+        <v>47786.25800000001</v>
       </c>
       <c r="G59">
         <v>1268.4</v>
@@ -6131,28 +6131,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M59">
-        <v>5112.204224012708</v>
+        <v>5201.89201741644</v>
       </c>
       <c r="N59">
-        <v>1539.040673946476</v>
+        <v>1449.352880542744</v>
       </c>
       <c r="O59">
-        <v>461.7122021839428</v>
+        <v>434.8058641628232</v>
       </c>
       <c r="P59">
-        <v>1077.328471762533</v>
+        <v>1014.547016379921</v>
       </c>
       <c r="Q59">
-        <v>8828.328471762534</v>
+        <v>8765.547016379922</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1300964411226913</v>
+        <v>0.1317911826008314</v>
       </c>
       <c r="T59">
-        <v>1.226615930424777</v>
+        <v>1.251276483911403</v>
       </c>
       <c r="U59">
         <v>0.1088574882221671</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.301052267575187</v>
+        <v>1.278620331927339</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09954843691054907</v>
+        <v>0.09972126633769618</v>
       </c>
       <c r="C60">
-        <v>22362.17146639504</v>
+        <v>21403.54412341092</v>
       </c>
       <c r="D60">
-        <v>68880.02946639505</v>
+        <v>68745.30312341092</v>
       </c>
       <c r="E60">
-        <v>9174.058000000005</v>
+        <v>9997.959000000003</v>
       </c>
       <c r="F60">
-        <v>47786.258</v>
+        <v>48610.159</v>
       </c>
       <c r="G60">
         <v>1268.4</v>
@@ -6213,28 +6213,28 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M60">
-        <v>5201.89201741644</v>
+        <v>5291.579810820171</v>
       </c>
       <c r="N60">
-        <v>1449.352880542745</v>
+        <v>1359.665087139014</v>
       </c>
       <c r="O60">
-        <v>434.8058641628235</v>
+        <v>407.8995261417041</v>
       </c>
       <c r="P60">
-        <v>1014.547016379922</v>
+        <v>951.7655609973096</v>
       </c>
       <c r="Q60">
-        <v>8765.547016379922</v>
+        <v>8702.76556099731</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1317911826008314</v>
+        <v>0.1335685943949784</v>
       </c>
       <c r="T60">
-        <v>1.251276483911403</v>
+        <v>1.277139991226645</v>
       </c>
       <c r="U60">
         <v>0.1088574882221671</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.278620331927339</v>
+        <v>1.256948800877723</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09972126633769618</v>
+        <v>0.1125964349327888</v>
       </c>
       <c r="C61">
-        <v>21403.54412341092</v>
+        <v>11836.61020111425</v>
       </c>
       <c r="D61">
-        <v>68745.30312341092</v>
+        <v>60002.27020111425</v>
       </c>
       <c r="E61">
-        <v>9997.959000000003</v>
+        <v>10821.86000000001</v>
       </c>
       <c r="F61">
-        <v>48610.159</v>
+        <v>49434.06</v>
       </c>
       <c r="G61">
         <v>1268.4</v>
@@ -6295,45 +6295,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M61">
-        <v>5291.579810820171</v>
+        <v>6795.081720223904</v>
       </c>
       <c r="N61">
-        <v>1359.665087139014</v>
+        <v>-143.8368222647196</v>
       </c>
       <c r="O61">
-        <v>407.8995261417041</v>
+        <v>-43.15104667941586</v>
       </c>
       <c r="P61">
-        <v>951.7655609973096</v>
+        <v>-100.6857755853037</v>
       </c>
       <c r="Q61">
-        <v>8702.76556099731</v>
+        <v>7650.314224414697</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1335685943949784</v>
+        <v>0.135851373008402</v>
       </c>
       <c r="T61">
-        <v>1.277139991226645</v>
+        <v>1.310357201533102</v>
       </c>
       <c r="U61">
-        <v>0.1088574882221671</v>
+        <v>0.1374574882221671</v>
       </c>
       <c r="V61">
-        <v>0.3</v>
+        <v>0.2936496647934362</v>
       </c>
       <c r="W61">
-        <v>0.07620024175551698</v>
+        <v>0.09709314288238005</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.256948800877723</v>
+        <v>0.9788322159781208</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1125964349327888</v>
+        <v>0.1135130098150105</v>
       </c>
       <c r="C62">
-        <v>11836.61020111425</v>
+        <v>10474.33103256379</v>
       </c>
       <c r="D62">
-        <v>60002.27020111425</v>
+        <v>59463.8920325638</v>
       </c>
       <c r="E62">
-        <v>10821.86000000001</v>
+        <v>11645.76100000001</v>
       </c>
       <c r="F62">
-        <v>49434.06</v>
+        <v>50257.961</v>
       </c>
       <c r="G62">
         <v>1268.4</v>
@@ -6377,37 +6377,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M62">
-        <v>6795.081720223904</v>
+        <v>6908.333082227636</v>
       </c>
       <c r="N62">
-        <v>-143.8368222647196</v>
+        <v>-257.0881842684512</v>
       </c>
       <c r="O62">
-        <v>-43.15104667941586</v>
+        <v>-77.12645528053535</v>
       </c>
       <c r="P62">
-        <v>-100.6857755853037</v>
+        <v>-179.9617289879158</v>
       </c>
       <c r="Q62">
-        <v>7650.314224414697</v>
+        <v>7571.038271012084</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.135851373008402</v>
+        <v>0.13816038257272</v>
       </c>
       <c r="T62">
-        <v>1.310357201533102</v>
+        <v>1.343956104136515</v>
       </c>
       <c r="U62">
         <v>0.1374574882221671</v>
       </c>
       <c r="V62">
-        <v>0.2936496647934362</v>
+        <v>0.2888357358623962</v>
       </c>
       <c r="W62">
-        <v>0.09709314288238005</v>
+        <v>0.09775485346172082</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9788322159781208</v>
+        <v>0.9627857862079876</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1135130098150105</v>
+        <v>0.1144295846972322</v>
       </c>
       <c r="C63">
-        <v>10474.33103256379</v>
+        <v>9121.627283510039</v>
       </c>
       <c r="D63">
-        <v>59463.8920325638</v>
+        <v>58935.08928351004</v>
       </c>
       <c r="E63">
-        <v>11645.76100000001</v>
+        <v>12469.662</v>
       </c>
       <c r="F63">
-        <v>50257.961</v>
+        <v>51081.862</v>
       </c>
       <c r="G63">
         <v>1268.4</v>
@@ -6459,37 +6459,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M63">
-        <v>6908.333082227636</v>
+        <v>7021.584444231367</v>
       </c>
       <c r="N63">
-        <v>-257.0881842684512</v>
+        <v>-370.3395462721828</v>
       </c>
       <c r="O63">
-        <v>-77.12645528053535</v>
+        <v>-111.1018638816548</v>
       </c>
       <c r="P63">
-        <v>-179.9617289879158</v>
+        <v>-259.237682390528</v>
       </c>
       <c r="Q63">
-        <v>7571.038271012084</v>
+        <v>7491.762317609472</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.13816038257272</v>
+        <v>0.1405909189562127</v>
       </c>
       <c r="T63">
-        <v>1.343956104136515</v>
+        <v>1.379323370034845</v>
       </c>
       <c r="U63">
         <v>0.1374574882221671</v>
       </c>
       <c r="V63">
-        <v>0.2888357358623962</v>
+        <v>0.2841770949613899</v>
       </c>
       <c r="W63">
-        <v>0.09775485346172082</v>
+        <v>0.09839521853850221</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9627857862079876</v>
+        <v>0.947256983204633</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1144295846972322</v>
+        <v>0.1153461595794538</v>
       </c>
       <c r="C64">
-        <v>9121.627283510039</v>
+        <v>7778.245747716588</v>
       </c>
       <c r="D64">
-        <v>58935.08928351004</v>
+        <v>58415.60874771659</v>
       </c>
       <c r="E64">
-        <v>12469.662</v>
+        <v>13293.56300000001</v>
       </c>
       <c r="F64">
-        <v>51081.862</v>
+        <v>51905.76300000001</v>
       </c>
       <c r="G64">
         <v>1268.4</v>
@@ -6541,37 +6541,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M64">
-        <v>7021.584444231367</v>
+        <v>7134.8358062351</v>
       </c>
       <c r="N64">
-        <v>-370.3395462721828</v>
+        <v>-483.5909082759154</v>
       </c>
       <c r="O64">
-        <v>-111.1018638816548</v>
+        <v>-145.0772724827746</v>
       </c>
       <c r="P64">
-        <v>-259.237682390528</v>
+        <v>-338.5136357931408</v>
       </c>
       <c r="Q64">
-        <v>7491.762317609472</v>
+        <v>7412.486364206859</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1405909189562127</v>
+        <v>0.143152835684759</v>
       </c>
       <c r="T64">
-        <v>1.379323370034845</v>
+        <v>1.416602380035786</v>
       </c>
       <c r="U64">
         <v>0.1374574882221671</v>
       </c>
       <c r="V64">
-        <v>0.2841770949613899</v>
+        <v>0.2796663474223202</v>
       </c>
       <c r="W64">
-        <v>0.09839521853850221</v>
+        <v>0.09901525456522706</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.947256983204633</v>
+        <v>0.9322211580744006</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1153461595794538</v>
+        <v>0.1162627344616755</v>
       </c>
       <c r="C65">
-        <v>7778.245747716588</v>
+        <v>6443.942068440752</v>
       </c>
       <c r="D65">
-        <v>58415.60874771659</v>
+        <v>57905.20606844076</v>
       </c>
       <c r="E65">
-        <v>13293.56300000001</v>
+        <v>14117.46400000001</v>
       </c>
       <c r="F65">
-        <v>51905.76300000001</v>
+        <v>52729.664</v>
       </c>
       <c r="G65">
         <v>1268.4</v>
@@ -6623,37 +6623,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M65">
-        <v>7134.8358062351</v>
+        <v>7248.087168238831</v>
       </c>
       <c r="N65">
-        <v>-483.5909082759154</v>
+        <v>-596.8422702796461</v>
       </c>
       <c r="O65">
-        <v>-145.0772724827746</v>
+        <v>-179.0526810838938</v>
       </c>
       <c r="P65">
-        <v>-338.5136357931408</v>
+        <v>-417.7895891957522</v>
       </c>
       <c r="Q65">
-        <v>7412.486364206859</v>
+        <v>7333.210410804248</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.143152835684759</v>
+        <v>0.1458570811204467</v>
       </c>
       <c r="T65">
-        <v>1.416602380035786</v>
+        <v>1.455952446147891</v>
       </c>
       <c r="U65">
         <v>0.1374574882221671</v>
       </c>
       <c r="V65">
-        <v>0.2796663474223202</v>
+        <v>0.2752965607438465</v>
       </c>
       <c r="W65">
-        <v>0.09901525456522706</v>
+        <v>0.09961591446611674</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9322211580744006</v>
+        <v>0.9176552024794882</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1162627344616755</v>
+        <v>0.1171793093438972</v>
       </c>
       <c r="C66">
-        <v>6443.942068440752</v>
+        <v>5118.480355172913</v>
       </c>
       <c r="D66">
-        <v>57905.20606844076</v>
+        <v>57403.64535517291</v>
       </c>
       <c r="E66">
-        <v>14117.46400000001</v>
+        <v>14941.36500000001</v>
       </c>
       <c r="F66">
-        <v>52729.664</v>
+        <v>53553.565</v>
       </c>
       <c r="G66">
         <v>1268.4</v>
@@ -6705,37 +6705,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M66">
-        <v>7248.087168238831</v>
+        <v>7361.338530242562</v>
       </c>
       <c r="N66">
-        <v>-596.8422702796461</v>
+        <v>-710.0936322833777</v>
       </c>
       <c r="O66">
-        <v>-179.0526810838938</v>
+        <v>-213.0280896850133</v>
       </c>
       <c r="P66">
-        <v>-417.7895891957522</v>
+        <v>-497.0655425983644</v>
       </c>
       <c r="Q66">
-        <v>7333.210410804248</v>
+        <v>7253.934457401636</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1458570811204467</v>
+        <v>0.1487158548667452</v>
       </c>
       <c r="T66">
-        <v>1.455952446147891</v>
+        <v>1.497551087466403</v>
       </c>
       <c r="U66">
         <v>0.1374574882221671</v>
       </c>
       <c r="V66">
-        <v>0.2752965607438465</v>
+        <v>0.271061229040095</v>
       </c>
       <c r="W66">
-        <v>0.09961591446611674</v>
+        <v>0.1001980925239021</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9176552024794882</v>
+        <v>0.90353743013365</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1171793093438972</v>
+        <v>0.1180958842261189</v>
       </c>
       <c r="C67">
-        <v>5118.480355172913</v>
+        <v>3801.632820122941</v>
       </c>
       <c r="D67">
-        <v>57403.64535517291</v>
+        <v>56910.69882012295</v>
       </c>
       <c r="E67">
-        <v>14941.36500000001</v>
+        <v>15765.26600000001</v>
       </c>
       <c r="F67">
-        <v>53553.565</v>
+        <v>54377.46600000001</v>
       </c>
       <c r="G67">
         <v>1268.4</v>
@@ -6787,37 +6787,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M67">
-        <v>7361.338530242562</v>
+        <v>7474.589892246295</v>
       </c>
       <c r="N67">
-        <v>-710.0936322833777</v>
+        <v>-823.3449942871102</v>
       </c>
       <c r="O67">
-        <v>-213.0280896850133</v>
+        <v>-247.0034982861331</v>
       </c>
       <c r="P67">
-        <v>-497.0655425983644</v>
+        <v>-576.3414960009771</v>
       </c>
       <c r="Q67">
-        <v>7253.934457401636</v>
+        <v>7174.658503999023</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1487158548667452</v>
+        <v>0.1517427917745906</v>
       </c>
       <c r="T67">
-        <v>1.497551087466403</v>
+        <v>1.541596707686003</v>
       </c>
       <c r="U67">
         <v>0.1374574882221671</v>
       </c>
       <c r="V67">
-        <v>0.271061229040095</v>
+        <v>0.2669542407213056</v>
       </c>
       <c r="W67">
-        <v>0.1001980925239021</v>
+        <v>0.1007626288223607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.90353743013365</v>
+        <v>0.8898474690710187</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1180958842261189</v>
+        <v>0.1190124591083405</v>
       </c>
       <c r="C68">
-        <v>3801.632820122941</v>
+        <v>2493.179433277022</v>
       </c>
       <c r="D68">
-        <v>56910.69882012295</v>
+        <v>56426.14643327703</v>
       </c>
       <c r="E68">
-        <v>15765.26600000001</v>
+        <v>16589.16700000001</v>
       </c>
       <c r="F68">
-        <v>54377.46600000001</v>
+        <v>55201.36700000001</v>
       </c>
       <c r="G68">
         <v>1268.4</v>
@@ -6869,37 +6869,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M68">
-        <v>7474.589892246295</v>
+        <v>7587.841254250026</v>
       </c>
       <c r="N68">
-        <v>-823.3449942871102</v>
+        <v>-936.5963562908419</v>
       </c>
       <c r="O68">
-        <v>-247.0034982861331</v>
+        <v>-280.9789068872525</v>
       </c>
       <c r="P68">
-        <v>-576.3414960009771</v>
+        <v>-655.6174494035893</v>
       </c>
       <c r="Q68">
-        <v>7174.658503999023</v>
+        <v>7095.382550596411</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1517427917745906</v>
+        <v>0.1549531794041237</v>
       </c>
       <c r="T68">
-        <v>1.541596707686003</v>
+        <v>1.588311759434064</v>
       </c>
       <c r="U68">
         <v>0.1374574882221671</v>
       </c>
       <c r="V68">
-        <v>0.2669542407213056</v>
+        <v>0.2629698490687488</v>
       </c>
       <c r="W68">
-        <v>0.1007626288223607</v>
+        <v>0.1013103132910145</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8898474690710187</v>
+        <v>0.8765661635624962</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1190124591083405</v>
+        <v>0.1199290339905622</v>
       </c>
       <c r="C69">
-        <v>2493.179433277022</v>
+        <v>1192.907594927194</v>
       </c>
       <c r="D69">
-        <v>56426.14643327703</v>
+        <v>55949.7755949272</v>
       </c>
       <c r="E69">
-        <v>16589.16700000001</v>
+        <v>17413.06800000001</v>
       </c>
       <c r="F69">
-        <v>55201.36700000001</v>
+        <v>56025.26800000001</v>
       </c>
       <c r="G69">
         <v>1268.4</v>
@@ -6951,37 +6951,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M69">
-        <v>7587.841254250026</v>
+        <v>7701.092616253759</v>
       </c>
       <c r="N69">
-        <v>-936.5963562908419</v>
+        <v>-1049.847718294574</v>
       </c>
       <c r="O69">
-        <v>-280.9789068872525</v>
+        <v>-314.9543154883723</v>
       </c>
       <c r="P69">
-        <v>-655.6174494035893</v>
+        <v>-734.8934028062022</v>
       </c>
       <c r="Q69">
-        <v>7095.382550596411</v>
+        <v>7016.106597193798</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1549531794041237</v>
+        <v>0.1583642162605025</v>
       </c>
       <c r="T69">
-        <v>1.588311759434064</v>
+        <v>1.637946501916378</v>
       </c>
       <c r="U69">
         <v>0.1374574882221671</v>
       </c>
       <c r="V69">
-        <v>0.2629698490687488</v>
+        <v>0.2591026454059731</v>
       </c>
       <c r="W69">
-        <v>0.1013103132910145</v>
+        <v>0.1018418893929433</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8765661635624962</v>
+        <v>0.863675484686577</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1199290339905622</v>
+        <v>0.1208456088727839</v>
       </c>
       <c r="C70">
-        <v>1192.907594927194</v>
+        <v>-99.38817535003182</v>
       </c>
       <c r="D70">
-        <v>55949.7755949272</v>
+        <v>55481.38082464998</v>
       </c>
       <c r="E70">
-        <v>17413.06800000001</v>
+        <v>18236.96900000001</v>
       </c>
       <c r="F70">
-        <v>56025.26800000001</v>
+        <v>56849.16900000001</v>
       </c>
       <c r="G70">
         <v>1268.4</v>
@@ -7033,37 +7033,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M70">
-        <v>7701.092616253759</v>
+        <v>7814.343978257491</v>
       </c>
       <c r="N70">
-        <v>-1049.847718294574</v>
+        <v>-1163.099080298306</v>
       </c>
       <c r="O70">
-        <v>-314.9543154883723</v>
+        <v>-348.9297240894918</v>
       </c>
       <c r="P70">
-        <v>-734.8934028062022</v>
+        <v>-814.1693562088142</v>
       </c>
       <c r="Q70">
-        <v>7016.106597193798</v>
+        <v>6936.830643791186</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1583642162605025</v>
+        <v>0.1619953200108414</v>
       </c>
       <c r="T70">
-        <v>1.637946501916378</v>
+        <v>1.690783485849165</v>
       </c>
       <c r="U70">
         <v>0.1374574882221671</v>
       </c>
       <c r="V70">
-        <v>0.2591026454059731</v>
+        <v>0.255347534602988</v>
       </c>
       <c r="W70">
-        <v>0.1018418893929433</v>
+        <v>0.1023580574919175</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.863675484686577</v>
+        <v>0.8511584486766266</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1208456088727839</v>
+        <v>0.1217621837550056</v>
       </c>
       <c r="C71">
-        <v>-99.38817535003182</v>
+        <v>-1383.906534222282</v>
       </c>
       <c r="D71">
-        <v>55481.38082464998</v>
+        <v>55020.76346577772</v>
       </c>
       <c r="E71">
-        <v>18236.96900000001</v>
+        <v>19060.87000000001</v>
       </c>
       <c r="F71">
-        <v>56849.16900000001</v>
+        <v>57673.07000000001</v>
       </c>
       <c r="G71">
         <v>1268.4</v>
@@ -7115,37 +7115,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M71">
-        <v>7814.343978257491</v>
+        <v>7927.595340261221</v>
       </c>
       <c r="N71">
-        <v>-1163.099080298306</v>
+        <v>-1276.350442302037</v>
       </c>
       <c r="O71">
-        <v>-348.9297240894918</v>
+        <v>-382.905132690611</v>
       </c>
       <c r="P71">
-        <v>-814.1693562088142</v>
+        <v>-893.4453096114257</v>
       </c>
       <c r="Q71">
-        <v>6936.830643791186</v>
+        <v>6857.554690388574</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1619953200108414</v>
+        <v>0.1658684973445361</v>
       </c>
       <c r="T71">
-        <v>1.690783485849165</v>
+        <v>1.74714293537747</v>
       </c>
       <c r="U71">
         <v>0.1374574882221671</v>
       </c>
       <c r="V71">
-        <v>0.255347534602988</v>
+        <v>0.2516997126800882</v>
       </c>
       <c r="W71">
-        <v>0.1023580574919175</v>
+        <v>0.1028594779309211</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8511584486766266</v>
+        <v>0.8389990422669606</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1217621837550056</v>
+        <v>0.1226787586372272</v>
       </c>
       <c r="C72">
-        <v>-1383.906534222282</v>
+        <v>-2660.839595529782</v>
       </c>
       <c r="D72">
-        <v>55020.76346577772</v>
+        <v>54567.73140447023</v>
       </c>
       <c r="E72">
-        <v>19060.87000000001</v>
+        <v>19884.77100000002</v>
       </c>
       <c r="F72">
-        <v>57673.07000000001</v>
+        <v>58496.97100000001</v>
       </c>
       <c r="G72">
         <v>1268.4</v>
@@ -7197,37 +7197,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M72">
-        <v>7927.595340261221</v>
+        <v>8040.846702264954</v>
       </c>
       <c r="N72">
-        <v>-1276.350442302037</v>
+        <v>-1389.601804305769</v>
       </c>
       <c r="O72">
-        <v>-382.905132690611</v>
+        <v>-416.8805412917308</v>
       </c>
       <c r="P72">
-        <v>-893.4453096114257</v>
+        <v>-972.7212630140385</v>
       </c>
       <c r="Q72">
-        <v>6857.554690388574</v>
+        <v>6778.278736985962</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1658684973445361</v>
+        <v>0.1700087903564166</v>
       </c>
       <c r="T72">
-        <v>1.74714293537747</v>
+        <v>1.807389243493935</v>
       </c>
       <c r="U72">
         <v>0.1374574882221671</v>
       </c>
       <c r="V72">
-        <v>0.2516997126800882</v>
+        <v>0.2481546463043123</v>
       </c>
       <c r="W72">
-        <v>0.1028594779309211</v>
+        <v>0.1033467738505161</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8389990422669606</v>
+        <v>0.8271821543477076</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1226787586372272</v>
+        <v>0.1235953335194489</v>
       </c>
       <c r="C73">
-        <v>-2660.839595529767</v>
+        <v>-3930.373197448469</v>
       </c>
       <c r="D73">
-        <v>54567.73140447023</v>
+        <v>54122.09880255153</v>
       </c>
       <c r="E73">
-        <v>19884.771</v>
+        <v>20708.67200000001</v>
       </c>
       <c r="F73">
-        <v>58496.971</v>
+        <v>59320.872</v>
       </c>
       <c r="G73">
         <v>1268.4</v>
@@ -7279,37 +7279,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M73">
-        <v>8040.846702264952</v>
+        <v>8154.098064268685</v>
       </c>
       <c r="N73">
-        <v>-1389.601804305767</v>
+        <v>-1502.8531663095</v>
       </c>
       <c r="O73">
-        <v>-416.8805412917303</v>
+        <v>-450.85594989285</v>
       </c>
       <c r="P73">
-        <v>-972.7212630140373</v>
+        <v>-1051.99721641665</v>
       </c>
       <c r="Q73">
-        <v>6778.278736985962</v>
+        <v>6699.00278358335</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1700087903564166</v>
+        <v>0.1744448185834315</v>
       </c>
       <c r="T73">
-        <v>1.807389243493934</v>
+        <v>1.871938859333003</v>
       </c>
       <c r="U73">
         <v>0.1374574882221671</v>
       </c>
       <c r="V73">
-        <v>0.2481546463043123</v>
+        <v>0.2447080539945302</v>
       </c>
       <c r="W73">
-        <v>0.1033467738505161</v>
+        <v>0.1038205337723446</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8271821543477078</v>
+        <v>0.8156935133151006</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1235953335194489</v>
+        <v>0.1245119084016706</v>
       </c>
       <c r="C74">
-        <v>-3930.373197448469</v>
+        <v>-5192.687156668362</v>
       </c>
       <c r="D74">
-        <v>54122.09880255153</v>
+        <v>53683.68584333164</v>
       </c>
       <c r="E74">
-        <v>20708.67200000001</v>
+        <v>21532.573</v>
       </c>
       <c r="F74">
-        <v>59320.872</v>
+        <v>60144.773</v>
       </c>
       <c r="G74">
         <v>1268.4</v>
@@ -7361,37 +7361,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M74">
-        <v>8154.098064268685</v>
+        <v>8267.349426272416</v>
       </c>
       <c r="N74">
-        <v>-1502.8531663095</v>
+        <v>-1616.104528313232</v>
       </c>
       <c r="O74">
-        <v>-450.85594989285</v>
+        <v>-484.8313584939694</v>
       </c>
       <c r="P74">
-        <v>-1051.99721641665</v>
+        <v>-1131.273169819262</v>
       </c>
       <c r="Q74">
-        <v>6699.00278358335</v>
+        <v>6619.726830180738</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1744448185834315</v>
+        <v>0.1792094414939289</v>
       </c>
       <c r="T74">
-        <v>1.871938859333003</v>
+        <v>1.941269928197188</v>
       </c>
       <c r="U74">
         <v>0.1374574882221671</v>
       </c>
       <c r="V74">
-        <v>0.2447080539945302</v>
+        <v>0.2413558888713174</v>
       </c>
       <c r="W74">
-        <v>0.1038205337723446</v>
+        <v>0.1042813139702873</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8156935133151006</v>
+        <v>0.8045196295710582</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1245119084016706</v>
+        <v>0.1476079037613627</v>
       </c>
       <c r="C75">
-        <v>-5192.687156668362</v>
+        <v>-15116.79807155282</v>
       </c>
       <c r="D75">
-        <v>53683.68584333164</v>
+        <v>44583.47592844719</v>
       </c>
       <c r="E75">
-        <v>21532.573</v>
+        <v>22356.47400000001</v>
       </c>
       <c r="F75">
-        <v>60144.773</v>
+        <v>60968.67400000001</v>
       </c>
       <c r="G75">
         <v>1268.4</v>
@@ -7443,45 +7443,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M75">
-        <v>8267.349426272416</v>
+        <v>10099.91739507615</v>
       </c>
       <c r="N75">
-        <v>-1616.104528313232</v>
+        <v>-3448.672497116964</v>
       </c>
       <c r="O75">
-        <v>-484.8313584939694</v>
+        <v>-1034.601749135089</v>
       </c>
       <c r="P75">
-        <v>-1131.273169819262</v>
+        <v>-2414.070747981875</v>
       </c>
       <c r="Q75">
-        <v>6619.726830180738</v>
+        <v>5336.929252018125</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1792094414939289</v>
+        <v>0.1893844987724281</v>
       </c>
       <c r="T75">
-        <v>1.941269928197188</v>
+        <v>2.089329409529574</v>
       </c>
       <c r="U75">
-        <v>0.1374574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V75">
-        <v>0.2413558888713174</v>
+        <v>0.1975633454547389</v>
       </c>
       <c r="W75">
-        <v>0.1042813139702873</v>
+        <v>0.1329296406493668</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8045196295710582</v>
+        <v>0.6585444848491295</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1476079037613627</v>
+        <v>0.1908779591670749</v>
       </c>
       <c r="C76">
-        <v>-15116.79807155282</v>
+        <v>-26686.90518644346</v>
       </c>
       <c r="D76">
-        <v>44583.47592844719</v>
+        <v>33837.26981355654</v>
       </c>
       <c r="E76">
-        <v>22356.47400000001</v>
+        <v>23180.37500000001</v>
       </c>
       <c r="F76">
-        <v>60968.67400000001</v>
+        <v>61792.575</v>
       </c>
       <c r="G76">
         <v>1268.4</v>
@@ -7525,45 +7525,45 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M76">
-        <v>10099.91739507615</v>
+        <v>13573.20181527988</v>
       </c>
       <c r="N76">
-        <v>-3448.672497116964</v>
+        <v>-6921.956917320695</v>
       </c>
       <c r="O76">
-        <v>-1034.601749135089</v>
+        <v>-2076.587075196208</v>
       </c>
       <c r="P76">
-        <v>-2414.070747981875</v>
+        <v>-4845.369842124486</v>
       </c>
       <c r="Q76">
-        <v>5336.929252018125</v>
+        <v>2905.630157875514</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1893844987724281</v>
+        <v>0.2014138008172871</v>
       </c>
       <c r="T76">
-        <v>2.089329409529574</v>
+        <v>2.264370411541027</v>
       </c>
       <c r="U76">
-        <v>0.1656574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V76">
-        <v>0.1975633454547389</v>
+        <v>0.14700831068035</v>
       </c>
       <c r="W76">
-        <v>0.1329296406493668</v>
+        <v>0.1873660119503374</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.6585444848491295</v>
+        <v>0.4900277022678334</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1908779591670749</v>
+        <v>0.1926165340492965</v>
       </c>
       <c r="C77">
-        <v>-26686.90518644346</v>
+        <v>-27835.36747588204</v>
       </c>
       <c r="D77">
-        <v>33837.26981355654</v>
+        <v>33512.70852411796</v>
       </c>
       <c r="E77">
-        <v>23180.37500000001</v>
+        <v>24004.27600000001</v>
       </c>
       <c r="F77">
-        <v>61792.575</v>
+        <v>62616.476</v>
       </c>
       <c r="G77">
         <v>1268.4</v>
@@ -7607,37 +7607,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M77">
-        <v>13573.20181527988</v>
+        <v>13754.17783948361</v>
       </c>
       <c r="N77">
-        <v>-6921.956917320695</v>
+        <v>-7102.932941524426</v>
       </c>
       <c r="O77">
-        <v>-2076.587075196208</v>
+        <v>-2130.879882457328</v>
       </c>
       <c r="P77">
-        <v>-4845.369842124486</v>
+        <v>-4972.053059067099</v>
       </c>
       <c r="Q77">
-        <v>2905.630157875514</v>
+        <v>2778.946940932901</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2014138008172871</v>
+        <v>0.2078977091846741</v>
       </c>
       <c r="T77">
-        <v>2.264370411541027</v>
+        <v>2.358719178688571</v>
       </c>
       <c r="U77">
         <v>0.2196574882221671</v>
       </c>
       <c r="V77">
-        <v>0.14700831068035</v>
+        <v>0.145073990802977</v>
       </c>
       <c r="W77">
-        <v>0.1873660119503374</v>
+        <v>0.1877908997960194</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4900277022678334</v>
+        <v>0.4835799693432566</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1926165340492965</v>
+        <v>0.1943551089315182</v>
       </c>
       <c r="C78">
-        <v>-27835.36747588204</v>
+        <v>-28977.66264680264</v>
       </c>
       <c r="D78">
-        <v>33512.70852411796</v>
+        <v>33194.31435319737</v>
       </c>
       <c r="E78">
-        <v>24004.27600000001</v>
+        <v>24828.17700000001</v>
       </c>
       <c r="F78">
-        <v>62616.476</v>
+        <v>63440.37700000001</v>
       </c>
       <c r="G78">
         <v>1268.4</v>
@@ -7689,37 +7689,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M78">
-        <v>13754.17783948361</v>
+        <v>13935.15386368734</v>
       </c>
       <c r="N78">
-        <v>-7102.932941524426</v>
+        <v>-7283.90896572816</v>
       </c>
       <c r="O78">
-        <v>-2130.879882457328</v>
+        <v>-2185.172689718448</v>
       </c>
       <c r="P78">
-        <v>-4972.053059067099</v>
+        <v>-5098.736276009712</v>
       </c>
       <c r="Q78">
-        <v>2778.946940932901</v>
+        <v>2652.263723990288</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2078977091846741</v>
+        <v>0.2149454356709642</v>
       </c>
       <c r="T78">
-        <v>2.358719178688571</v>
+        <v>2.461272186457639</v>
       </c>
       <c r="U78">
         <v>0.2196574882221671</v>
       </c>
       <c r="V78">
-        <v>0.145073990802977</v>
+        <v>0.1431899130003409</v>
       </c>
       <c r="W78">
-        <v>0.1877908997960194</v>
+        <v>0.1882047515937616</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4835799693432566</v>
+        <v>0.4772997100011364</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1943551089315182</v>
+        <v>0.1960936838137399</v>
       </c>
       <c r="C79">
-        <v>-28977.66264680264</v>
+        <v>-30113.96482074703</v>
       </c>
       <c r="D79">
-        <v>33194.31435319737</v>
+        <v>32881.91317925297</v>
       </c>
       <c r="E79">
-        <v>24828.17700000001</v>
+        <v>25652.07800000001</v>
       </c>
       <c r="F79">
-        <v>63440.37700000001</v>
+        <v>64264.27800000001</v>
       </c>
       <c r="G79">
         <v>1268.4</v>
@@ -7771,37 +7771,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M79">
-        <v>13935.15386368734</v>
+        <v>14116.12988789107</v>
       </c>
       <c r="N79">
-        <v>-7283.90896572816</v>
+        <v>-7464.88498993189</v>
       </c>
       <c r="O79">
-        <v>-2185.172689718448</v>
+        <v>-2239.465496979567</v>
       </c>
       <c r="P79">
-        <v>-5098.736276009712</v>
+        <v>-5225.419492952324</v>
       </c>
       <c r="Q79">
-        <v>2652.263723990288</v>
+        <v>2525.580507047676</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2149454356709642</v>
+        <v>0.222633864565099</v>
       </c>
       <c r="T79">
-        <v>2.461272186457639</v>
+        <v>2.573148194932986</v>
       </c>
       <c r="U79">
         <v>0.2196574882221671</v>
       </c>
       <c r="V79">
-        <v>0.1431899130003409</v>
+        <v>0.1413541448849519</v>
       </c>
       <c r="W79">
-        <v>0.1882047515937616</v>
+        <v>0.1886079918069463</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4772997100011364</v>
+        <v>0.4711804829498398</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1960936838137399</v>
+        <v>0.1978322586959616</v>
       </c>
       <c r="C80">
-        <v>-30113.96482074703</v>
+        <v>-31244.44162554102</v>
       </c>
       <c r="D80">
-        <v>32881.91317925297</v>
+        <v>32575.33737445899</v>
       </c>
       <c r="E80">
-        <v>25652.07800000001</v>
+        <v>26475.97900000001</v>
       </c>
       <c r="F80">
-        <v>64264.27800000001</v>
+        <v>65088.17900000001</v>
       </c>
       <c r="G80">
         <v>1268.4</v>
@@ -7853,37 +7853,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M80">
-        <v>14116.12988789107</v>
+        <v>14297.10591209481</v>
       </c>
       <c r="N80">
-        <v>-7464.88498993189</v>
+        <v>-7645.861014135624</v>
       </c>
       <c r="O80">
-        <v>-2239.465496979567</v>
+        <v>-2293.758304240687</v>
       </c>
       <c r="P80">
-        <v>-5225.419492952324</v>
+        <v>-5352.102709894936</v>
       </c>
       <c r="Q80">
-        <v>2525.580507047676</v>
+        <v>2398.897290105064</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.222633864565099</v>
+        <v>0.2310545247824847</v>
       </c>
       <c r="T80">
-        <v>2.573148194932986</v>
+        <v>2.695679061358367</v>
       </c>
       <c r="U80">
         <v>0.2196574882221671</v>
       </c>
       <c r="V80">
-        <v>0.1413541448849519</v>
+        <v>0.1395648519117247</v>
       </c>
       <c r="W80">
-        <v>0.1886079918069463</v>
+        <v>0.189001023407139</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4711804829498398</v>
+        <v>0.4652161730390822</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1978322586959616</v>
+        <v>0.1995708335781832</v>
       </c>
       <c r="C81">
-        <v>-31244.44162554102</v>
+        <v>-32369.25449522</v>
       </c>
       <c r="D81">
-        <v>32575.33737445899</v>
+        <v>32274.42550478</v>
       </c>
       <c r="E81">
-        <v>26475.97900000001</v>
+        <v>27299.88</v>
       </c>
       <c r="F81">
-        <v>65088.17900000001</v>
+        <v>65912.08</v>
       </c>
       <c r="G81">
         <v>1268.4</v>
@@ -7935,37 +7935,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M81">
-        <v>14297.10591209481</v>
+        <v>14478.08193629854</v>
       </c>
       <c r="N81">
-        <v>-7645.861014135624</v>
+        <v>-7826.837038339354</v>
       </c>
       <c r="O81">
-        <v>-2293.758304240687</v>
+        <v>-2348.051111501806</v>
       </c>
       <c r="P81">
-        <v>-5352.102709894936</v>
+        <v>-5478.785926837548</v>
       </c>
       <c r="Q81">
-        <v>2398.897290105064</v>
+        <v>2272.214073162452</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2310545247824847</v>
+        <v>0.2403172510216089</v>
       </c>
       <c r="T81">
-        <v>2.695679061358367</v>
+        <v>2.830463014426285</v>
       </c>
       <c r="U81">
         <v>0.2196574882221671</v>
       </c>
       <c r="V81">
-        <v>0.1395648519117247</v>
+        <v>0.1378202912628281</v>
       </c>
       <c r="W81">
-        <v>0.189001023407139</v>
+        <v>0.1893842292173268</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4652161730390822</v>
+        <v>0.4594009708760938</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1995708335781832</v>
+        <v>0.2013094084604049</v>
       </c>
       <c r="C82">
-        <v>-32369.25449522</v>
+        <v>-33488.55895348376</v>
       </c>
       <c r="D82">
-        <v>32274.42550478</v>
+        <v>31979.02204651626</v>
       </c>
       <c r="E82">
-        <v>27299.88</v>
+        <v>28123.78100000002</v>
       </c>
       <c r="F82">
-        <v>65912.08</v>
+        <v>66735.98100000001</v>
       </c>
       <c r="G82">
         <v>1268.4</v>
@@ -8017,37 +8017,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M82">
-        <v>14478.08193629854</v>
+        <v>14659.05796050227</v>
       </c>
       <c r="N82">
-        <v>-7826.837038339354</v>
+        <v>-8007.813062543088</v>
       </c>
       <c r="O82">
-        <v>-2348.051111501806</v>
+        <v>-2402.343918762926</v>
       </c>
       <c r="P82">
-        <v>-5478.785926837548</v>
+        <v>-5605.469143780161</v>
       </c>
       <c r="Q82">
-        <v>2272.214073162452</v>
+        <v>2145.530856219839</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2403172510216089</v>
+        <v>0.2505550010753778</v>
       </c>
       <c r="T82">
-        <v>2.830463014426285</v>
+        <v>2.979434752027669</v>
       </c>
       <c r="U82">
         <v>0.2196574882221671</v>
       </c>
       <c r="V82">
-        <v>0.1378202912628281</v>
+        <v>0.1361188061855093</v>
       </c>
       <c r="W82">
-        <v>0.1893842292173268</v>
+        <v>0.1897579731556582</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4594009708760938</v>
+        <v>0.4537293539516976</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2013094084604049</v>
+        <v>0.2030479833426266</v>
       </c>
       <c r="C83">
-        <v>-33488.55895348376</v>
+        <v>-34602.50488172552</v>
       </c>
       <c r="D83">
-        <v>31979.02204651626</v>
+        <v>31688.97711827449</v>
       </c>
       <c r="E83">
-        <v>28123.78100000002</v>
+        <v>28947.68200000002</v>
       </c>
       <c r="F83">
-        <v>66735.98100000001</v>
+        <v>67559.88200000001</v>
       </c>
       <c r="G83">
         <v>1268.4</v>
@@ -8099,37 +8099,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M83">
-        <v>14659.05796050227</v>
+        <v>14840.033984706</v>
       </c>
       <c r="N83">
-        <v>-8007.813062543088</v>
+        <v>-8188.78908674682</v>
       </c>
       <c r="O83">
-        <v>-2402.343918762926</v>
+        <v>-2456.636726024046</v>
       </c>
       <c r="P83">
-        <v>-5605.469143780161</v>
+        <v>-5732.152360722774</v>
       </c>
       <c r="Q83">
-        <v>2145.530856219839</v>
+        <v>2018.847639277226</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2505550010753778</v>
+        <v>0.2619302789128988</v>
       </c>
       <c r="T83">
-        <v>2.979434752027669</v>
+        <v>3.144958904918095</v>
       </c>
       <c r="U83">
         <v>0.2196574882221671</v>
       </c>
       <c r="V83">
-        <v>0.1361188061855093</v>
+        <v>0.1344588207442226</v>
       </c>
       <c r="W83">
-        <v>0.1897579731556582</v>
+        <v>0.1901226013881766</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4537293539516976</v>
+        <v>0.4481960691474085</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2030479833426266</v>
+        <v>0.2047865582248483</v>
       </c>
       <c r="C84">
-        <v>-34602.50488172552</v>
+        <v>-35711.2367726067</v>
       </c>
       <c r="D84">
-        <v>31688.97711827449</v>
+        <v>31404.1462273933</v>
       </c>
       <c r="E84">
-        <v>28947.68200000002</v>
+        <v>29771.58300000001</v>
       </c>
       <c r="F84">
-        <v>67559.88200000001</v>
+        <v>68383.78300000001</v>
       </c>
       <c r="G84">
         <v>1268.4</v>
@@ -8181,37 +8181,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M84">
-        <v>14840.033984706</v>
+        <v>15021.01000890974</v>
       </c>
       <c r="N84">
-        <v>-8188.78908674682</v>
+        <v>-8369.765110950551</v>
       </c>
       <c r="O84">
-        <v>-2456.636726024046</v>
+        <v>-2510.929533285165</v>
       </c>
       <c r="P84">
-        <v>-5732.152360722774</v>
+        <v>-5858.835577665386</v>
       </c>
       <c r="Q84">
-        <v>2018.847639277226</v>
+        <v>1892.164422334614</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2619302789128988</v>
+        <v>0.2746438247313047</v>
       </c>
       <c r="T84">
-        <v>3.144958904918095</v>
+        <v>3.329956487560337</v>
       </c>
       <c r="U84">
         <v>0.2196574882221671</v>
       </c>
       <c r="V84">
-        <v>0.1344588207442226</v>
+        <v>0.1328388349521235</v>
       </c>
       <c r="W84">
-        <v>0.1901226013881766</v>
+        <v>0.1904784433982247</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4481960691474085</v>
+        <v>0.4427961165070783</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2047865582248483</v>
+        <v>0.2065251331070699</v>
       </c>
       <c r="C85">
-        <v>-35711.2367726067</v>
+        <v>-36814.89397007778</v>
       </c>
       <c r="D85">
-        <v>31404.1462273933</v>
+        <v>31124.39002992222</v>
       </c>
       <c r="E85">
-        <v>29771.58300000001</v>
+        <v>30595.48400000001</v>
       </c>
       <c r="F85">
-        <v>68383.78300000001</v>
+        <v>69207.68400000001</v>
       </c>
       <c r="G85">
         <v>1268.4</v>
@@ -8263,37 +8263,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M85">
-        <v>15021.01000890974</v>
+        <v>15201.98603311347</v>
       </c>
       <c r="N85">
-        <v>-8369.765110950551</v>
+        <v>-8550.741135154281</v>
       </c>
       <c r="O85">
-        <v>-2510.929533285165</v>
+        <v>-2565.222340546284</v>
       </c>
       <c r="P85">
-        <v>-5858.835577665386</v>
+        <v>-5985.518794607997</v>
       </c>
       <c r="Q85">
-        <v>1892.164422334614</v>
+        <v>1765.481205392003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2746438247313047</v>
+        <v>0.2889465637770112</v>
       </c>
       <c r="T85">
-        <v>3.329956487560337</v>
+        <v>3.538078768032858</v>
       </c>
       <c r="U85">
         <v>0.2196574882221671</v>
       </c>
       <c r="V85">
-        <v>0.1328388349521235</v>
+        <v>0.1312574202503125</v>
       </c>
       <c r="W85">
-        <v>0.1904784433982247</v>
+        <v>0.1908258129794621</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4427961165070783</v>
+        <v>0.4375247341677083</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2065251331070699</v>
+        <v>0.2082637079892916</v>
       </c>
       <c r="C86">
-        <v>-36814.89397007778</v>
+        <v>-37913.61089668361</v>
       </c>
       <c r="D86">
-        <v>31124.39002992222</v>
+        <v>30849.57410331639</v>
       </c>
       <c r="E86">
-        <v>30595.48400000001</v>
+        <v>31419.38500000001</v>
       </c>
       <c r="F86">
-        <v>69207.68400000001</v>
+        <v>70031.58500000001</v>
       </c>
       <c r="G86">
         <v>1268.4</v>
@@ -8345,37 +8345,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M86">
-        <v>15201.98603311347</v>
+        <v>15382.9620573172</v>
       </c>
       <c r="N86">
-        <v>-8550.741135154281</v>
+        <v>-8731.717159358013</v>
       </c>
       <c r="O86">
-        <v>-2565.222340546284</v>
+        <v>-2619.515147807404</v>
       </c>
       <c r="P86">
-        <v>-5985.518794607997</v>
+        <v>-6112.202011550609</v>
       </c>
       <c r="Q86">
-        <v>1765.481205392003</v>
+        <v>1638.797988449391</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2889465637770111</v>
+        <v>0.3051563346954784</v>
       </c>
       <c r="T86">
-        <v>3.538078768032856</v>
+        <v>3.773950685901712</v>
       </c>
       <c r="U86">
         <v>0.2196574882221671</v>
       </c>
       <c r="V86">
-        <v>0.1312574202503125</v>
+        <v>0.1297132153061912</v>
       </c>
       <c r="W86">
-        <v>0.1908258129794621</v>
+        <v>0.191165009158788</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4375247341677083</v>
+        <v>0.4323773843539707</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2082637079892916</v>
+        <v>0.2100022828715133</v>
       </c>
       <c r="C87">
-        <v>-37913.61089668361</v>
+        <v>-39007.51726893207</v>
       </c>
       <c r="D87">
-        <v>30849.57410331639</v>
+        <v>30579.56873106794</v>
       </c>
       <c r="E87">
-        <v>31419.38500000001</v>
+        <v>32243.28600000001</v>
       </c>
       <c r="F87">
-        <v>70031.58500000001</v>
+        <v>70855.486</v>
       </c>
       <c r="G87">
         <v>1268.4</v>
@@ -8427,37 +8427,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M87">
-        <v>15382.9620573172</v>
+        <v>15563.93808152093</v>
       </c>
       <c r="N87">
-        <v>-8731.717159358013</v>
+        <v>-8912.693183561745</v>
       </c>
       <c r="O87">
-        <v>-2619.515147807404</v>
+        <v>-2673.807955068523</v>
       </c>
       <c r="P87">
-        <v>-6112.202011550609</v>
+        <v>-6238.885228493222</v>
       </c>
       <c r="Q87">
-        <v>1638.797988449391</v>
+        <v>1512.114771506778</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3051563346954784</v>
+        <v>0.3236817871737269</v>
       </c>
       <c r="T87">
-        <v>3.773950685901712</v>
+        <v>4.043518592037549</v>
       </c>
       <c r="U87">
         <v>0.2196574882221671</v>
       </c>
       <c r="V87">
-        <v>0.1297132153061912</v>
+        <v>0.1282049221049564</v>
       </c>
       <c r="W87">
-        <v>0.191165009158788</v>
+        <v>0.1914963170548738</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4323773843539707</v>
+        <v>0.4273497403498546</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2100022828715133</v>
+        <v>0.2117408577537349</v>
       </c>
       <c r="C88">
-        <v>-39007.51726893207</v>
+        <v>-40096.73830145088</v>
       </c>
       <c r="D88">
-        <v>30579.56873106794</v>
+        <v>30314.24869854912</v>
       </c>
       <c r="E88">
-        <v>32243.28600000001</v>
+        <v>33067.18700000001</v>
       </c>
       <c r="F88">
-        <v>70855.486</v>
+        <v>71679.387</v>
       </c>
       <c r="G88">
         <v>1268.4</v>
@@ -8509,37 +8509,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M88">
-        <v>15563.93808152093</v>
+        <v>15744.91410572466</v>
       </c>
       <c r="N88">
-        <v>-8912.693183561745</v>
+        <v>-9093.669207765475</v>
       </c>
       <c r="O88">
-        <v>-2673.807955068523</v>
+        <v>-2728.100762329642</v>
       </c>
       <c r="P88">
-        <v>-6238.885228493222</v>
+        <v>-6365.568445435832</v>
       </c>
       <c r="Q88">
-        <v>1512.114771506778</v>
+        <v>1385.431554564168</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3236817871737269</v>
+        <v>0.3450573092640136</v>
       </c>
       <c r="T88">
-        <v>4.043518592037549</v>
+        <v>4.354558483732745</v>
       </c>
       <c r="U88">
         <v>0.2196574882221671</v>
       </c>
       <c r="V88">
-        <v>0.1282049221049564</v>
+        <v>0.1267313023106466</v>
       </c>
       <c r="W88">
-        <v>0.1914963170548738</v>
+        <v>0.1918200086774864</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4273497403498546</v>
+        <v>0.422437674368822</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2117408577537349</v>
+        <v>0.2134794326359566</v>
       </c>
       <c r="C89">
-        <v>-40096.73830145088</v>
+        <v>-41181.39490060796</v>
       </c>
       <c r="D89">
-        <v>30314.24869854912</v>
+        <v>30053.49309939204</v>
       </c>
       <c r="E89">
-        <v>33067.18700000001</v>
+        <v>33891.088</v>
       </c>
       <c r="F89">
-        <v>71679.387</v>
+        <v>72503.288</v>
       </c>
       <c r="G89">
         <v>1268.4</v>
@@ -8591,37 +8591,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M89">
-        <v>15744.91410572466</v>
+        <v>15925.89012992839</v>
       </c>
       <c r="N89">
-        <v>-9093.669207765475</v>
+        <v>-9274.645231969207</v>
       </c>
       <c r="O89">
-        <v>-2728.100762329642</v>
+        <v>-2782.393569590762</v>
       </c>
       <c r="P89">
-        <v>-6365.568445435832</v>
+        <v>-6492.251662378445</v>
       </c>
       <c r="Q89">
-        <v>1385.431554564168</v>
+        <v>1258.748337621555</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3450573092640136</v>
+        <v>0.3699954183693481</v>
       </c>
       <c r="T89">
-        <v>4.354558483732745</v>
+        <v>4.717438357377142</v>
       </c>
       <c r="U89">
         <v>0.2196574882221671</v>
       </c>
       <c r="V89">
-        <v>0.1267313023106466</v>
+        <v>0.1252911738752983</v>
       </c>
       <c r="W89">
-        <v>0.1918200086774864</v>
+        <v>0.1921363436723123</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.422437674368822</v>
+        <v>0.4176372462509944</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2134794326359566</v>
+        <v>0.2152180075181783</v>
       </c>
       <c r="C90">
-        <v>-41181.39490060796</v>
+        <v>-42261.60384822397</v>
       </c>
       <c r="D90">
-        <v>30053.49309939204</v>
+        <v>29797.18515177604</v>
       </c>
       <c r="E90">
-        <v>33891.088</v>
+        <v>34714.98900000002</v>
       </c>
       <c r="F90">
-        <v>72503.288</v>
+        <v>73327.18900000001</v>
       </c>
       <c r="G90">
         <v>1268.4</v>
@@ -8673,37 +8673,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M90">
-        <v>15925.89012992839</v>
+        <v>16106.86615413213</v>
       </c>
       <c r="N90">
-        <v>-9274.645231969207</v>
+        <v>-9455.621256172941</v>
       </c>
       <c r="O90">
-        <v>-2782.393569590762</v>
+        <v>-2836.686376851882</v>
       </c>
       <c r="P90">
-        <v>-6492.251662378445</v>
+        <v>-6618.934879321059</v>
       </c>
       <c r="Q90">
-        <v>1258.748337621555</v>
+        <v>1132.065120678941</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3699954183693481</v>
+        <v>0.399467729130198</v>
       </c>
       <c r="T90">
-        <v>4.717438357377142</v>
+        <v>5.146296389865973</v>
       </c>
       <c r="U90">
         <v>0.2196574882221671</v>
       </c>
       <c r="V90">
-        <v>0.1252911738752983</v>
+        <v>0.1238834078766994</v>
       </c>
       <c r="W90">
-        <v>0.1921363436723123</v>
+        <v>0.1924455700155691</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4176372462509944</v>
+        <v>0.4129446929223315</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2152180075181783</v>
+        <v>0.2169565824003999</v>
       </c>
       <c r="C91">
-        <v>-42261.60384822397</v>
+        <v>-43337.47797596376</v>
       </c>
       <c r="D91">
-        <v>29797.18515177604</v>
+        <v>29545.21202403625</v>
       </c>
       <c r="E91">
-        <v>34714.98900000002</v>
+        <v>35538.89000000001</v>
       </c>
       <c r="F91">
-        <v>73327.18900000001</v>
+        <v>74151.09000000001</v>
       </c>
       <c r="G91">
         <v>1268.4</v>
@@ -8755,37 +8755,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M91">
-        <v>16106.86615413213</v>
+        <v>16287.84217833586</v>
       </c>
       <c r="N91">
-        <v>-9455.621256172941</v>
+        <v>-9636.597280376673</v>
       </c>
       <c r="O91">
-        <v>-2836.686376851882</v>
+        <v>-2890.979184113002</v>
       </c>
       <c r="P91">
-        <v>-6618.934879321059</v>
+        <v>-6745.618096263671</v>
       </c>
       <c r="Q91">
-        <v>1132.065120678941</v>
+        <v>1005.381903736329</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.399467729130198</v>
+        <v>0.4348345020432178</v>
       </c>
       <c r="T91">
-        <v>5.146296389865973</v>
+        <v>5.660926028852571</v>
       </c>
       <c r="U91">
         <v>0.2196574882221671</v>
       </c>
       <c r="V91">
-        <v>0.1238834078766994</v>
+        <v>0.1225069255669583</v>
       </c>
       <c r="W91">
-        <v>0.1924455700155691</v>
+        <v>0.1927479246623091</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4129446929223315</v>
+        <v>0.4083564185565278</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2169565824003999</v>
+        <v>0.2186951572826216</v>
       </c>
       <c r="C92">
-        <v>-43337.47797596376</v>
+        <v>-44409.12633095396</v>
       </c>
       <c r="D92">
-        <v>29545.21202403625</v>
+        <v>29297.46466904605</v>
       </c>
       <c r="E92">
-        <v>35538.89000000001</v>
+        <v>36362.79100000001</v>
       </c>
       <c r="F92">
-        <v>74151.09000000001</v>
+        <v>74974.99100000001</v>
       </c>
       <c r="G92">
         <v>1268.4</v>
@@ -8837,37 +8837,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M92">
-        <v>16287.84217833586</v>
+        <v>16468.81820253959</v>
       </c>
       <c r="N92">
-        <v>-9636.597280376673</v>
+        <v>-9817.573304580403</v>
       </c>
       <c r="O92">
-        <v>-2890.979184113002</v>
+        <v>-2945.271991374121</v>
       </c>
       <c r="P92">
-        <v>-6745.618096263671</v>
+        <v>-6872.301313206282</v>
       </c>
       <c r="Q92">
-        <v>1005.381903736329</v>
+        <v>878.6986867937176</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4348345020432178</v>
+        <v>0.4780605578257975</v>
       </c>
       <c r="T92">
-        <v>5.660926028852571</v>
+        <v>6.289917809836189</v>
       </c>
       <c r="U92">
         <v>0.2196574882221671</v>
       </c>
       <c r="V92">
-        <v>0.1225069255669583</v>
+        <v>0.1211606956156731</v>
       </c>
       <c r="W92">
-        <v>0.1927479246623091</v>
+        <v>0.1930436341519778</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4083564185565278</v>
+        <v>0.4038689853855769</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2186951572826216</v>
+        <v>0.2204337321648433</v>
       </c>
       <c r="C93">
-        <v>-44409.12633095396</v>
+        <v>-45476.65433313706</v>
       </c>
       <c r="D93">
-        <v>29297.46466904605</v>
+        <v>29053.83766686295</v>
       </c>
       <c r="E93">
-        <v>36362.79100000001</v>
+        <v>37186.69200000001</v>
       </c>
       <c r="F93">
-        <v>74974.99100000001</v>
+        <v>75798.89200000001</v>
       </c>
       <c r="G93">
         <v>1268.4</v>
@@ -8919,37 +8919,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M93">
-        <v>16468.81820253959</v>
+        <v>16649.79422674332</v>
       </c>
       <c r="N93">
-        <v>-9817.573304580403</v>
+        <v>-9998.549328784136</v>
       </c>
       <c r="O93">
-        <v>-2945.271991374121</v>
+        <v>-2999.564798635241</v>
       </c>
       <c r="P93">
-        <v>-6872.301313206282</v>
+        <v>-6998.984530148895</v>
       </c>
       <c r="Q93">
-        <v>878.6986867937176</v>
+        <v>752.0154698511051</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4780605578257975</v>
+        <v>0.5320931275540224</v>
       </c>
       <c r="T93">
-        <v>6.289917809836189</v>
+        <v>7.076157536065716</v>
       </c>
       <c r="U93">
         <v>0.2196574882221671</v>
       </c>
       <c r="V93">
-        <v>0.1211606956156731</v>
+        <v>0.119843731532894</v>
       </c>
       <c r="W93">
-        <v>0.1930436341519778</v>
+        <v>0.1933329151744799</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4038689853855769</v>
+        <v>0.3994791051096468</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2204337321648433</v>
+        <v>0.2221723070470649</v>
       </c>
       <c r="C94">
-        <v>-45476.65433313706</v>
+        <v>-46540.16392483936</v>
       </c>
       <c r="D94">
-        <v>29053.83766686295</v>
+        <v>28814.22907516064</v>
       </c>
       <c r="E94">
-        <v>37186.69200000001</v>
+        <v>38010.59300000001</v>
       </c>
       <c r="F94">
-        <v>75798.89200000001</v>
+        <v>76622.79300000001</v>
       </c>
       <c r="G94">
         <v>1268.4</v>
@@ -9001,37 +9001,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M94">
-        <v>16649.79422674332</v>
+        <v>16830.77025094705</v>
       </c>
       <c r="N94">
-        <v>-9998.549328784136</v>
+        <v>-10179.52535298787</v>
       </c>
       <c r="O94">
-        <v>-2999.564798635241</v>
+        <v>-3053.85760589636</v>
       </c>
       <c r="P94">
-        <v>-6998.984530148895</v>
+        <v>-7125.667747091506</v>
       </c>
       <c r="Q94">
-        <v>752.0154698511051</v>
+        <v>625.3322529084935</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5320931275540224</v>
+        <v>0.6015635743474541</v>
       </c>
       <c r="T94">
-        <v>7.076157536065716</v>
+        <v>8.087037184075104</v>
       </c>
       <c r="U94">
         <v>0.2196574882221671</v>
       </c>
       <c r="V94">
-        <v>0.119843731532894</v>
+        <v>0.1185550892583468</v>
       </c>
       <c r="W94">
-        <v>0.1933329151744799</v>
+        <v>0.1936159750997238</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3994791051096468</v>
+        <v>0.3951836308611559</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2221723070470649</v>
+        <v>0.2239108819292866</v>
       </c>
       <c r="C95">
-        <v>-46540.16392483936</v>
+        <v>-47599.75371299853</v>
       </c>
       <c r="D95">
-        <v>28814.22907516064</v>
+        <v>28578.54028700147</v>
       </c>
       <c r="E95">
-        <v>38010.59300000001</v>
+        <v>38834.49400000001</v>
       </c>
       <c r="F95">
-        <v>76622.79300000001</v>
+        <v>77446.694</v>
       </c>
       <c r="G95">
         <v>1268.4</v>
@@ -9083,37 +9083,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M95">
-        <v>16830.77025094705</v>
+        <v>17011.74627515078</v>
       </c>
       <c r="N95">
-        <v>-10179.52535298787</v>
+        <v>-10360.5013771916</v>
       </c>
       <c r="O95">
-        <v>-3053.85760589636</v>
+        <v>-3108.150413157479</v>
       </c>
       <c r="P95">
-        <v>-7125.667747091506</v>
+        <v>-7252.350964034118</v>
       </c>
       <c r="Q95">
-        <v>625.3322529084935</v>
+        <v>498.6490359658819</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6015635743474541</v>
+        <v>0.6941908367386967</v>
       </c>
       <c r="T95">
-        <v>8.087037184075104</v>
+        <v>9.43487671475429</v>
       </c>
       <c r="U95">
         <v>0.2196574882221671</v>
       </c>
       <c r="V95">
-        <v>0.1185550892583468</v>
+        <v>0.1172938649045346</v>
       </c>
       <c r="W95">
-        <v>0.1936159750997238</v>
+        <v>0.1938930124733668</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3951836308611559</v>
+        <v>0.3909795496817819</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2239108819292866</v>
+        <v>0.2256494568115083</v>
       </c>
       <c r="C96">
-        <v>-47599.75371299853</v>
+        <v>-48655.5191044675</v>
       </c>
       <c r="D96">
-        <v>28578.54028700147</v>
+        <v>28346.67589553251</v>
       </c>
       <c r="E96">
-        <v>38834.49400000001</v>
+        <v>39658.39500000002</v>
       </c>
       <c r="F96">
-        <v>77446.694</v>
+        <v>78270.59500000002</v>
       </c>
       <c r="G96">
         <v>1268.4</v>
@@ -9165,37 +9165,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M96">
-        <v>17011.74627515078</v>
+        <v>17192.72229935452</v>
       </c>
       <c r="N96">
-        <v>-10360.5013771916</v>
+        <v>-10541.47740139533</v>
       </c>
       <c r="O96">
-        <v>-3108.150413157479</v>
+        <v>-3162.4432204186</v>
       </c>
       <c r="P96">
-        <v>-7252.350964034118</v>
+        <v>-7379.034180976734</v>
       </c>
       <c r="Q96">
-        <v>498.6490359658819</v>
+        <v>371.9658190232658</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6941908367386967</v>
+        <v>0.8238690040864365</v>
       </c>
       <c r="T96">
-        <v>9.43487671475429</v>
+        <v>11.32185205770515</v>
       </c>
       <c r="U96">
         <v>0.2196574882221671</v>
       </c>
       <c r="V96">
-        <v>0.1172938649045346</v>
+        <v>0.1160591926423816</v>
       </c>
       <c r="W96">
-        <v>0.1938930124733668</v>
+        <v>0.194164217481249</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3909795496817819</v>
+        <v>0.3868639754746052</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2256494568115083</v>
+        <v>0.22738803169373</v>
       </c>
       <c r="C97">
-        <v>-48655.5191044675</v>
+        <v>-49707.55243478483</v>
       </c>
       <c r="D97">
-        <v>28346.67589553251</v>
+        <v>28118.54356521519</v>
       </c>
       <c r="E97">
-        <v>39658.39500000002</v>
+        <v>40482.29600000002</v>
       </c>
       <c r="F97">
-        <v>78270.59500000002</v>
+        <v>79094.49600000001</v>
       </c>
       <c r="G97">
         <v>1268.4</v>
@@ -9247,37 +9247,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M97">
-        <v>17192.72229935452</v>
+        <v>17373.69832355825</v>
       </c>
       <c r="N97">
-        <v>-10541.47740139533</v>
+        <v>-10722.45342559906</v>
       </c>
       <c r="O97">
-        <v>-3162.4432204186</v>
+        <v>-3216.736027679719</v>
       </c>
       <c r="P97">
-        <v>-7379.034180976734</v>
+        <v>-7505.717397919345</v>
       </c>
       <c r="Q97">
-        <v>371.9658190232658</v>
+        <v>245.2826020806551</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8238690040864365</v>
+        <v>1.018386255108046</v>
       </c>
       <c r="T97">
-        <v>11.32185205770515</v>
+        <v>14.15231507213145</v>
       </c>
       <c r="U97">
         <v>0.2196574882221671</v>
       </c>
       <c r="V97">
-        <v>0.1160591926423816</v>
+        <v>0.1148502427190234</v>
       </c>
       <c r="W97">
-        <v>0.194164217481249</v>
+        <v>0.1944297723848002</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3868639754746052</v>
+        <v>0.3828341423967447</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.22738803169373</v>
+        <v>0.2291266065759516</v>
       </c>
       <c r="C98">
-        <v>-49707.55243478481</v>
+        <v>-50755.94309077694</v>
       </c>
       <c r="D98">
-        <v>28118.54356521519</v>
+        <v>27894.05390922306</v>
       </c>
       <c r="E98">
-        <v>40482.296</v>
+        <v>41306.197</v>
       </c>
       <c r="F98">
-        <v>79094.496</v>
+        <v>79918.397</v>
       </c>
       <c r="G98">
         <v>1268.4</v>
@@ -9329,37 +9329,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M98">
-        <v>17373.69832355824</v>
+        <v>17554.67434776197</v>
       </c>
       <c r="N98">
-        <v>-10722.45342559906</v>
+        <v>-10903.42944980279</v>
       </c>
       <c r="O98">
-        <v>-3216.736027679718</v>
+        <v>-3271.028834940837</v>
       </c>
       <c r="P98">
-        <v>-7505.717397919342</v>
+        <v>-7632.400614861954</v>
       </c>
       <c r="Q98">
-        <v>245.2826020806579</v>
+        <v>118.5993851380463</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.018386255108043</v>
+        <v>1.342581673477391</v>
       </c>
       <c r="T98">
-        <v>14.15231507213141</v>
+        <v>18.86975342950855</v>
       </c>
       <c r="U98">
         <v>0.2196574882221671</v>
       </c>
       <c r="V98">
-        <v>0.1148502427190234</v>
+        <v>0.1136662195982088</v>
       </c>
       <c r="W98">
-        <v>0.1944297723848002</v>
+        <v>0.1946898519295153</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3828341423967448</v>
+        <v>0.378887398660696</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2291266065759516</v>
+        <v>0.2308651814581733</v>
       </c>
       <c r="C99">
-        <v>-50755.94309077694</v>
+        <v>-51800.77762733374</v>
       </c>
       <c r="D99">
-        <v>27894.05390922306</v>
+        <v>27673.12037266627</v>
       </c>
       <c r="E99">
-        <v>41306.197</v>
+        <v>42130.09800000001</v>
       </c>
       <c r="F99">
-        <v>79918.397</v>
+        <v>80742.29800000001</v>
       </c>
       <c r="G99">
         <v>1268.4</v>
@@ -9411,37 +9411,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M99">
-        <v>17554.67434776197</v>
+        <v>17735.65037196571</v>
       </c>
       <c r="N99">
-        <v>-10903.42944980279</v>
+        <v>-11084.40547400653</v>
       </c>
       <c r="O99">
-        <v>-3271.028834940837</v>
+        <v>-3325.321642201958</v>
       </c>
       <c r="P99">
-        <v>-7632.400614861954</v>
+        <v>-7759.08383180457</v>
       </c>
       <c r="Q99">
-        <v>118.5993851380463</v>
+        <v>-8.083831804569854</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.342581673477391</v>
+        <v>1.990972510216087</v>
       </c>
       <c r="T99">
-        <v>18.86975342950855</v>
+        <v>28.30463014426283</v>
       </c>
       <c r="U99">
         <v>0.2196574882221671</v>
       </c>
       <c r="V99">
-        <v>0.1136662195982088</v>
+        <v>0.1125063602145536</v>
       </c>
       <c r="W99">
-        <v>0.1946898519295153</v>
+        <v>0.1949446237284199</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.378887398660696</v>
+        <v>0.3750212007151785</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2308651814581733</v>
+        <v>0.232603756340395</v>
       </c>
       <c r="C100">
-        <v>-51800.77762733374</v>
+        <v>-52842.13987867824</v>
       </c>
       <c r="D100">
-        <v>27673.12037266627</v>
+        <v>27455.65912132177</v>
       </c>
       <c r="E100">
-        <v>42130.09800000001</v>
+        <v>42953.99900000001</v>
       </c>
       <c r="F100">
-        <v>80742.29800000001</v>
+        <v>81566.19900000001</v>
       </c>
       <c r="G100">
         <v>1268.4</v>
@@ -9493,37 +9493,37 @@
         <v>6651.244897959185</v>
       </c>
       <c r="M100">
-        <v>17735.65037196571</v>
+        <v>17916.62639616944</v>
       </c>
       <c r="N100">
-        <v>-11084.40547400653</v>
+        <v>-11265.38149821026</v>
       </c>
       <c r="O100">
-        <v>-3325.321642201958</v>
+        <v>-3379.614449463077</v>
       </c>
       <c r="P100">
-        <v>-7759.08383180457</v>
+        <v>-7885.767048747181</v>
       </c>
       <c r="Q100">
-        <v>-8.083831804569854</v>
+        <v>-134.7670487471805</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.990972510216087</v>
+        <v>3.936145020432174</v>
       </c>
       <c r="T100">
-        <v>28.30463014426283</v>
+        <v>56.60926028852565</v>
       </c>
       <c r="U100">
         <v>0.2196574882221671</v>
       </c>
       <c r="V100">
-        <v>0.1125063602145536</v>
+        <v>0.1113699323335985</v>
       </c>
       <c r="W100">
-        <v>0.1949446237284199</v>
+        <v>0.1951942486222962</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3750212007151785</v>
+        <v>0.3712331077786616</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.232603756340395</v>
-      </c>
-      <c r="C101">
-        <v>-52842.13987867824</v>
-      </c>
-      <c r="D101">
-        <v>27455.65912132177</v>
-      </c>
-      <c r="E101">
-        <v>42953.99900000001</v>
-      </c>
-      <c r="F101">
-        <v>81566.19900000001</v>
-      </c>
-      <c r="G101">
-        <v>1268.4</v>
-      </c>
-      <c r="H101">
-        <v>43777.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14402.24489795918</v>
-      </c>
-      <c r="K101">
-        <v>7751</v>
-      </c>
-      <c r="L101">
-        <v>6651.244897959185</v>
-      </c>
-      <c r="M101">
-        <v>17916.62639616944</v>
-      </c>
-      <c r="N101">
-        <v>-11265.38149821026</v>
-      </c>
-      <c r="O101">
-        <v>-3379.614449463077</v>
-      </c>
-      <c r="P101">
-        <v>-7885.767048747181</v>
-      </c>
-      <c r="Q101">
-        <v>-134.7670487471805</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.936145020432174</v>
-      </c>
-      <c r="T101">
-        <v>56.60926028852565</v>
-      </c>
-      <c r="U101">
-        <v>0.2196574882221671</v>
-      </c>
-      <c r="V101">
-        <v>0.1113699323335985</v>
-      </c>
-      <c r="W101">
-        <v>0.1951942486222962</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3712331077786616</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
